--- a/features/quotation/data/Attractions.xlsx
+++ b/features/quotation/data/Attractions.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\VISHAKH NAIR\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{737634F9-4430-4482-8CBA-574755DBC79D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D0EF5C4-EC5E-4AF8-BD8F-EEA7DA9803A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{440128AA-9F10-42BF-BF5F-9CF7A067EEF0}"/>
   </bookViews>
@@ -16,6 +16,9 @@
     <sheet name="Attractions" sheetId="1" r:id="rId1"/>
     <sheet name="Ferry Time &amp; Tickets" sheetId="2" r:id="rId2"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Attractions!$A$1:$G$708</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -32,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2708" uniqueCount="1096">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2708" uniqueCount="1116">
   <si>
     <t>City</t>
   </si>
@@ -2318,6 +2321,20 @@
   </si>
   <si>
     <t>Yona Beach Club - Afternoon Ladies Pass</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Yona Beach Club - Morning Pool Sofa (2 Pax)                             </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> Discuss for THIS ENTIRE YONA</t>
+    </r>
   </si>
   <si>
     <t>Phi Phi Island Tour by Big Boat + Lunch + SIC Transfer **Economy Seats** Excluding NPF</t>
@@ -2597,9 +2614,6 @@
     <t>EasyKart Bangkok</t>
   </si>
   <si>
-    <t>ASN Sea Tours</t>
-  </si>
-  <si>
     <t>Baan Teelanka (Upside Down House )</t>
   </si>
   <si>
@@ -2616,9 +2630,6 @@
   </si>
   <si>
     <t>Good Day</t>
-  </si>
-  <si>
-    <t>Green Beach</t>
   </si>
   <si>
     <t>Krabi</t>
@@ -2991,9 +3002,6 @@
     <t>Aonang - Phuket</t>
   </si>
   <si>
-    <t>WangSai Speed Boat</t>
-  </si>
-  <si>
     <t>Hong Island By Speed Boat Day Trip + Lunch Box + SIC Transfer - Exclude NPF</t>
   </si>
   <si>
@@ -3058,9 +3066,6 @@
   </si>
   <si>
     <t xml:space="preserve">HONG ISLAND KAYA KING SPEED BOAT ( PHUKET ) EXC NPF </t>
-  </si>
-  <si>
-    <t>Thai Smiles - Sharing</t>
   </si>
   <si>
     <t xml:space="preserve">PHUKET CITY TOUR SIC </t>
@@ -3321,70 +3326,140 @@
     <t>Guide Sai - Safari World</t>
   </si>
   <si>
-    <t>Golden Buddha Ticket Price - Wat Tramit</t>
-  </si>
-  <si>
-    <t>Marble Buddha Ticket Price - Wat Benchamabophit</t>
-  </si>
-  <si>
-    <t>Reclining Buddha Ticket Price - Wat Pho</t>
-  </si>
-  <si>
-    <t>Mini Reclining Buddha Ticket Price</t>
-  </si>
-  <si>
-    <t>Wat Arun Ticket Price</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Boat From Wat Pho to Wat Arun </t>
-  </si>
-  <si>
-    <t>Bangkok Temples</t>
-  </si>
-  <si>
-    <t>Ayuthaya Temples</t>
-  </si>
-  <si>
-    <t>Wat Mahathat</t>
-  </si>
-  <si>
-    <t>Wat Phra Si Sanphet</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Wat Chaiwatthanaram </t>
-  </si>
-  <si>
-    <t>Wat Yai Chai Mongkhon</t>
-  </si>
-  <si>
-    <t>Wat Phanan Choeng</t>
-  </si>
-  <si>
-    <t>Grand Palace + Emerald Buddha Ticket Price</t>
-  </si>
-  <si>
     <r>
-      <t xml:space="preserve">Yona Beach Club - Morning Pool Sofa (2 Pax)                             </t>
+      <t xml:space="preserve">Guide Sai - Grand Palace + Emerald Buddha + Wat Arun Temple of Dawn                                          </t>
     </r>
     <r>
       <rPr>
+        <b/>
         <sz val="11"/>
         <color rgb="FFFF0000"/>
-        <rFont val="Aptos"/>
+        <rFont val="Calibri"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve"> </t>
+      <t>Fixed Price for 01 GUIDE</t>
     </r>
   </si>
   <si>
-    <t xml:space="preserve">Guide Sai - Grand Palace + Emerald Buddha + Wat Arun Temple of Dawn                                         </t>
+    <t>Golden Buddha Ticket Price - Wat Tramit</t>
+  </si>
+  <si>
+    <t>Marble Buddha Ticket Price - Wat Benchamabophit</t>
+  </si>
+  <si>
+    <t>Reclining Buddha Ticket Price - Wat Pho</t>
+  </si>
+  <si>
+    <t>Mini Reclining Buddha Ticket Price</t>
+  </si>
+  <si>
+    <t>Wat Arun Ticket Price</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Boat From Wat Pho to Wat Arun </t>
+  </si>
+  <si>
+    <t>Bangkok Temples</t>
+  </si>
+  <si>
+    <t>Ayuthaya Temples</t>
+  </si>
+  <si>
+    <t>Wat Mahathat</t>
+  </si>
+  <si>
+    <t>Wat Phra Si Sanphet</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wat Chaiwatthanaram </t>
+  </si>
+  <si>
+    <t>Wat Yai Chai Mongkhon</t>
+  </si>
+  <si>
+    <t>Wat Phanan Choeng</t>
+  </si>
+  <si>
+    <t>Grand Palace + Emerald Buddha Ticket Price</t>
+  </si>
+  <si>
+    <t>Coral Island Tour by ASN Sea Tours</t>
+  </si>
+  <si>
+    <t>Phi Phi Island Tour by Good Day</t>
+  </si>
+  <si>
+    <t>James Bond Island Tour by Good Day</t>
+  </si>
+  <si>
+    <t>3 Khai Island Tour by Good Day</t>
+  </si>
+  <si>
+    <t>Krabi 3 Island Tour by Good Day</t>
+  </si>
+  <si>
+    <t>Surin Island Day Tour By Good Day</t>
+  </si>
+  <si>
+    <t>Similan Island Tour by Good Day</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Coral Island Tour HKT by Good Day </t>
+  </si>
+  <si>
+    <t>Koh Tao &amp; Koh Nangyuan Tour By Good Day</t>
+  </si>
+  <si>
+    <t>Angthong National Park By Good Day</t>
+  </si>
+  <si>
+    <t>Phi Phi Island Tour Krabi by Good Day</t>
+  </si>
+  <si>
+    <t>4 Island Tour Krabi by Good Day</t>
+  </si>
+  <si>
+    <t>7 Island Tour Krabi by Good Day</t>
+  </si>
+  <si>
+    <t>Emerald Pool &amp; Hot Spring by Good Day</t>
+  </si>
+  <si>
+    <t>Hong Island Tour by Good Day</t>
+  </si>
+  <si>
+    <t>Half Day Krabi City Tour by Good Day</t>
+  </si>
+  <si>
+    <t>Half Day Ao Thalane Tour by Good Day</t>
+  </si>
+  <si>
+    <t>Phi Phi Island Tour by Green Beach</t>
+  </si>
+  <si>
+    <t>Hong Island Tour by Green Beach</t>
+  </si>
+  <si>
+    <t>Phi Phi Island Tour by WangSai</t>
+  </si>
+  <si>
+    <t>4 Island Tour Krabi  by WangSai</t>
+  </si>
+  <si>
+    <t>Hong Island Tour by WangSai</t>
+  </si>
+  <si>
+    <t>Thai Smiles - BKK Sharing</t>
+  </si>
+  <si>
+    <t>Thai Smiles - HKT Sharing</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="26" x14ac:knownFonts="1">
+  <fonts count="27" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -3550,6 +3625,13 @@
     <font>
       <sz val="10"/>
       <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
       <family val="2"/>
     </font>
   </fonts>
@@ -4057,16 +4139,12 @@
     <xf numFmtId="0" fontId="23" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="25" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
@@ -4078,10 +4156,14 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -4465,7 +4547,7 @@
         <v>721</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>791</v>
+        <v>792</v>
       </c>
       <c r="G1" s="3" t="s">
         <v>4</v>
@@ -4486,7 +4568,7 @@
       </c>
       <c r="E2" s="4"/>
       <c r="F2" s="3" t="s">
-        <v>792</v>
+        <v>793</v>
       </c>
       <c r="G2" s="3" t="s">
         <v>8</v>
@@ -4507,7 +4589,7 @@
       </c>
       <c r="E3" s="4"/>
       <c r="F3" s="3" t="s">
-        <v>792</v>
+        <v>793</v>
       </c>
       <c r="G3" s="3" t="s">
         <v>10</v>
@@ -4528,7 +4610,7 @@
       </c>
       <c r="E4" s="4"/>
       <c r="F4" s="3" t="s">
-        <v>792</v>
+        <v>793</v>
       </c>
       <c r="G4" s="3" t="s">
         <v>12</v>
@@ -4549,7 +4631,7 @@
       </c>
       <c r="E5" s="4"/>
       <c r="F5" s="3" t="s">
-        <v>792</v>
+        <v>793</v>
       </c>
       <c r="G5" s="3" t="s">
         <v>14</v>
@@ -4570,7 +4652,7 @@
       </c>
       <c r="E6" s="4"/>
       <c r="F6" s="3" t="s">
-        <v>792</v>
+        <v>793</v>
       </c>
       <c r="G6" s="3" t="s">
         <v>16</v>
@@ -4591,7 +4673,7 @@
       </c>
       <c r="E7" s="4"/>
       <c r="F7" s="3" t="s">
-        <v>792</v>
+        <v>793</v>
       </c>
       <c r="G7" s="3" t="s">
         <v>18</v>
@@ -4612,7 +4694,7 @@
       </c>
       <c r="E8" s="4"/>
       <c r="F8" s="3" t="s">
-        <v>792</v>
+        <v>793</v>
       </c>
       <c r="G8" s="3" t="s">
         <v>20</v>
@@ -4633,7 +4715,7 @@
       </c>
       <c r="E9" s="4"/>
       <c r="F9" s="3" t="s">
-        <v>793</v>
+        <v>794</v>
       </c>
       <c r="G9" s="3" t="s">
         <v>22</v>
@@ -4654,7 +4736,7 @@
       </c>
       <c r="E10" s="4"/>
       <c r="F10" s="3" t="s">
-        <v>793</v>
+        <v>794</v>
       </c>
       <c r="G10" s="3" t="s">
         <v>24</v>
@@ -4675,7 +4757,7 @@
       </c>
       <c r="E11" s="4"/>
       <c r="F11" s="3" t="s">
-        <v>794</v>
+        <v>795</v>
       </c>
       <c r="G11" s="3" t="s">
         <v>26</v>
@@ -4696,7 +4778,7 @@
       </c>
       <c r="E12" s="4"/>
       <c r="F12" s="3" t="s">
-        <v>794</v>
+        <v>795</v>
       </c>
       <c r="G12" s="3" t="s">
         <v>28</v>
@@ -4717,7 +4799,7 @@
       </c>
       <c r="E13" s="4"/>
       <c r="F13" s="3" t="s">
-        <v>794</v>
+        <v>795</v>
       </c>
       <c r="G13" s="3" t="s">
         <v>28</v>
@@ -4738,7 +4820,7 @@
       </c>
       <c r="E14" s="4"/>
       <c r="F14" s="3" t="s">
-        <v>794</v>
+        <v>795</v>
       </c>
       <c r="G14" s="3" t="s">
         <v>28</v>
@@ -4759,7 +4841,7 @@
       </c>
       <c r="E15" s="4"/>
       <c r="F15" s="3" t="s">
-        <v>794</v>
+        <v>795</v>
       </c>
       <c r="G15" s="3" t="s">
         <v>28</v>
@@ -4780,7 +4862,7 @@
       </c>
       <c r="E16" s="4"/>
       <c r="F16" s="3" t="s">
-        <v>794</v>
+        <v>795</v>
       </c>
       <c r="G16" s="3"/>
     </row>
@@ -4799,7 +4881,7 @@
       </c>
       <c r="E17" s="4"/>
       <c r="F17" s="3" t="s">
-        <v>794</v>
+        <v>795</v>
       </c>
       <c r="G17" s="3"/>
     </row>
@@ -4818,7 +4900,7 @@
       </c>
       <c r="E18" s="4"/>
       <c r="F18" s="3" t="s">
-        <v>799</v>
+        <v>800</v>
       </c>
       <c r="G18" s="3" t="s">
         <v>34</v>
@@ -4839,7 +4921,7 @@
       </c>
       <c r="E19" s="4"/>
       <c r="F19" s="3" t="s">
-        <v>799</v>
+        <v>800</v>
       </c>
       <c r="G19" s="3" t="s">
         <v>35</v>
@@ -4860,7 +4942,7 @@
       </c>
       <c r="E20" s="4"/>
       <c r="F20" s="3" t="s">
-        <v>799</v>
+        <v>800</v>
       </c>
       <c r="G20" s="3" t="s">
         <v>36</v>
@@ -4881,7 +4963,7 @@
       </c>
       <c r="E21" s="4"/>
       <c r="F21" s="3" t="s">
-        <v>799</v>
+        <v>800</v>
       </c>
       <c r="G21" s="3"/>
     </row>
@@ -4900,7 +4982,7 @@
       </c>
       <c r="E22" s="4"/>
       <c r="F22" s="3" t="s">
-        <v>799</v>
+        <v>800</v>
       </c>
       <c r="G22" s="3"/>
     </row>
@@ -4919,7 +5001,7 @@
       </c>
       <c r="E23" s="4"/>
       <c r="F23" s="3" t="s">
-        <v>795</v>
+        <v>796</v>
       </c>
       <c r="G23" s="3" t="s">
         <v>40</v>
@@ -4942,7 +5024,7 @@
         <v>450</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>796</v>
+        <v>797</v>
       </c>
       <c r="G24" s="3" t="s">
         <v>42</v>
@@ -4961,7 +5043,7 @@
       <c r="D25" s="4"/>
       <c r="E25" s="4"/>
       <c r="F25" s="3" t="s">
-        <v>796</v>
+        <v>797</v>
       </c>
       <c r="G25" s="3"/>
     </row>
@@ -4978,7 +5060,7 @@
       <c r="D26" s="4"/>
       <c r="E26" s="4"/>
       <c r="F26" s="3" t="s">
-        <v>796</v>
+        <v>797</v>
       </c>
       <c r="G26" s="3" t="s">
         <v>44</v>
@@ -5001,7 +5083,7 @@
         <v>450</v>
       </c>
       <c r="F27" s="3" t="s">
-        <v>796</v>
+        <v>797</v>
       </c>
       <c r="G27" s="3" t="s">
         <v>46</v>
@@ -5020,7 +5102,7 @@
       <c r="D28" s="4"/>
       <c r="E28" s="4"/>
       <c r="F28" s="3" t="s">
-        <v>796</v>
+        <v>797</v>
       </c>
       <c r="G28" s="3"/>
     </row>
@@ -5037,7 +5119,7 @@
       <c r="D29" s="4"/>
       <c r="E29" s="4"/>
       <c r="F29" s="3" t="s">
-        <v>796</v>
+        <v>797</v>
       </c>
       <c r="G29" s="3"/>
     </row>
@@ -5054,7 +5136,7 @@
       <c r="D30" s="4"/>
       <c r="E30" s="4"/>
       <c r="F30" s="3" t="s">
-        <v>796</v>
+        <v>797</v>
       </c>
       <c r="G30" s="3" t="s">
         <v>49</v>
@@ -5073,7 +5155,7 @@
       <c r="D31" s="4"/>
       <c r="E31" s="4"/>
       <c r="F31" s="3" t="s">
-        <v>796</v>
+        <v>797</v>
       </c>
       <c r="G31" s="3" t="s">
         <v>51</v>
@@ -5094,7 +5176,7 @@
       </c>
       <c r="E32" s="4"/>
       <c r="F32" s="3" t="s">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="G32" s="3" t="s">
         <v>52</v>
@@ -5115,7 +5197,7 @@
       </c>
       <c r="E33" s="4"/>
       <c r="F33" s="3" t="s">
-        <v>798</v>
+        <v>799</v>
       </c>
       <c r="G33" s="3" t="s">
         <v>53</v>
@@ -5136,7 +5218,7 @@
       </c>
       <c r="E34" s="4"/>
       <c r="F34" s="3" t="s">
-        <v>798</v>
+        <v>799</v>
       </c>
       <c r="G34" s="3" t="s">
         <v>54</v>
@@ -5157,7 +5239,7 @@
       </c>
       <c r="E35" s="4"/>
       <c r="F35" s="3" t="s">
-        <v>798</v>
+        <v>799</v>
       </c>
       <c r="G35" s="3" t="s">
         <v>55</v>
@@ -5178,7 +5260,7 @@
       </c>
       <c r="E36" s="4"/>
       <c r="F36" s="3" t="s">
-        <v>798</v>
+        <v>799</v>
       </c>
       <c r="G36" s="3" t="s">
         <v>55</v>
@@ -5199,7 +5281,7 @@
       </c>
       <c r="E37" s="4"/>
       <c r="F37" s="3" t="s">
-        <v>847</v>
+        <v>848</v>
       </c>
       <c r="G37" s="3" t="s">
         <v>56</v>
@@ -5220,7 +5302,7 @@
       </c>
       <c r="E38" s="4"/>
       <c r="F38" s="3" t="s">
-        <v>847</v>
+        <v>848</v>
       </c>
       <c r="G38" s="3" t="s">
         <v>57</v>
@@ -5241,7 +5323,7 @@
       </c>
       <c r="E39" s="4"/>
       <c r="F39" s="3" t="s">
-        <v>847</v>
+        <v>848</v>
       </c>
       <c r="G39" s="3" t="s">
         <v>58</v>
@@ -5262,7 +5344,7 @@
       </c>
       <c r="E40" s="4"/>
       <c r="F40" s="3" t="s">
-        <v>848</v>
+        <v>849</v>
       </c>
       <c r="G40" s="3" t="s">
         <v>59</v>
@@ -5283,7 +5365,7 @@
       </c>
       <c r="E41" s="4"/>
       <c r="F41" s="3" t="s">
-        <v>848</v>
+        <v>849</v>
       </c>
       <c r="G41" s="3" t="s">
         <v>60</v>
@@ -5304,7 +5386,7 @@
       </c>
       <c r="E42" s="4"/>
       <c r="F42" s="3" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="G42" s="3" t="s">
         <v>61</v>
@@ -5325,7 +5407,7 @@
       </c>
       <c r="E43" s="4"/>
       <c r="F43" s="3" t="s">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="G43" s="3" t="s">
         <v>62</v>
@@ -5348,7 +5430,7 @@
         <v>400</v>
       </c>
       <c r="F44" s="3" t="s">
-        <v>800</v>
+        <v>801</v>
       </c>
       <c r="G44" s="3" t="s">
         <v>64</v>
@@ -5371,7 +5453,7 @@
         <v>450</v>
       </c>
       <c r="F45" s="3" t="s">
-        <v>800</v>
+        <v>801</v>
       </c>
       <c r="G45" s="3" t="s">
         <v>66</v>
@@ -5394,7 +5476,7 @@
         <v>450</v>
       </c>
       <c r="F46" s="3" t="s">
-        <v>800</v>
+        <v>801</v>
       </c>
       <c r="G46" s="3" t="s">
         <v>66</v>
@@ -5417,7 +5499,7 @@
         <v>450</v>
       </c>
       <c r="F47" s="3" t="s">
-        <v>800</v>
+        <v>801</v>
       </c>
       <c r="G47" s="3" t="s">
         <v>66</v>
@@ -5440,7 +5522,7 @@
         <v>1400</v>
       </c>
       <c r="F48" s="3" t="s">
-        <v>800</v>
+        <v>801</v>
       </c>
       <c r="G48" s="3" t="s">
         <v>70</v>
@@ -5463,7 +5545,7 @@
         <v>2500</v>
       </c>
       <c r="F49" s="3" t="s">
-        <v>800</v>
+        <v>801</v>
       </c>
       <c r="G49" s="3" t="s">
         <v>72</v>
@@ -5486,7 +5568,7 @@
         <v>1900</v>
       </c>
       <c r="F50" s="3" t="s">
-        <v>800</v>
+        <v>801</v>
       </c>
       <c r="G50" s="3" t="s">
         <v>72</v>
@@ -5507,7 +5589,7 @@
       </c>
       <c r="E51" s="4"/>
       <c r="F51" s="3" t="s">
-        <v>851</v>
+        <v>852</v>
       </c>
       <c r="G51" s="3" t="s">
         <v>75</v>
@@ -5528,7 +5610,7 @@
       </c>
       <c r="E52" s="4"/>
       <c r="F52" s="3" t="s">
-        <v>851</v>
+        <v>852</v>
       </c>
       <c r="G52" s="3" t="s">
         <v>77</v>
@@ -5547,7 +5629,7 @@
       <c r="D53" s="4"/>
       <c r="E53" s="4"/>
       <c r="F53" s="3" t="s">
-        <v>801</v>
+        <v>802</v>
       </c>
       <c r="G53" s="3"/>
     </row>
@@ -5566,7 +5648,7 @@
       </c>
       <c r="E54" s="4"/>
       <c r="F54" s="3" t="s">
-        <v>801</v>
+        <v>802</v>
       </c>
       <c r="G54" s="3" t="s">
         <v>80</v>
@@ -5585,7 +5667,7 @@
       <c r="D55" s="4"/>
       <c r="E55" s="4"/>
       <c r="F55" s="3" t="s">
-        <v>801</v>
+        <v>802</v>
       </c>
       <c r="G55" s="3" t="s">
         <v>82</v>
@@ -5604,7 +5686,7 @@
       <c r="D56" s="4"/>
       <c r="E56" s="4"/>
       <c r="F56" s="3" t="s">
-        <v>801</v>
+        <v>802</v>
       </c>
       <c r="G56" s="3" t="s">
         <v>82</v>
@@ -5623,7 +5705,7 @@
       <c r="D57" s="4"/>
       <c r="E57" s="4"/>
       <c r="F57" s="3" t="s">
-        <v>801</v>
+        <v>802</v>
       </c>
       <c r="G57" s="3" t="s">
         <v>85</v>
@@ -5642,7 +5724,7 @@
       <c r="D58" s="4"/>
       <c r="E58" s="4"/>
       <c r="F58" s="3" t="s">
-        <v>801</v>
+        <v>802</v>
       </c>
       <c r="G58" s="3" t="s">
         <v>87</v>
@@ -5661,7 +5743,7 @@
       <c r="D59" s="4"/>
       <c r="E59" s="4"/>
       <c r="F59" s="3" t="s">
-        <v>801</v>
+        <v>802</v>
       </c>
       <c r="G59" s="3" t="s">
         <v>89</v>
@@ -5680,7 +5762,7 @@
       <c r="D60" s="4"/>
       <c r="E60" s="4"/>
       <c r="F60" s="3" t="s">
-        <v>801</v>
+        <v>802</v>
       </c>
       <c r="G60" s="3" t="s">
         <v>85</v>
@@ -5699,7 +5781,7 @@
       <c r="D61" s="4"/>
       <c r="E61" s="4"/>
       <c r="F61" s="3" t="s">
-        <v>801</v>
+        <v>802</v>
       </c>
       <c r="G61" s="3" t="s">
         <v>92</v>
@@ -5720,7 +5802,7 @@
       </c>
       <c r="E62" s="4"/>
       <c r="F62" s="3" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="G62" s="3" t="s">
         <v>94</v>
@@ -5741,7 +5823,7 @@
       </c>
       <c r="E63" s="4"/>
       <c r="F63" s="3" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="G63" s="3"/>
     </row>
@@ -5760,7 +5842,7 @@
       </c>
       <c r="E64" s="4"/>
       <c r="F64" s="3" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="G64" s="3"/>
     </row>
@@ -5779,7 +5861,7 @@
       </c>
       <c r="E65" s="4"/>
       <c r="F65" s="3" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="G65" s="3"/>
     </row>
@@ -5798,7 +5880,7 @@
       </c>
       <c r="E66" s="4"/>
       <c r="F66" s="3" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="G66" s="3"/>
     </row>
@@ -5817,7 +5899,7 @@
       </c>
       <c r="E67" s="4"/>
       <c r="F67" s="3" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="G67" s="3"/>
     </row>
@@ -5836,7 +5918,7 @@
       </c>
       <c r="E68" s="4"/>
       <c r="F68" s="3" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="G68" s="3"/>
     </row>
@@ -5855,7 +5937,7 @@
       </c>
       <c r="E69" s="4"/>
       <c r="F69" s="3" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="G69" s="3"/>
     </row>
@@ -5874,7 +5956,7 @@
       </c>
       <c r="E70" s="4"/>
       <c r="F70" s="3" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="G70" s="3"/>
     </row>
@@ -5893,7 +5975,7 @@
       </c>
       <c r="E71" s="4"/>
       <c r="F71" s="3" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="G71" s="3"/>
     </row>
@@ -5912,7 +5994,7 @@
       </c>
       <c r="E72" s="4"/>
       <c r="F72" s="3" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="G72" s="3" t="s">
         <v>105</v>
@@ -5933,7 +6015,7 @@
       </c>
       <c r="E73" s="4"/>
       <c r="F73" s="3" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="G73" s="3" t="s">
         <v>107</v>
@@ -5954,7 +6036,7 @@
       </c>
       <c r="E74" s="4"/>
       <c r="F74" s="3" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="G74" s="3" t="s">
         <v>109</v>
@@ -5973,7 +6055,7 @@
       <c r="D75" s="4"/>
       <c r="E75" s="4"/>
       <c r="F75" s="3" t="s">
-        <v>994</v>
+        <v>1114</v>
       </c>
       <c r="G75" s="3" t="s">
         <v>111</v>
@@ -5992,7 +6074,7 @@
       <c r="D76" s="4"/>
       <c r="E76" s="4"/>
       <c r="F76" s="3" t="s">
-        <v>994</v>
+        <v>1114</v>
       </c>
       <c r="G76" s="3" t="s">
         <v>112</v>
@@ -6011,7 +6093,7 @@
       <c r="D77" s="4"/>
       <c r="E77" s="4"/>
       <c r="F77" s="3" t="s">
-        <v>994</v>
+        <v>1114</v>
       </c>
       <c r="G77" s="3" t="s">
         <v>113</v>
@@ -6030,7 +6112,7 @@
       <c r="D78" s="4"/>
       <c r="E78" s="4"/>
       <c r="F78" s="3" t="s">
-        <v>994</v>
+        <v>1114</v>
       </c>
       <c r="G78" s="3" t="s">
         <v>725</v>
@@ -6051,7 +6133,7 @@
       </c>
       <c r="E79" s="4"/>
       <c r="F79" s="3" t="s">
-        <v>994</v>
+        <v>1114</v>
       </c>
       <c r="G79" s="3" t="s">
         <v>115</v>
@@ -6070,7 +6152,7 @@
       <c r="D80" s="4"/>
       <c r="E80" s="4"/>
       <c r="F80" s="3" t="s">
-        <v>994</v>
+        <v>1114</v>
       </c>
       <c r="G80" s="3" t="s">
         <v>117</v>
@@ -6089,7 +6171,7 @@
       <c r="D81" s="4"/>
       <c r="E81" s="4"/>
       <c r="F81" s="3" t="s">
-        <v>994</v>
+        <v>1114</v>
       </c>
       <c r="G81" s="3" t="s">
         <v>119</v>
@@ -6108,7 +6190,7 @@
       <c r="D82" s="4"/>
       <c r="E82" s="4"/>
       <c r="F82" s="3" t="s">
-        <v>994</v>
+        <v>1114</v>
       </c>
       <c r="G82" s="3" t="s">
         <v>119</v>
@@ -6127,7 +6209,7 @@
       <c r="D83" s="4"/>
       <c r="E83" s="4"/>
       <c r="F83" s="3" t="s">
-        <v>994</v>
+        <v>1114</v>
       </c>
       <c r="G83" s="3" t="s">
         <v>122</v>
@@ -6146,7 +6228,7 @@
       <c r="D84" s="4"/>
       <c r="E84" s="4"/>
       <c r="F84" s="3" t="s">
-        <v>994</v>
+        <v>1114</v>
       </c>
       <c r="G84" s="3" t="s">
         <v>119</v>
@@ -6165,7 +6247,7 @@
       <c r="D85" s="4"/>
       <c r="E85" s="4"/>
       <c r="F85" s="3" t="s">
-        <v>994</v>
+        <v>1114</v>
       </c>
       <c r="G85" s="3" t="s">
         <v>119</v>
@@ -6184,7 +6266,7 @@
       <c r="D86" s="4"/>
       <c r="E86" s="4"/>
       <c r="F86" s="3" t="s">
-        <v>994</v>
+        <v>1114</v>
       </c>
       <c r="G86" s="3" t="s">
         <v>726</v>
@@ -6203,7 +6285,7 @@
       <c r="D87" s="4"/>
       <c r="E87" s="4"/>
       <c r="F87" s="3" t="s">
-        <v>994</v>
+        <v>1114</v>
       </c>
       <c r="G87" s="3" t="s">
         <v>119</v>
@@ -6222,7 +6304,7 @@
       <c r="D88" s="4"/>
       <c r="E88" s="4"/>
       <c r="F88" s="3" t="s">
-        <v>994</v>
+        <v>1114</v>
       </c>
       <c r="G88" s="3" t="s">
         <v>119</v>
@@ -6241,7 +6323,7 @@
       <c r="D89" s="4"/>
       <c r="E89" s="4"/>
       <c r="F89" s="3" t="s">
-        <v>994</v>
+        <v>1114</v>
       </c>
       <c r="G89" s="3" t="s">
         <v>117</v>
@@ -6260,7 +6342,7 @@
       <c r="D90" s="4"/>
       <c r="E90" s="4"/>
       <c r="F90" s="3" t="s">
-        <v>994</v>
+        <v>1114</v>
       </c>
       <c r="G90" s="3" t="s">
         <v>130</v>
@@ -6279,7 +6361,7 @@
       <c r="D91" s="4"/>
       <c r="E91" s="4"/>
       <c r="F91" s="3" t="s">
-        <v>994</v>
+        <v>1114</v>
       </c>
       <c r="G91" s="3" t="s">
         <v>117</v>
@@ -6300,7 +6382,7 @@
       </c>
       <c r="E92" s="4"/>
       <c r="F92" s="3" t="s">
-        <v>852</v>
+        <v>853</v>
       </c>
       <c r="G92" s="3"/>
     </row>
@@ -6319,7 +6401,7 @@
       </c>
       <c r="E93" s="4"/>
       <c r="F93" s="3" t="s">
-        <v>852</v>
+        <v>853</v>
       </c>
       <c r="G93" s="3"/>
     </row>
@@ -6338,7 +6420,7 @@
       </c>
       <c r="E94" s="4"/>
       <c r="F94" s="3" t="s">
-        <v>853</v>
+        <v>854</v>
       </c>
       <c r="G94" s="3"/>
     </row>
@@ -6357,7 +6439,7 @@
       </c>
       <c r="E95" s="4"/>
       <c r="F95" s="3" t="s">
-        <v>853</v>
+        <v>854</v>
       </c>
       <c r="G95" s="3"/>
     </row>
@@ -6376,7 +6458,7 @@
       </c>
       <c r="E96" s="4"/>
       <c r="F96" s="3" t="s">
-        <v>853</v>
+        <v>854</v>
       </c>
       <c r="G96" s="3"/>
     </row>
@@ -6395,7 +6477,7 @@
       </c>
       <c r="E97" s="4"/>
       <c r="F97" s="3" t="s">
-        <v>853</v>
+        <v>854</v>
       </c>
       <c r="G97" s="3"/>
     </row>
@@ -6414,7 +6496,7 @@
       </c>
       <c r="E98" s="4"/>
       <c r="F98" s="3" t="s">
-        <v>853</v>
+        <v>854</v>
       </c>
       <c r="G98" s="3"/>
     </row>
@@ -6433,7 +6515,7 @@
       </c>
       <c r="E99" s="4"/>
       <c r="F99" s="3" t="s">
-        <v>853</v>
+        <v>854</v>
       </c>
       <c r="G99" s="3"/>
     </row>
@@ -6452,7 +6534,7 @@
       </c>
       <c r="E100" s="4"/>
       <c r="F100" s="3" t="s">
-        <v>853</v>
+        <v>854</v>
       </c>
       <c r="G100" s="3"/>
     </row>
@@ -6471,7 +6553,7 @@
       </c>
       <c r="E101" s="4"/>
       <c r="F101" s="3" t="s">
-        <v>853</v>
+        <v>854</v>
       </c>
       <c r="G101" s="3"/>
     </row>
@@ -6490,7 +6572,7 @@
       </c>
       <c r="E102" s="4"/>
       <c r="F102" s="3" t="s">
-        <v>853</v>
+        <v>854</v>
       </c>
       <c r="G102" s="3"/>
     </row>
@@ -6509,7 +6591,7 @@
       </c>
       <c r="E103" s="4"/>
       <c r="F103" s="3" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="G103" s="3" t="s">
         <v>142</v>
@@ -6530,7 +6612,7 @@
       </c>
       <c r="E104" s="4"/>
       <c r="F104" s="3" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="G104" s="3" t="s">
         <v>144</v>
@@ -6551,7 +6633,7 @@
       </c>
       <c r="E105" s="4"/>
       <c r="F105" s="3" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="G105" s="3" t="s">
         <v>144</v>
@@ -6572,7 +6654,7 @@
       </c>
       <c r="E106" s="4"/>
       <c r="F106" s="3" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="G106" s="3" t="s">
         <v>144</v>
@@ -6593,7 +6675,7 @@
       </c>
       <c r="E107" s="4"/>
       <c r="F107" s="3" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="G107" s="3" t="s">
         <v>144</v>
@@ -6614,7 +6696,7 @@
       </c>
       <c r="E108" s="4"/>
       <c r="F108" s="3" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="G108" s="3" t="s">
         <v>144</v>
@@ -6635,7 +6717,7 @@
       </c>
       <c r="E109" s="4"/>
       <c r="F109" s="3" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="G109" s="3" t="s">
         <v>144</v>
@@ -6656,7 +6738,7 @@
       </c>
       <c r="E110" s="4"/>
       <c r="F110" s="3" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="G110" s="3" t="s">
         <v>144</v>
@@ -6677,7 +6759,7 @@
       </c>
       <c r="E111" s="4"/>
       <c r="F111" s="3" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="G111" s="3" t="s">
         <v>144</v>
@@ -6698,7 +6780,7 @@
       </c>
       <c r="E112" s="4"/>
       <c r="F112" s="3" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="G112" s="3" t="s">
         <v>144</v>
@@ -6719,7 +6801,7 @@
       </c>
       <c r="E113" s="4"/>
       <c r="F113" s="3" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="G113" s="3" t="s">
         <v>144</v>
@@ -6740,7 +6822,7 @@
       </c>
       <c r="E114" s="4"/>
       <c r="F114" s="3" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="G114" s="3" t="s">
         <v>144</v>
@@ -6761,7 +6843,7 @@
       </c>
       <c r="E115" s="4"/>
       <c r="F115" s="3" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="G115" s="3"/>
     </row>
@@ -6780,7 +6862,7 @@
       </c>
       <c r="E116" s="4"/>
       <c r="F116" s="3" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="G116" s="3"/>
     </row>
@@ -6799,7 +6881,7 @@
       </c>
       <c r="E117" s="4"/>
       <c r="F117" s="3" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="G117" s="3"/>
     </row>
@@ -6818,7 +6900,7 @@
       </c>
       <c r="E118" s="4"/>
       <c r="F118" s="3" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="G118" s="3"/>
     </row>
@@ -6837,7 +6919,7 @@
       </c>
       <c r="E119" s="4"/>
       <c r="F119" s="3" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="G119" s="3"/>
     </row>
@@ -6856,7 +6938,7 @@
       </c>
       <c r="E120" s="4"/>
       <c r="F120" s="3" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="G120" s="3"/>
     </row>
@@ -6873,7 +6955,7 @@
       <c r="D121" s="4"/>
       <c r="E121" s="4"/>
       <c r="F121" s="3" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="G121" s="3" t="s">
         <v>134</v>
@@ -6892,7 +6974,7 @@
       <c r="D122" s="4"/>
       <c r="E122" s="4"/>
       <c r="F122" s="3" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="G122" s="3" t="s">
         <v>134</v>
@@ -6911,7 +6993,7 @@
       <c r="D123" s="4"/>
       <c r="E123" s="4"/>
       <c r="F123" s="3" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="G123" s="3" t="s">
         <v>138</v>
@@ -6930,7 +7012,7 @@
       <c r="D124" s="4"/>
       <c r="E124" s="4"/>
       <c r="F124" s="3" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="G124" s="3" t="s">
         <v>140</v>
@@ -6951,7 +7033,7 @@
       </c>
       <c r="E125" s="4"/>
       <c r="F125" s="3" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
       <c r="G125" s="3" t="s">
         <v>161</v>
@@ -6972,7 +7054,7 @@
       </c>
       <c r="E126" s="4"/>
       <c r="F126" s="3" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
       <c r="G126" s="3"/>
     </row>
@@ -6991,7 +7073,7 @@
       </c>
       <c r="E127" s="4"/>
       <c r="F127" s="3" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
       <c r="G127" s="3"/>
     </row>
@@ -7010,7 +7092,7 @@
       </c>
       <c r="E128" s="4"/>
       <c r="F128" s="3" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
       <c r="G128" s="3" t="s">
         <v>165</v>
@@ -7031,7 +7113,7 @@
       </c>
       <c r="E129" s="4"/>
       <c r="F129" s="3" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
       <c r="G129" s="3"/>
     </row>
@@ -7050,7 +7132,7 @@
       </c>
       <c r="E130" s="4"/>
       <c r="F130" s="3" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
       <c r="G130" s="3"/>
     </row>
@@ -7069,7 +7151,7 @@
       </c>
       <c r="E131" s="4"/>
       <c r="F131" s="3" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
       <c r="G131" s="3"/>
     </row>
@@ -7088,7 +7170,7 @@
       </c>
       <c r="E132" s="4"/>
       <c r="F132" s="3" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
       <c r="G132" s="3"/>
     </row>
@@ -7107,7 +7189,7 @@
       </c>
       <c r="E133" s="4"/>
       <c r="F133" s="3" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
       <c r="G133" s="3"/>
     </row>
@@ -7126,7 +7208,7 @@
       </c>
       <c r="E134" s="4"/>
       <c r="F134" s="3" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
       <c r="G134" s="3"/>
     </row>
@@ -7145,7 +7227,7 @@
       </c>
       <c r="E135" s="4"/>
       <c r="F135" s="3" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
       <c r="G135" s="3"/>
     </row>
@@ -7164,7 +7246,7 @@
       </c>
       <c r="E136" s="4"/>
       <c r="F136" s="3" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
       <c r="G136" s="3"/>
     </row>
@@ -7183,7 +7265,7 @@
       </c>
       <c r="E137" s="4"/>
       <c r="F137" s="3" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
       <c r="G137" s="3"/>
     </row>
@@ -7202,7 +7284,7 @@
       </c>
       <c r="E138" s="4"/>
       <c r="F138" s="3" t="s">
-        <v>805</v>
+        <v>806</v>
       </c>
       <c r="G138" s="3" t="s">
         <v>171</v>
@@ -7223,7 +7305,7 @@
       </c>
       <c r="E139" s="4"/>
       <c r="F139" s="3" t="s">
-        <v>805</v>
+        <v>806</v>
       </c>
       <c r="G139" s="3" t="s">
         <v>172</v>
@@ -7244,7 +7326,7 @@
       </c>
       <c r="E140" s="4"/>
       <c r="F140" s="3" t="s">
-        <v>806</v>
+        <v>807</v>
       </c>
       <c r="G140" s="3" t="s">
         <v>743</v>
@@ -7265,7 +7347,7 @@
       </c>
       <c r="E141" s="4"/>
       <c r="F141" s="3" t="s">
-        <v>806</v>
+        <v>807</v>
       </c>
       <c r="G141" s="3"/>
     </row>
@@ -7284,7 +7366,7 @@
       </c>
       <c r="E142" s="4"/>
       <c r="F142" s="3" t="s">
-        <v>806</v>
+        <v>807</v>
       </c>
       <c r="G142" s="3"/>
     </row>
@@ -7303,7 +7385,7 @@
       </c>
       <c r="E143" s="4"/>
       <c r="F143" s="3" t="s">
-        <v>806</v>
+        <v>807</v>
       </c>
       <c r="G143" s="3"/>
     </row>
@@ -7320,7 +7402,7 @@
       <c r="D144" s="4"/>
       <c r="E144" s="4"/>
       <c r="F144" s="3" t="s">
-        <v>806</v>
+        <v>807</v>
       </c>
       <c r="G144" s="3" t="s">
         <v>179</v>
@@ -7339,7 +7421,7 @@
       <c r="D145" s="4"/>
       <c r="E145" s="4"/>
       <c r="F145" s="3" t="s">
-        <v>806</v>
+        <v>807</v>
       </c>
       <c r="G145" s="3"/>
     </row>
@@ -7356,7 +7438,7 @@
       <c r="D146" s="4"/>
       <c r="E146" s="4"/>
       <c r="F146" s="3" t="s">
-        <v>806</v>
+        <v>807</v>
       </c>
       <c r="G146" s="3"/>
     </row>
@@ -7373,7 +7455,7 @@
       <c r="D147" s="4"/>
       <c r="E147" s="4"/>
       <c r="F147" s="3" t="s">
-        <v>806</v>
+        <v>807</v>
       </c>
       <c r="G147" s="3"/>
     </row>
@@ -7392,7 +7474,7 @@
       </c>
       <c r="E148" s="4"/>
       <c r="F148" s="3" t="s">
-        <v>807</v>
+        <v>808</v>
       </c>
       <c r="G148" s="3" t="s">
         <v>185</v>
@@ -7413,7 +7495,7 @@
       </c>
       <c r="E149" s="4"/>
       <c r="F149" s="3" t="s">
-        <v>807</v>
+        <v>808</v>
       </c>
       <c r="G149" s="3" t="s">
         <v>744</v>
@@ -7434,7 +7516,7 @@
       </c>
       <c r="E150" s="4"/>
       <c r="F150" s="3" t="s">
-        <v>808</v>
+        <v>809</v>
       </c>
       <c r="G150" s="3" t="s">
         <v>187</v>
@@ -7455,7 +7537,7 @@
       </c>
       <c r="E151" s="4"/>
       <c r="F151" s="3" t="s">
-        <v>854</v>
+        <v>1092</v>
       </c>
       <c r="G151" s="3" t="s">
         <v>189</v>
@@ -7476,7 +7558,7 @@
       </c>
       <c r="E152" s="4"/>
       <c r="F152" s="3" t="s">
-        <v>854</v>
+        <v>1092</v>
       </c>
       <c r="G152" s="3" t="s">
         <v>191</v>
@@ -7497,7 +7579,7 @@
       </c>
       <c r="E153" s="4"/>
       <c r="F153" s="3" t="s">
-        <v>854</v>
+        <v>1092</v>
       </c>
       <c r="G153" s="3" t="s">
         <v>193</v>
@@ -7518,7 +7600,7 @@
       </c>
       <c r="E154" s="4"/>
       <c r="F154" s="3" t="s">
-        <v>854</v>
+        <v>1092</v>
       </c>
       <c r="G154" s="3" t="s">
         <v>195</v>
@@ -7539,7 +7621,7 @@
       </c>
       <c r="E155" s="4"/>
       <c r="F155" s="3" t="s">
-        <v>854</v>
+        <v>1092</v>
       </c>
       <c r="G155" s="3" t="s">
         <v>197</v>
@@ -7560,7 +7642,7 @@
       </c>
       <c r="E156" s="4"/>
       <c r="F156" s="3" t="s">
-        <v>854</v>
+        <v>1092</v>
       </c>
       <c r="G156" s="3" t="s">
         <v>199</v>
@@ -7579,7 +7661,7 @@
       <c r="D157" s="4"/>
       <c r="E157" s="4"/>
       <c r="F157" s="3" t="s">
-        <v>854</v>
+        <v>1092</v>
       </c>
       <c r="G157" s="3" t="s">
         <v>201</v>
@@ -7598,7 +7680,7 @@
       <c r="D158" s="4"/>
       <c r="E158" s="4"/>
       <c r="F158" s="3" t="s">
-        <v>854</v>
+        <v>1092</v>
       </c>
       <c r="G158" s="3" t="s">
         <v>203</v>
@@ -7617,7 +7699,7 @@
       <c r="D159" s="4"/>
       <c r="E159" s="4"/>
       <c r="F159" s="3" t="s">
-        <v>854</v>
+        <v>1092</v>
       </c>
       <c r="G159" s="3"/>
     </row>
@@ -7634,7 +7716,7 @@
       <c r="D160" s="4"/>
       <c r="E160" s="4"/>
       <c r="F160" s="3" t="s">
-        <v>854</v>
+        <v>1092</v>
       </c>
       <c r="G160" s="3"/>
     </row>
@@ -7651,7 +7733,7 @@
       <c r="D161" s="4"/>
       <c r="E161" s="4"/>
       <c r="F161" s="3" t="s">
-        <v>854</v>
+        <v>1092</v>
       </c>
       <c r="G161" s="3"/>
     </row>
@@ -7668,7 +7750,7 @@
       <c r="D162" s="4"/>
       <c r="E162" s="4"/>
       <c r="F162" s="3" t="s">
-        <v>854</v>
+        <v>1092</v>
       </c>
       <c r="G162" s="3"/>
     </row>
@@ -7685,7 +7767,7 @@
       <c r="D163" s="4"/>
       <c r="E163" s="4"/>
       <c r="F163" s="3" t="s">
-        <v>854</v>
+        <v>1092</v>
       </c>
       <c r="G163" s="3" t="s">
         <v>209</v>
@@ -7704,7 +7786,7 @@
       <c r="D164" s="4"/>
       <c r="E164" s="4"/>
       <c r="F164" s="3" t="s">
-        <v>809</v>
+        <v>810</v>
       </c>
       <c r="G164" s="3" t="s">
         <v>211</v>
@@ -7723,7 +7805,7 @@
       <c r="D165" s="4"/>
       <c r="E165" s="4"/>
       <c r="F165" s="3" t="s">
-        <v>809</v>
+        <v>810</v>
       </c>
       <c r="G165" s="3"/>
     </row>
@@ -7740,7 +7822,7 @@
       <c r="D166" s="4"/>
       <c r="E166" s="4"/>
       <c r="F166" s="3" t="s">
-        <v>809</v>
+        <v>810</v>
       </c>
       <c r="G166" s="3"/>
     </row>
@@ -7757,7 +7839,7 @@
       <c r="D167" s="4"/>
       <c r="E167" s="4"/>
       <c r="F167" s="3" t="s">
-        <v>809</v>
+        <v>810</v>
       </c>
       <c r="G167" s="3" t="s">
         <v>215</v>
@@ -7776,7 +7858,7 @@
       <c r="D168" s="4"/>
       <c r="E168" s="4"/>
       <c r="F168" s="3" t="s">
-        <v>809</v>
+        <v>810</v>
       </c>
       <c r="G168" s="3" t="s">
         <v>217</v>
@@ -7795,7 +7877,7 @@
       <c r="D169" s="4"/>
       <c r="E169" s="4"/>
       <c r="F169" s="3" t="s">
-        <v>809</v>
+        <v>810</v>
       </c>
       <c r="G169" s="3" t="s">
         <v>219</v>
@@ -7814,7 +7896,7 @@
       <c r="D170" s="4"/>
       <c r="E170" s="4"/>
       <c r="F170" s="3" t="s">
-        <v>809</v>
+        <v>810</v>
       </c>
       <c r="G170" s="3"/>
     </row>
@@ -7831,7 +7913,7 @@
       <c r="D171" s="4"/>
       <c r="E171" s="4"/>
       <c r="F171" s="3" t="s">
-        <v>809</v>
+        <v>810</v>
       </c>
       <c r="G171" s="3"/>
     </row>
@@ -7848,7 +7930,7 @@
       <c r="D172" s="4"/>
       <c r="E172" s="4"/>
       <c r="F172" s="3" t="s">
-        <v>809</v>
+        <v>810</v>
       </c>
       <c r="G172" s="3" t="s">
         <v>215</v>
@@ -7867,7 +7949,7 @@
       <c r="D173" s="4"/>
       <c r="E173" s="4"/>
       <c r="F173" s="3" t="s">
-        <v>809</v>
+        <v>810</v>
       </c>
       <c r="G173" s="3" t="s">
         <v>217</v>
@@ -7886,7 +7968,7 @@
       <c r="D174" s="4"/>
       <c r="E174" s="4"/>
       <c r="F174" s="3" t="s">
-        <v>810</v>
+        <v>811</v>
       </c>
       <c r="G174" s="3" t="s">
         <v>225</v>
@@ -7905,7 +7987,7 @@
       <c r="D175" s="4"/>
       <c r="E175" s="4"/>
       <c r="F175" s="3" t="s">
-        <v>810</v>
+        <v>811</v>
       </c>
       <c r="G175" s="3"/>
     </row>
@@ -7922,7 +8004,7 @@
       <c r="D176" s="4"/>
       <c r="E176" s="4"/>
       <c r="F176" s="3" t="s">
-        <v>810</v>
+        <v>811</v>
       </c>
       <c r="G176" s="3"/>
     </row>
@@ -7943,7 +8025,7 @@
         <v>890</v>
       </c>
       <c r="F177" s="3" t="s">
-        <v>811</v>
+        <v>812</v>
       </c>
       <c r="G177" s="3" t="s">
         <v>745</v>
@@ -7964,7 +8046,7 @@
       </c>
       <c r="E178" s="4"/>
       <c r="F178" s="3" t="s">
-        <v>811</v>
+        <v>812</v>
       </c>
       <c r="G178" s="3"/>
     </row>
@@ -7983,7 +8065,7 @@
       </c>
       <c r="E179" s="4"/>
       <c r="F179" s="3" t="s">
-        <v>811</v>
+        <v>812</v>
       </c>
       <c r="G179" s="3"/>
     </row>
@@ -8002,7 +8084,7 @@
       </c>
       <c r="E180" s="4"/>
       <c r="F180" s="3" t="s">
-        <v>811</v>
+        <v>812</v>
       </c>
       <c r="G180" s="3" t="s">
         <v>232</v>
@@ -8023,7 +8105,7 @@
       </c>
       <c r="E181" s="4"/>
       <c r="F181" s="3" t="s">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="G181" s="3" t="s">
         <v>234</v>
@@ -8044,7 +8126,7 @@
       </c>
       <c r="E182" s="4"/>
       <c r="F182" s="3" t="s">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="G182" s="3"/>
     </row>
@@ -8063,7 +8145,7 @@
       </c>
       <c r="E183" s="4"/>
       <c r="F183" s="3" t="s">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="G183" s="3"/>
     </row>
@@ -8080,7 +8162,7 @@
       <c r="D184" s="4"/>
       <c r="E184" s="4"/>
       <c r="F184" s="3" t="s">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="G184" s="3" t="s">
         <v>238</v>
@@ -8101,7 +8183,7 @@
       </c>
       <c r="E185" s="4"/>
       <c r="F185" s="3" t="s">
-        <v>813</v>
+        <v>814</v>
       </c>
       <c r="G185" s="3" t="s">
         <v>240</v>
@@ -8120,7 +8202,7 @@
       <c r="D186" s="4"/>
       <c r="E186" s="4"/>
       <c r="F186" s="3" t="s">
-        <v>814</v>
+        <v>815</v>
       </c>
       <c r="G186" s="3" t="s">
         <v>242</v>
@@ -8139,7 +8221,7 @@
       <c r="D187" s="4"/>
       <c r="E187" s="4"/>
       <c r="F187" s="3" t="s">
-        <v>814</v>
+        <v>815</v>
       </c>
       <c r="G187" s="3" t="s">
         <v>244</v>
@@ -8158,7 +8240,7 @@
       <c r="D188" s="4"/>
       <c r="E188" s="4"/>
       <c r="F188" s="3" t="s">
-        <v>814</v>
+        <v>815</v>
       </c>
       <c r="G188" s="3" t="s">
         <v>246</v>
@@ -8177,7 +8259,7 @@
       <c r="D189" s="4"/>
       <c r="E189" s="4"/>
       <c r="F189" s="3" t="s">
-        <v>814</v>
+        <v>815</v>
       </c>
       <c r="G189" s="3" t="s">
         <v>248</v>
@@ -8196,7 +8278,7 @@
       <c r="D190" s="4"/>
       <c r="E190" s="4"/>
       <c r="F190" s="3" t="s">
-        <v>814</v>
+        <v>815</v>
       </c>
       <c r="G190" s="3" t="s">
         <v>250</v>
@@ -8215,7 +8297,7 @@
       <c r="D191" s="4"/>
       <c r="E191" s="4"/>
       <c r="F191" s="3" t="s">
-        <v>814</v>
+        <v>815</v>
       </c>
       <c r="G191" s="3" t="s">
         <v>252</v>
@@ -8236,7 +8318,7 @@
       </c>
       <c r="E192" s="4"/>
       <c r="F192" s="3" t="s">
-        <v>815</v>
+        <v>816</v>
       </c>
       <c r="G192" s="3" t="s">
         <v>254</v>
@@ -8255,7 +8337,7 @@
       <c r="D193" s="4"/>
       <c r="E193" s="4"/>
       <c r="F193" s="3" t="s">
-        <v>815</v>
+        <v>816</v>
       </c>
       <c r="G193" s="3" t="s">
         <v>256</v>
@@ -8274,7 +8356,7 @@
       <c r="D194" s="4"/>
       <c r="E194" s="4"/>
       <c r="F194" s="3" t="s">
-        <v>815</v>
+        <v>816</v>
       </c>
       <c r="G194" s="3"/>
     </row>
@@ -8293,7 +8375,7 @@
       </c>
       <c r="E195" s="4"/>
       <c r="F195" s="3" t="s">
-        <v>816</v>
+        <v>817</v>
       </c>
       <c r="G195" s="3" t="s">
         <v>746</v>
@@ -8314,7 +8396,7 @@
       </c>
       <c r="E196" s="4"/>
       <c r="F196" s="3" t="s">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="G196" s="3" t="s">
         <v>260</v>
@@ -8335,7 +8417,7 @@
       </c>
       <c r="E197" s="4"/>
       <c r="F197" s="3" t="s">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="G197" s="3" t="s">
         <v>262</v>
@@ -8356,7 +8438,7 @@
       </c>
       <c r="E198" s="4"/>
       <c r="F198" s="3" t="s">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="G198" s="3"/>
     </row>
@@ -8375,7 +8457,7 @@
       </c>
       <c r="E199" s="4"/>
       <c r="F199" s="3" t="s">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="G199" s="3"/>
     </row>
@@ -8394,7 +8476,7 @@
       </c>
       <c r="E200" s="4"/>
       <c r="F200" s="3" t="s">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="G200" s="3" t="s">
         <v>266</v>
@@ -8413,7 +8495,7 @@
       <c r="D201" s="4"/>
       <c r="E201" s="4"/>
       <c r="F201" s="3" t="s">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="G201" s="3"/>
     </row>
@@ -8430,7 +8512,7 @@
       <c r="D202" s="4"/>
       <c r="E202" s="4"/>
       <c r="F202" s="3" t="s">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="G202" s="3"/>
     </row>
@@ -8447,7 +8529,7 @@
       <c r="D203" s="4"/>
       <c r="E203" s="4"/>
       <c r="F203" s="3" t="s">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="G203" s="3"/>
     </row>
@@ -8464,7 +8546,7 @@
       <c r="D204" s="4"/>
       <c r="E204" s="4"/>
       <c r="F204" s="3" t="s">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="G204" s="3"/>
     </row>
@@ -8481,7 +8563,7 @@
       <c r="D205" s="4"/>
       <c r="E205" s="4"/>
       <c r="F205" s="3" t="s">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="G205" s="3" t="s">
         <v>272</v>
@@ -8500,7 +8582,7 @@
       <c r="D206" s="4"/>
       <c r="E206" s="4"/>
       <c r="F206" s="3" t="s">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="G206" s="3"/>
     </row>
@@ -8517,7 +8599,7 @@
       <c r="D207" s="4"/>
       <c r="E207" s="4"/>
       <c r="F207" s="3" t="s">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="G207" s="3"/>
     </row>
@@ -8534,7 +8616,7 @@
       <c r="D208" s="4"/>
       <c r="E208" s="4"/>
       <c r="F208" s="3" t="s">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="G208" s="3"/>
     </row>
@@ -8551,7 +8633,7 @@
       <c r="D209" s="4"/>
       <c r="E209" s="4"/>
       <c r="F209" s="3" t="s">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="G209" s="3"/>
     </row>
@@ -8568,7 +8650,7 @@
       <c r="D210" s="4"/>
       <c r="E210" s="4"/>
       <c r="F210" s="3" t="s">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="G210" s="3"/>
     </row>
@@ -8585,7 +8667,7 @@
       <c r="D211" s="4"/>
       <c r="E211" s="4"/>
       <c r="F211" s="3" t="s">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="G211" s="3"/>
     </row>
@@ -8602,7 +8684,7 @@
       <c r="D212" s="4"/>
       <c r="E212" s="4"/>
       <c r="F212" s="3" t="s">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="G212" s="3"/>
     </row>
@@ -8619,7 +8701,7 @@
       <c r="D213" s="4"/>
       <c r="E213" s="4"/>
       <c r="F213" s="3" t="s">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="G213" s="3"/>
     </row>
@@ -8636,7 +8718,7 @@
       <c r="D214" s="4"/>
       <c r="E214" s="4"/>
       <c r="F214" s="3" t="s">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="G214" s="3" t="s">
         <v>282</v>
@@ -8655,7 +8737,7 @@
       <c r="D215" s="4"/>
       <c r="E215" s="4"/>
       <c r="F215" s="3" t="s">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="G215" s="3" t="s">
         <v>284</v>
@@ -8674,7 +8756,7 @@
       <c r="D216" s="4"/>
       <c r="E216" s="4"/>
       <c r="F216" s="3" t="s">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="G216" s="3" t="s">
         <v>286</v>
@@ -8695,7 +8777,7 @@
       </c>
       <c r="E217" s="4"/>
       <c r="F217" s="3" t="s">
-        <v>818</v>
+        <v>819</v>
       </c>
       <c r="G217" s="3" t="s">
         <v>288</v>
@@ -8716,7 +8798,7 @@
       </c>
       <c r="E218" s="4"/>
       <c r="F218" s="3" t="s">
-        <v>818</v>
+        <v>819</v>
       </c>
       <c r="G218" s="3" t="s">
         <v>290</v>
@@ -8737,7 +8819,7 @@
       </c>
       <c r="E219" s="4"/>
       <c r="F219" s="3" t="s">
-        <v>818</v>
+        <v>819</v>
       </c>
       <c r="G219" s="3" t="s">
         <v>292</v>
@@ -8758,7 +8840,7 @@
       </c>
       <c r="E220" s="4"/>
       <c r="F220" s="3" t="s">
-        <v>818</v>
+        <v>819</v>
       </c>
       <c r="G220" s="3" t="s">
         <v>292</v>
@@ -8777,7 +8859,7 @@
       <c r="D221" s="4"/>
       <c r="E221" s="4"/>
       <c r="F221" s="3" t="s">
-        <v>818</v>
+        <v>819</v>
       </c>
       <c r="G221" s="3" t="s">
         <v>295</v>
@@ -8796,7 +8878,7 @@
       </c>
       <c r="E222" s="4"/>
       <c r="F222" s="3" t="s">
-        <v>819</v>
+        <v>820</v>
       </c>
       <c r="G222" s="3"/>
     </row>
@@ -8813,7 +8895,7 @@
       <c r="D223" s="4"/>
       <c r="E223" s="4"/>
       <c r="F223" s="3" t="s">
-        <v>819</v>
+        <v>820</v>
       </c>
       <c r="G223" s="3"/>
     </row>
@@ -8830,7 +8912,7 @@
       <c r="D224" s="4"/>
       <c r="E224" s="4"/>
       <c r="F224" s="3" t="s">
-        <v>819</v>
+        <v>820</v>
       </c>
       <c r="G224" s="3"/>
     </row>
@@ -8847,7 +8929,7 @@
       <c r="D225" s="4"/>
       <c r="E225" s="4"/>
       <c r="F225" s="3" t="s">
-        <v>819</v>
+        <v>820</v>
       </c>
       <c r="G225" s="3"/>
     </row>
@@ -8864,7 +8946,7 @@
       <c r="D226" s="4"/>
       <c r="E226" s="4"/>
       <c r="F226" s="3" t="s">
-        <v>819</v>
+        <v>820</v>
       </c>
       <c r="G226" s="3"/>
     </row>
@@ -8881,7 +8963,7 @@
       <c r="D227" s="4"/>
       <c r="E227" s="4"/>
       <c r="F227" s="3" t="s">
-        <v>819</v>
+        <v>820</v>
       </c>
       <c r="G227" s="3"/>
     </row>
@@ -8898,7 +8980,7 @@
       <c r="D228" s="4"/>
       <c r="E228" s="4"/>
       <c r="F228" s="3" t="s">
-        <v>819</v>
+        <v>820</v>
       </c>
       <c r="G228" s="3"/>
     </row>
@@ -8915,7 +8997,7 @@
       <c r="D229" s="4"/>
       <c r="E229" s="4"/>
       <c r="F229" s="3" t="s">
-        <v>820</v>
+        <v>821</v>
       </c>
       <c r="G229" s="3" t="s">
         <v>304</v>
@@ -8934,7 +9016,7 @@
       <c r="D230" s="4"/>
       <c r="E230" s="4"/>
       <c r="F230" s="3" t="s">
-        <v>820</v>
+        <v>821</v>
       </c>
       <c r="G230" s="3"/>
     </row>
@@ -8951,7 +9033,7 @@
       <c r="D231" s="4"/>
       <c r="E231" s="4"/>
       <c r="F231" s="3" t="s">
-        <v>820</v>
+        <v>821</v>
       </c>
       <c r="G231" s="3"/>
     </row>
@@ -8968,7 +9050,7 @@
       <c r="D232" s="4"/>
       <c r="E232" s="4"/>
       <c r="F232" s="3" t="s">
-        <v>820</v>
+        <v>821</v>
       </c>
       <c r="G232" s="3"/>
     </row>
@@ -8985,7 +9067,7 @@
       <c r="D233" s="4"/>
       <c r="E233" s="4"/>
       <c r="F233" s="3" t="s">
-        <v>820</v>
+        <v>821</v>
       </c>
       <c r="G233" s="3"/>
     </row>
@@ -9002,7 +9084,7 @@
       <c r="D234" s="4"/>
       <c r="E234" s="4"/>
       <c r="F234" s="3" t="s">
-        <v>820</v>
+        <v>821</v>
       </c>
       <c r="G234" s="3"/>
     </row>
@@ -9019,7 +9101,7 @@
       <c r="D235" s="4"/>
       <c r="E235" s="4"/>
       <c r="F235" s="3" t="s">
-        <v>820</v>
+        <v>821</v>
       </c>
       <c r="G235" s="3"/>
     </row>
@@ -9036,7 +9118,7 @@
       <c r="D236" s="4"/>
       <c r="E236" s="4"/>
       <c r="F236" s="3" t="s">
-        <v>820</v>
+        <v>821</v>
       </c>
       <c r="G236" s="3"/>
     </row>
@@ -9053,7 +9135,7 @@
       <c r="D237" s="4"/>
       <c r="E237" s="4"/>
       <c r="F237" s="3" t="s">
-        <v>820</v>
+        <v>821</v>
       </c>
       <c r="G237" s="3"/>
     </row>
@@ -9070,7 +9152,7 @@
       <c r="D238" s="4"/>
       <c r="E238" s="4"/>
       <c r="F238" s="3" t="s">
-        <v>820</v>
+        <v>821</v>
       </c>
       <c r="G238" s="3"/>
     </row>
@@ -9089,7 +9171,7 @@
       </c>
       <c r="E239" s="4"/>
       <c r="F239" s="3" t="s">
-        <v>821</v>
+        <v>822</v>
       </c>
       <c r="G239" s="3" t="s">
         <v>314</v>
@@ -9110,7 +9192,7 @@
       </c>
       <c r="E240" s="4"/>
       <c r="F240" s="3" t="s">
-        <v>822</v>
+        <v>823</v>
       </c>
       <c r="G240" s="3" t="s">
         <v>316</v>
@@ -9131,7 +9213,7 @@
       </c>
       <c r="E241" s="4"/>
       <c r="F241" s="3" t="s">
-        <v>822</v>
+        <v>823</v>
       </c>
       <c r="G241" s="3" t="s">
         <v>318</v>
@@ -9152,7 +9234,7 @@
       </c>
       <c r="E242" s="4"/>
       <c r="F242" s="3" t="s">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="G242" s="3" t="s">
         <v>320</v>
@@ -9171,7 +9253,7 @@
       <c r="D243" s="4"/>
       <c r="E243" s="4"/>
       <c r="F243" s="3" t="s">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="G243" s="3"/>
     </row>
@@ -9188,7 +9270,7 @@
       <c r="D244" s="4"/>
       <c r="E244" s="4"/>
       <c r="F244" s="3" t="s">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="G244" s="3"/>
     </row>
@@ -9205,7 +9287,7 @@
       <c r="D245" s="4"/>
       <c r="E245" s="4"/>
       <c r="F245" s="3" t="s">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="G245" s="3"/>
     </row>
@@ -9222,7 +9304,7 @@
       <c r="D246" s="4"/>
       <c r="E246" s="4"/>
       <c r="F246" s="3" t="s">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="G246" s="3"/>
     </row>
@@ -9239,7 +9321,7 @@
       <c r="D247" s="4"/>
       <c r="E247" s="4"/>
       <c r="F247" s="3" t="s">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="G247" s="3"/>
     </row>
@@ -9256,7 +9338,7 @@
       <c r="D248" s="4"/>
       <c r="E248" s="4"/>
       <c r="F248" s="3" t="s">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="G248" s="3"/>
     </row>
@@ -9275,7 +9357,7 @@
       </c>
       <c r="E249" s="4"/>
       <c r="F249" s="3" t="s">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="G249" s="3"/>
     </row>
@@ -9294,7 +9376,7 @@
       </c>
       <c r="E250" s="4"/>
       <c r="F250" s="3" t="s">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="G250" s="3"/>
     </row>
@@ -9313,7 +9395,7 @@
       </c>
       <c r="E251" s="4"/>
       <c r="F251" s="3" t="s">
-        <v>824</v>
+        <v>825</v>
       </c>
       <c r="G251" s="3"/>
     </row>
@@ -9330,7 +9412,7 @@
       <c r="D252" s="4"/>
       <c r="E252" s="4"/>
       <c r="F252" s="3" t="s">
-        <v>825</v>
+        <v>826</v>
       </c>
       <c r="G252" s="3" t="s">
         <v>331</v>
@@ -9349,7 +9431,7 @@
       <c r="D253" s="4"/>
       <c r="E253" s="4"/>
       <c r="F253" s="3" t="s">
-        <v>825</v>
+        <v>826</v>
       </c>
       <c r="G253" s="3"/>
     </row>
@@ -9366,7 +9448,7 @@
       <c r="D254" s="4"/>
       <c r="E254" s="4"/>
       <c r="F254" s="3" t="s">
-        <v>825</v>
+        <v>826</v>
       </c>
       <c r="G254" s="3"/>
     </row>
@@ -9383,7 +9465,7 @@
       <c r="D255" s="4"/>
       <c r="E255" s="4"/>
       <c r="F255" s="3" t="s">
-        <v>825</v>
+        <v>826</v>
       </c>
       <c r="G255" s="3"/>
     </row>
@@ -9400,7 +9482,7 @@
       <c r="D256" s="4"/>
       <c r="E256" s="4"/>
       <c r="F256" s="3" t="s">
-        <v>825</v>
+        <v>826</v>
       </c>
       <c r="G256" s="3"/>
     </row>
@@ -9419,7 +9501,7 @@
       </c>
       <c r="E257" s="4"/>
       <c r="F257" s="3" t="s">
-        <v>826</v>
+        <v>827</v>
       </c>
       <c r="G257" s="3" t="s">
         <v>337</v>
@@ -9440,7 +9522,7 @@
       </c>
       <c r="E258" s="4"/>
       <c r="F258" s="3" t="s">
-        <v>826</v>
+        <v>827</v>
       </c>
       <c r="G258" s="3" t="s">
         <v>339</v>
@@ -9459,7 +9541,7 @@
       <c r="D259" s="4"/>
       <c r="E259" s="4"/>
       <c r="F259" s="3" t="s">
-        <v>827</v>
+        <v>828</v>
       </c>
       <c r="G259" s="3" t="s">
         <v>341</v>
@@ -9478,7 +9560,7 @@
       <c r="D260" s="4"/>
       <c r="E260" s="4"/>
       <c r="F260" s="3" t="s">
-        <v>827</v>
+        <v>828</v>
       </c>
       <c r="G260" s="3"/>
     </row>
@@ -9495,7 +9577,7 @@
       <c r="D261" s="4"/>
       <c r="E261" s="4"/>
       <c r="F261" s="3" t="s">
-        <v>827</v>
+        <v>828</v>
       </c>
       <c r="G261" s="3"/>
     </row>
@@ -9512,7 +9594,7 @@
       <c r="D262" s="4"/>
       <c r="E262" s="4"/>
       <c r="F262" s="3" t="s">
-        <v>827</v>
+        <v>828</v>
       </c>
       <c r="G262" s="3"/>
     </row>
@@ -9529,7 +9611,7 @@
       <c r="D263" s="4"/>
       <c r="E263" s="4"/>
       <c r="F263" s="3" t="s">
-        <v>827</v>
+        <v>828</v>
       </c>
       <c r="G263" s="3" t="s">
         <v>346</v>
@@ -9548,7 +9630,7 @@
       <c r="D264" s="4"/>
       <c r="E264" s="4"/>
       <c r="F264" s="3" t="s">
-        <v>827</v>
+        <v>828</v>
       </c>
       <c r="G264" s="3"/>
     </row>
@@ -9565,7 +9647,7 @@
       <c r="D265" s="4"/>
       <c r="E265" s="4"/>
       <c r="F265" s="3" t="s">
-        <v>827</v>
+        <v>828</v>
       </c>
       <c r="G265" s="3"/>
     </row>
@@ -9582,7 +9664,7 @@
       <c r="D266" s="4"/>
       <c r="E266" s="4"/>
       <c r="F266" s="3" t="s">
-        <v>827</v>
+        <v>828</v>
       </c>
       <c r="G266" s="3" t="s">
         <v>748</v>
@@ -9601,7 +9683,7 @@
       <c r="D267" s="4"/>
       <c r="E267" s="4"/>
       <c r="F267" s="3" t="s">
-        <v>827</v>
+        <v>828</v>
       </c>
       <c r="G267" s="3" t="s">
         <v>749</v>
@@ -9620,7 +9702,7 @@
       <c r="D268" s="4"/>
       <c r="E268" s="4"/>
       <c r="F268" s="3" t="s">
-        <v>827</v>
+        <v>828</v>
       </c>
       <c r="G268" s="3" t="s">
         <v>750</v>
@@ -9639,7 +9721,7 @@
       <c r="D269" s="4"/>
       <c r="E269" s="4"/>
       <c r="F269" s="3" t="s">
-        <v>827</v>
+        <v>828</v>
       </c>
       <c r="G269" s="3" t="s">
         <v>751</v>
@@ -9658,7 +9740,7 @@
       <c r="D270" s="4"/>
       <c r="E270" s="4"/>
       <c r="F270" s="3" t="s">
-        <v>827</v>
+        <v>828</v>
       </c>
       <c r="G270" s="3" t="s">
         <v>354</v>
@@ -9677,7 +9759,7 @@
       <c r="D271" s="4"/>
       <c r="E271" s="4"/>
       <c r="F271" s="3" t="s">
-        <v>827</v>
+        <v>828</v>
       </c>
       <c r="G271" s="3"/>
     </row>
@@ -9694,7 +9776,7 @@
       <c r="D272" s="4"/>
       <c r="E272" s="4"/>
       <c r="F272" s="3" t="s">
-        <v>827</v>
+        <v>828</v>
       </c>
       <c r="G272" s="3"/>
     </row>
@@ -9711,7 +9793,7 @@
       <c r="D273" s="4"/>
       <c r="E273" s="4"/>
       <c r="F273" s="3" t="s">
-        <v>827</v>
+        <v>828</v>
       </c>
       <c r="G273" s="3"/>
     </row>
@@ -9728,7 +9810,7 @@
       <c r="D274" s="4"/>
       <c r="E274" s="4"/>
       <c r="F274" s="3" t="s">
-        <v>827</v>
+        <v>828</v>
       </c>
       <c r="G274" s="3"/>
     </row>
@@ -9745,7 +9827,7 @@
       <c r="D275" s="4"/>
       <c r="E275" s="4"/>
       <c r="F275" s="3" t="s">
-        <v>828</v>
+        <v>829</v>
       </c>
       <c r="G275" s="3" t="s">
         <v>360</v>
@@ -9764,7 +9846,7 @@
       <c r="D276" s="4"/>
       <c r="E276" s="4"/>
       <c r="F276" s="3" t="s">
-        <v>828</v>
+        <v>829</v>
       </c>
       <c r="G276" s="3" t="s">
         <v>362</v>
@@ -9783,7 +9865,7 @@
       <c r="D277" s="4"/>
       <c r="E277" s="4"/>
       <c r="F277" s="3" t="s">
-        <v>828</v>
+        <v>829</v>
       </c>
       <c r="G277" s="3"/>
     </row>
@@ -9800,7 +9882,7 @@
       <c r="D278" s="4"/>
       <c r="E278" s="4"/>
       <c r="F278" s="3" t="s">
-        <v>828</v>
+        <v>829</v>
       </c>
       <c r="G278" s="3" t="s">
         <v>365</v>
@@ -9819,7 +9901,7 @@
       <c r="D279" s="4"/>
       <c r="E279" s="4"/>
       <c r="F279" s="3" t="s">
-        <v>828</v>
+        <v>829</v>
       </c>
       <c r="G279" s="3" t="s">
         <v>367</v>
@@ -9838,7 +9920,7 @@
       <c r="D280" s="4"/>
       <c r="E280" s="4"/>
       <c r="F280" s="3" t="s">
-        <v>828</v>
+        <v>829</v>
       </c>
       <c r="G280" s="3" t="s">
         <v>369</v>
@@ -9857,7 +9939,7 @@
       <c r="D281" s="4"/>
       <c r="E281" s="4"/>
       <c r="F281" s="3" t="s">
-        <v>828</v>
+        <v>829</v>
       </c>
       <c r="G281" s="3" t="s">
         <v>369</v>
@@ -9876,7 +9958,7 @@
       <c r="D282" s="4"/>
       <c r="E282" s="4"/>
       <c r="F282" s="3" t="s">
-        <v>828</v>
+        <v>829</v>
       </c>
       <c r="G282" s="3" t="s">
         <v>369</v>
@@ -9895,7 +9977,7 @@
       <c r="D283" s="4"/>
       <c r="E283" s="4"/>
       <c r="F283" s="3" t="s">
-        <v>828</v>
+        <v>829</v>
       </c>
       <c r="G283" s="3"/>
     </row>
@@ -9912,7 +9994,7 @@
       <c r="D284" s="4"/>
       <c r="E284" s="4"/>
       <c r="F284" s="3" t="s">
-        <v>828</v>
+        <v>829</v>
       </c>
       <c r="G284" s="3"/>
     </row>
@@ -9929,7 +10011,7 @@
       <c r="D285" s="4"/>
       <c r="E285" s="4"/>
       <c r="F285" s="3" t="s">
-        <v>828</v>
+        <v>829</v>
       </c>
       <c r="G285" s="3"/>
     </row>
@@ -9946,7 +10028,7 @@
       <c r="D286" s="4"/>
       <c r="E286" s="4"/>
       <c r="F286" s="3" t="s">
-        <v>828</v>
+        <v>829</v>
       </c>
       <c r="G286" s="3"/>
     </row>
@@ -9963,7 +10045,7 @@
       <c r="D287" s="4"/>
       <c r="E287" s="4"/>
       <c r="F287" s="3" t="s">
-        <v>828</v>
+        <v>829</v>
       </c>
       <c r="G287" s="3"/>
     </row>
@@ -9982,7 +10064,7 @@
       </c>
       <c r="E288" s="4"/>
       <c r="F288" s="3" t="s">
-        <v>829</v>
+        <v>830</v>
       </c>
       <c r="G288" s="3" t="s">
         <v>378</v>
@@ -10005,7 +10087,7 @@
         <v>800</v>
       </c>
       <c r="F289" s="3" t="s">
-        <v>830</v>
+        <v>831</v>
       </c>
       <c r="G289" s="3" t="s">
         <v>386</v>
@@ -10028,7 +10110,7 @@
         <v>1200</v>
       </c>
       <c r="F290" s="3" t="s">
-        <v>830</v>
+        <v>831</v>
       </c>
       <c r="G290" s="3" t="s">
         <v>388</v>
@@ -10049,7 +10131,7 @@
       </c>
       <c r="E291" s="4"/>
       <c r="F291" s="3" t="s">
-        <v>830</v>
+        <v>831</v>
       </c>
       <c r="G291" s="3" t="s">
         <v>390</v>
@@ -10070,7 +10152,7 @@
       </c>
       <c r="E292" s="4"/>
       <c r="F292" s="3" t="s">
-        <v>830</v>
+        <v>831</v>
       </c>
       <c r="G292" s="3" t="s">
         <v>390</v>
@@ -10091,7 +10173,7 @@
       </c>
       <c r="E293" s="4"/>
       <c r="F293" s="3" t="s">
-        <v>831</v>
+        <v>832</v>
       </c>
       <c r="G293" s="3" t="s">
         <v>393</v>
@@ -10112,7 +10194,7 @@
       </c>
       <c r="E294" s="4"/>
       <c r="F294" s="3" t="s">
-        <v>831</v>
+        <v>832</v>
       </c>
       <c r="G294" s="3"/>
     </row>
@@ -10131,7 +10213,7 @@
       </c>
       <c r="E295" s="4"/>
       <c r="F295" s="3" t="s">
-        <v>831</v>
+        <v>832</v>
       </c>
       <c r="G295" s="3"/>
     </row>
@@ -10150,7 +10232,7 @@
       </c>
       <c r="E296" s="4"/>
       <c r="F296" s="3" t="s">
-        <v>831</v>
+        <v>832</v>
       </c>
       <c r="G296" s="3"/>
     </row>
@@ -10169,7 +10251,7 @@
       </c>
       <c r="E297" s="4"/>
       <c r="F297" s="3" t="s">
-        <v>832</v>
+        <v>833</v>
       </c>
       <c r="G297" s="3" t="s">
         <v>398</v>
@@ -10190,7 +10272,7 @@
       </c>
       <c r="E298" s="4"/>
       <c r="F298" s="3" t="s">
-        <v>832</v>
+        <v>833</v>
       </c>
       <c r="G298" s="3" t="s">
         <v>400</v>
@@ -10209,7 +10291,7 @@
       <c r="D299" s="4"/>
       <c r="E299" s="4"/>
       <c r="F299" s="3" t="s">
-        <v>833</v>
+        <v>834</v>
       </c>
       <c r="G299" s="3" t="s">
         <v>402</v>
@@ -10228,7 +10310,7 @@
       <c r="D300" s="4"/>
       <c r="E300" s="4"/>
       <c r="F300" s="3" t="s">
-        <v>833</v>
+        <v>834</v>
       </c>
       <c r="G300" s="3"/>
     </row>
@@ -10617,7 +10699,7 @@
       </c>
       <c r="E319" s="4"/>
       <c r="F319" s="3" t="s">
-        <v>834</v>
+        <v>835</v>
       </c>
       <c r="G319" s="3" t="s">
         <v>437</v>
@@ -10638,7 +10720,7 @@
       </c>
       <c r="E320" s="4"/>
       <c r="F320" s="3" t="s">
-        <v>834</v>
+        <v>835</v>
       </c>
       <c r="G320" s="3"/>
     </row>
@@ -10657,7 +10739,7 @@
       </c>
       <c r="E321" s="4"/>
       <c r="F321" s="3" t="s">
-        <v>834</v>
+        <v>835</v>
       </c>
       <c r="G321" s="3" t="s">
         <v>7</v>
@@ -10678,7 +10760,7 @@
       </c>
       <c r="E322" s="4"/>
       <c r="F322" s="3" t="s">
-        <v>834</v>
+        <v>835</v>
       </c>
       <c r="G322" s="3" t="s">
         <v>7</v>
@@ -10697,7 +10779,7 @@
       <c r="D323" s="4"/>
       <c r="E323" s="4"/>
       <c r="F323" s="3" t="s">
-        <v>834</v>
+        <v>835</v>
       </c>
       <c r="G323" s="3" t="s">
         <v>440</v>
@@ -10718,7 +10800,7 @@
       </c>
       <c r="E324" s="4"/>
       <c r="F324" s="3" t="s">
-        <v>835</v>
+        <v>836</v>
       </c>
       <c r="G324" s="3" t="s">
         <v>759</v>
@@ -10739,7 +10821,7 @@
       </c>
       <c r="E325" s="4"/>
       <c r="F325" s="3" t="s">
-        <v>835</v>
+        <v>836</v>
       </c>
       <c r="G325" s="3" t="s">
         <v>759</v>
@@ -10760,7 +10842,7 @@
       </c>
       <c r="E326" s="4"/>
       <c r="F326" s="3" t="s">
-        <v>835</v>
+        <v>836</v>
       </c>
       <c r="G326" s="3" t="s">
         <v>759</v>
@@ -10781,7 +10863,7 @@
       </c>
       <c r="E327" s="4"/>
       <c r="F327" s="3" t="s">
-        <v>835</v>
+        <v>836</v>
       </c>
       <c r="G327" s="3" t="s">
         <v>759</v>
@@ -11187,7 +11269,7 @@
       <c r="D347" s="4"/>
       <c r="E347" s="4"/>
       <c r="F347" s="3" t="s">
-        <v>836</v>
+        <v>837</v>
       </c>
       <c r="G347" s="3" t="s">
         <v>466</v>
@@ -11206,7 +11288,7 @@
       <c r="D348" s="4"/>
       <c r="E348" s="4"/>
       <c r="F348" s="3" t="s">
-        <v>836</v>
+        <v>837</v>
       </c>
       <c r="G348" s="3" t="s">
         <v>468</v>
@@ -11225,7 +11307,7 @@
       <c r="D349" s="4"/>
       <c r="E349" s="4"/>
       <c r="F349" s="3" t="s">
-        <v>836</v>
+        <v>837</v>
       </c>
       <c r="G349" s="3" t="s">
         <v>470</v>
@@ -11244,7 +11326,7 @@
       <c r="D350" s="4"/>
       <c r="E350" s="4"/>
       <c r="F350" s="3" t="s">
-        <v>836</v>
+        <v>837</v>
       </c>
       <c r="G350" s="3" t="s">
         <v>472</v>
@@ -11263,7 +11345,7 @@
       <c r="D351" s="4"/>
       <c r="E351" s="4"/>
       <c r="F351" s="3" t="s">
-        <v>836</v>
+        <v>837</v>
       </c>
       <c r="G351" s="3" t="s">
         <v>474</v>
@@ -11282,7 +11364,7 @@
       <c r="D352" s="4"/>
       <c r="E352" s="4"/>
       <c r="F352" s="3" t="s">
-        <v>836</v>
+        <v>837</v>
       </c>
       <c r="G352" s="3" t="s">
         <v>476</v>
@@ -11301,7 +11383,7 @@
       <c r="D353" s="4"/>
       <c r="E353" s="4"/>
       <c r="F353" s="3" t="s">
-        <v>836</v>
+        <v>837</v>
       </c>
       <c r="G353" s="3" t="s">
         <v>478</v>
@@ -11320,7 +11402,7 @@
       <c r="D354" s="4"/>
       <c r="E354" s="4"/>
       <c r="F354" s="3" t="s">
-        <v>836</v>
+        <v>837</v>
       </c>
       <c r="G354" s="3" t="s">
         <v>480</v>
@@ -11339,7 +11421,7 @@
       <c r="D355" s="4"/>
       <c r="E355" s="4"/>
       <c r="F355" s="3" t="s">
-        <v>836</v>
+        <v>837</v>
       </c>
       <c r="G355" s="3" t="s">
         <v>482</v>
@@ -11358,7 +11440,7 @@
       <c r="D356" s="4"/>
       <c r="E356" s="4"/>
       <c r="F356" s="3" t="s">
-        <v>836</v>
+        <v>837</v>
       </c>
       <c r="G356" s="3" t="s">
         <v>484</v>
@@ -11377,7 +11459,7 @@
       <c r="D357" s="4"/>
       <c r="E357" s="4"/>
       <c r="F357" s="3" t="s">
-        <v>836</v>
+        <v>837</v>
       </c>
       <c r="G357" s="3" t="s">
         <v>486</v>
@@ -11396,7 +11478,7 @@
       <c r="D358" s="4"/>
       <c r="E358" s="4"/>
       <c r="F358" s="3" t="s">
-        <v>836</v>
+        <v>837</v>
       </c>
       <c r="G358" s="3" t="s">
         <v>488</v>
@@ -11415,7 +11497,7 @@
       <c r="D359" s="4"/>
       <c r="E359" s="4"/>
       <c r="F359" s="3" t="s">
-        <v>836</v>
+        <v>837</v>
       </c>
       <c r="G359" s="3" t="s">
         <v>490</v>
@@ -11434,7 +11516,7 @@
       <c r="D360" s="4"/>
       <c r="E360" s="4"/>
       <c r="F360" s="3" t="s">
-        <v>836</v>
+        <v>837</v>
       </c>
       <c r="G360" s="3" t="s">
         <v>492</v>
@@ -11453,7 +11535,7 @@
       <c r="D361" s="4"/>
       <c r="E361" s="4"/>
       <c r="F361" s="3" t="s">
-        <v>837</v>
+        <v>838</v>
       </c>
       <c r="G361" s="3" t="s">
         <v>494</v>
@@ -11472,7 +11554,7 @@
       <c r="D362" s="4"/>
       <c r="E362" s="4"/>
       <c r="F362" s="3" t="s">
-        <v>837</v>
+        <v>838</v>
       </c>
       <c r="G362" s="3" t="s">
         <v>496</v>
@@ -11491,7 +11573,7 @@
       <c r="D363" s="4"/>
       <c r="E363" s="4"/>
       <c r="F363" s="3" t="s">
-        <v>837</v>
+        <v>838</v>
       </c>
       <c r="G363" s="3" t="s">
         <v>498</v>
@@ -11510,7 +11592,7 @@
       <c r="D364" s="4"/>
       <c r="E364" s="4"/>
       <c r="F364" s="3" t="s">
-        <v>837</v>
+        <v>838</v>
       </c>
       <c r="G364" s="3" t="s">
         <v>500</v>
@@ -11529,7 +11611,7 @@
       <c r="D365" s="4"/>
       <c r="E365" s="4"/>
       <c r="F365" s="3" t="s">
-        <v>837</v>
+        <v>838</v>
       </c>
       <c r="G365" s="3" t="s">
         <v>502</v>
@@ -11548,7 +11630,7 @@
       <c r="D366" s="4"/>
       <c r="E366" s="4"/>
       <c r="F366" s="3" t="s">
-        <v>837</v>
+        <v>838</v>
       </c>
       <c r="G366" s="3" t="s">
         <v>504</v>
@@ -11567,7 +11649,7 @@
       <c r="D367" s="4"/>
       <c r="E367" s="4"/>
       <c r="F367" s="3" t="s">
-        <v>837</v>
+        <v>838</v>
       </c>
       <c r="G367" s="3" t="s">
         <v>506</v>
@@ -11586,7 +11668,7 @@
       <c r="D368" s="4"/>
       <c r="E368" s="4"/>
       <c r="F368" s="3" t="s">
-        <v>837</v>
+        <v>838</v>
       </c>
       <c r="G368" s="3" t="s">
         <v>508</v>
@@ -11605,7 +11687,7 @@
       <c r="D369" s="4"/>
       <c r="E369" s="4"/>
       <c r="F369" s="3" t="s">
-        <v>837</v>
+        <v>838</v>
       </c>
       <c r="G369" s="3" t="s">
         <v>510</v>
@@ -11624,7 +11706,7 @@
       <c r="D370" s="4"/>
       <c r="E370" s="4"/>
       <c r="F370" s="3" t="s">
-        <v>837</v>
+        <v>838</v>
       </c>
       <c r="G370" s="3" t="s">
         <v>512</v>
@@ -11643,7 +11725,7 @@
       <c r="D371" s="4"/>
       <c r="E371" s="4"/>
       <c r="F371" s="3" t="s">
-        <v>837</v>
+        <v>838</v>
       </c>
       <c r="G371" s="3" t="s">
         <v>514</v>
@@ -11662,7 +11744,7 @@
       <c r="D372" s="4"/>
       <c r="E372" s="4"/>
       <c r="F372" s="3" t="s">
-        <v>837</v>
+        <v>838</v>
       </c>
       <c r="G372" s="3" t="s">
         <v>516</v>
@@ -11681,7 +11763,7 @@
       <c r="D373" s="4"/>
       <c r="E373" s="4"/>
       <c r="F373" s="3" t="s">
-        <v>837</v>
+        <v>838</v>
       </c>
       <c r="G373" s="3" t="s">
         <v>518</v>
@@ -11700,7 +11782,7 @@
       <c r="D374" s="4"/>
       <c r="E374" s="4"/>
       <c r="F374" s="3" t="s">
-        <v>837</v>
+        <v>838</v>
       </c>
       <c r="G374" s="3" t="s">
         <v>520</v>
@@ -11719,7 +11801,7 @@
       <c r="D375" s="4"/>
       <c r="E375" s="4"/>
       <c r="F375" s="3" t="s">
-        <v>837</v>
+        <v>838</v>
       </c>
       <c r="G375" s="3"/>
     </row>
@@ -11736,7 +11818,7 @@
       <c r="D376" s="4"/>
       <c r="E376" s="4"/>
       <c r="F376" s="3" t="s">
-        <v>837</v>
+        <v>838</v>
       </c>
       <c r="G376" s="3"/>
     </row>
@@ -11753,7 +11835,7 @@
       <c r="D377" s="4"/>
       <c r="E377" s="4"/>
       <c r="F377" s="3" t="s">
-        <v>837</v>
+        <v>838</v>
       </c>
       <c r="G377" s="3"/>
     </row>
@@ -11770,7 +11852,7 @@
       <c r="D378" s="4"/>
       <c r="E378" s="4"/>
       <c r="F378" s="3" t="s">
-        <v>837</v>
+        <v>838</v>
       </c>
       <c r="G378" s="3"/>
     </row>
@@ -11787,7 +11869,7 @@
       <c r="D379" s="4"/>
       <c r="E379" s="4"/>
       <c r="F379" s="3" t="s">
-        <v>837</v>
+        <v>838</v>
       </c>
       <c r="G379" s="3" t="s">
         <v>526</v>
@@ -11806,7 +11888,7 @@
       <c r="D380" s="4"/>
       <c r="E380" s="4"/>
       <c r="F380" s="3" t="s">
-        <v>837</v>
+        <v>838</v>
       </c>
       <c r="G380" s="3"/>
     </row>
@@ -11825,7 +11907,7 @@
       </c>
       <c r="E381" s="4"/>
       <c r="F381" s="3" t="s">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="G381" s="3" t="s">
         <v>529</v>
@@ -11846,7 +11928,7 @@
       </c>
       <c r="E382" s="4"/>
       <c r="F382" s="3" t="s">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="G382" s="3" t="s">
         <v>531</v>
@@ -11867,7 +11949,7 @@
       </c>
       <c r="E383" s="4"/>
       <c r="F383" s="3" t="s">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="G383" s="3" t="s">
         <v>533</v>
@@ -11888,7 +11970,7 @@
       </c>
       <c r="E384" s="4"/>
       <c r="F384" s="3" t="s">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="G384" s="3" t="s">
         <v>535</v>
@@ -11909,7 +11991,7 @@
       </c>
       <c r="E385" s="4"/>
       <c r="F385" s="3" t="s">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="G385" s="3" t="s">
         <v>535</v>
@@ -11930,7 +12012,7 @@
       </c>
       <c r="E386" s="4"/>
       <c r="F386" s="3" t="s">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="G386" s="3" t="s">
         <v>535</v>
@@ -11951,7 +12033,7 @@
       </c>
       <c r="E387" s="4"/>
       <c r="F387" s="3" t="s">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="G387" s="3" t="s">
         <v>539</v>
@@ -11972,7 +12054,7 @@
       </c>
       <c r="E388" s="4"/>
       <c r="F388" s="3" t="s">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="G388" s="3" t="s">
         <v>541</v>
@@ -11993,7 +12075,7 @@
       </c>
       <c r="E389" s="4"/>
       <c r="F389" s="3" t="s">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="G389" s="3" t="s">
         <v>543</v>
@@ -12014,7 +12096,7 @@
       </c>
       <c r="E390" s="4"/>
       <c r="F390" s="3" t="s">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="G390" s="3"/>
     </row>
@@ -12033,7 +12115,7 @@
       </c>
       <c r="E391" s="4"/>
       <c r="F391" s="3" t="s">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="G391" s="3"/>
     </row>
@@ -12052,7 +12134,7 @@
       </c>
       <c r="E392" s="4"/>
       <c r="F392" s="3" t="s">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="G392" s="3"/>
     </row>
@@ -12071,7 +12153,7 @@
       </c>
       <c r="E393" s="4"/>
       <c r="F393" s="3" t="s">
-        <v>839</v>
+        <v>840</v>
       </c>
       <c r="G393" s="3" t="s">
         <v>548</v>
@@ -12092,7 +12174,7 @@
       </c>
       <c r="E394" s="4"/>
       <c r="F394" s="3" t="s">
-        <v>840</v>
+        <v>841</v>
       </c>
       <c r="G394" s="3" t="s">
         <v>550</v>
@@ -12113,7 +12195,7 @@
       </c>
       <c r="E395" s="4"/>
       <c r="F395" s="3" t="s">
-        <v>840</v>
+        <v>841</v>
       </c>
       <c r="G395" s="3" t="s">
         <v>552</v>
@@ -12134,7 +12216,7 @@
       </c>
       <c r="E396" s="4"/>
       <c r="F396" s="3" t="s">
-        <v>840</v>
+        <v>841</v>
       </c>
       <c r="G396" s="3" t="s">
         <v>552</v>
@@ -12155,7 +12237,7 @@
       </c>
       <c r="E397" s="4"/>
       <c r="F397" s="3" t="s">
-        <v>840</v>
+        <v>841</v>
       </c>
       <c r="G397" s="3" t="s">
         <v>552</v>
@@ -12176,7 +12258,7 @@
       </c>
       <c r="E398" s="4"/>
       <c r="F398" s="3" t="s">
-        <v>840</v>
+        <v>841</v>
       </c>
       <c r="G398" s="3" t="s">
         <v>556</v>
@@ -12197,7 +12279,7 @@
       </c>
       <c r="E399" s="4"/>
       <c r="F399" s="3" t="s">
-        <v>840</v>
+        <v>841</v>
       </c>
       <c r="G399" s="3" t="s">
         <v>558</v>
@@ -12218,7 +12300,7 @@
       </c>
       <c r="E400" s="4"/>
       <c r="F400" s="3" t="s">
-        <v>840</v>
+        <v>841</v>
       </c>
       <c r="G400" s="3" t="s">
         <v>560</v>
@@ -12239,7 +12321,7 @@
       </c>
       <c r="E401" s="4"/>
       <c r="F401" s="3" t="s">
-        <v>840</v>
+        <v>841</v>
       </c>
       <c r="G401" s="3" t="s">
         <v>562</v>
@@ -12260,7 +12342,7 @@
       </c>
       <c r="E402" s="4"/>
       <c r="F402" s="3" t="s">
-        <v>840</v>
+        <v>841</v>
       </c>
       <c r="G402" s="3" t="s">
         <v>564</v>
@@ -12281,7 +12363,7 @@
       </c>
       <c r="E403" s="4"/>
       <c r="F403" s="3" t="s">
-        <v>840</v>
+        <v>841</v>
       </c>
       <c r="G403" s="3" t="s">
         <v>566</v>
@@ -12302,7 +12384,7 @@
       </c>
       <c r="E404" s="4"/>
       <c r="F404" s="3" t="s">
-        <v>840</v>
+        <v>841</v>
       </c>
       <c r="G404" s="3" t="s">
         <v>568</v>
@@ -12323,7 +12405,7 @@
       </c>
       <c r="E405" s="4"/>
       <c r="F405" s="3" t="s">
-        <v>840</v>
+        <v>841</v>
       </c>
       <c r="G405" s="3" t="s">
         <v>570</v>
@@ -12344,7 +12426,7 @@
       </c>
       <c r="E406" s="4"/>
       <c r="F406" s="3" t="s">
-        <v>841</v>
+        <v>842</v>
       </c>
       <c r="G406" s="3" t="s">
         <v>572</v>
@@ -12365,7 +12447,7 @@
       </c>
       <c r="E407" s="4"/>
       <c r="F407" s="3" t="s">
-        <v>841</v>
+        <v>842</v>
       </c>
       <c r="G407" s="3" t="s">
         <v>574</v>
@@ -12386,7 +12468,7 @@
       </c>
       <c r="E408" s="4"/>
       <c r="F408" s="3" t="s">
-        <v>841</v>
+        <v>842</v>
       </c>
       <c r="G408" s="3"/>
     </row>
@@ -12405,7 +12487,7 @@
       </c>
       <c r="E409" s="4"/>
       <c r="F409" s="3" t="s">
-        <v>841</v>
+        <v>842</v>
       </c>
       <c r="G409" s="3"/>
     </row>
@@ -12424,7 +12506,7 @@
       </c>
       <c r="E410" s="4"/>
       <c r="F410" s="3" t="s">
-        <v>841</v>
+        <v>842</v>
       </c>
       <c r="G410" s="3"/>
     </row>
@@ -12443,7 +12525,7 @@
       </c>
       <c r="E411" s="4"/>
       <c r="F411" s="3" t="s">
-        <v>841</v>
+        <v>842</v>
       </c>
       <c r="G411" s="3"/>
     </row>
@@ -12460,7 +12542,7 @@
       <c r="D412" s="4"/>
       <c r="E412" s="4"/>
       <c r="F412" s="3" t="s">
-        <v>841</v>
+        <v>842</v>
       </c>
       <c r="G412" s="3"/>
     </row>
@@ -12477,7 +12559,7 @@
       <c r="D413" s="4"/>
       <c r="E413" s="4"/>
       <c r="F413" s="3" t="s">
-        <v>841</v>
+        <v>842</v>
       </c>
       <c r="G413" s="3"/>
     </row>
@@ -12496,7 +12578,7 @@
       </c>
       <c r="E414" s="4"/>
       <c r="F414" s="3" t="s">
-        <v>842</v>
+        <v>843</v>
       </c>
       <c r="G414" s="3" t="s">
         <v>582</v>
@@ -12517,7 +12599,7 @@
       </c>
       <c r="E415" s="4"/>
       <c r="F415" s="3" t="s">
-        <v>842</v>
+        <v>843</v>
       </c>
       <c r="G415" s="3"/>
     </row>
@@ -12536,7 +12618,7 @@
       </c>
       <c r="E416" s="4"/>
       <c r="F416" s="3" t="s">
-        <v>842</v>
+        <v>843</v>
       </c>
       <c r="G416" s="3"/>
     </row>
@@ -12555,7 +12637,7 @@
       </c>
       <c r="E417" s="4"/>
       <c r="F417" s="3" t="s">
-        <v>842</v>
+        <v>843</v>
       </c>
       <c r="G417" s="3"/>
     </row>
@@ -12574,7 +12656,7 @@
       </c>
       <c r="E418" s="4"/>
       <c r="F418" s="3" t="s">
-        <v>843</v>
+        <v>844</v>
       </c>
       <c r="G418" s="3" t="s">
         <v>587</v>
@@ -12595,7 +12677,7 @@
       </c>
       <c r="E419" s="4"/>
       <c r="F419" s="3" t="s">
-        <v>843</v>
+        <v>844</v>
       </c>
       <c r="G419" s="3"/>
     </row>
@@ -12614,7 +12696,7 @@
       </c>
       <c r="E420" s="4"/>
       <c r="F420" s="3" t="s">
-        <v>843</v>
+        <v>844</v>
       </c>
       <c r="G420" s="3"/>
     </row>
@@ -12633,7 +12715,7 @@
       </c>
       <c r="E421" s="4"/>
       <c r="F421" s="3" t="s">
-        <v>843</v>
+        <v>844</v>
       </c>
       <c r="G421" s="3"/>
     </row>
@@ -12652,7 +12734,7 @@
       </c>
       <c r="E422" s="4"/>
       <c r="F422" s="3" t="s">
-        <v>843</v>
+        <v>844</v>
       </c>
       <c r="G422" s="3"/>
     </row>
@@ -12671,7 +12753,7 @@
       </c>
       <c r="E423" s="4"/>
       <c r="F423" s="3" t="s">
-        <v>843</v>
+        <v>844</v>
       </c>
       <c r="G423" s="3"/>
     </row>
@@ -12690,7 +12772,7 @@
       </c>
       <c r="E424" s="4"/>
       <c r="F424" s="3" t="s">
-        <v>843</v>
+        <v>844</v>
       </c>
       <c r="G424" s="3"/>
     </row>
@@ -12709,7 +12791,7 @@
       </c>
       <c r="E425" s="4"/>
       <c r="F425" s="3" t="s">
-        <v>843</v>
+        <v>844</v>
       </c>
       <c r="G425" s="3"/>
     </row>
@@ -12728,7 +12810,7 @@
       </c>
       <c r="E426" s="4"/>
       <c r="F426" s="3" t="s">
-        <v>843</v>
+        <v>844</v>
       </c>
       <c r="G426" s="3"/>
     </row>
@@ -12747,7 +12829,7 @@
       </c>
       <c r="E427" s="4"/>
       <c r="F427" s="3" t="s">
-        <v>843</v>
+        <v>844</v>
       </c>
       <c r="G427" s="3"/>
     </row>
@@ -12766,7 +12848,7 @@
       </c>
       <c r="E428" s="4"/>
       <c r="F428" s="3" t="s">
-        <v>843</v>
+        <v>844</v>
       </c>
       <c r="G428" s="3"/>
     </row>
@@ -13110,7 +13192,7 @@
       <c r="D446" s="4"/>
       <c r="E446" s="4"/>
       <c r="F446" s="3" t="s">
-        <v>844</v>
+        <v>845</v>
       </c>
       <c r="G446" s="3" t="s">
         <v>626</v>
@@ -13129,7 +13211,7 @@
       <c r="D447" s="4"/>
       <c r="E447" s="4"/>
       <c r="F447" s="3" t="s">
-        <v>844</v>
+        <v>845</v>
       </c>
       <c r="G447" s="3"/>
     </row>
@@ -13146,7 +13228,7 @@
       <c r="D448" s="4"/>
       <c r="E448" s="4"/>
       <c r="F448" s="3" t="s">
-        <v>844</v>
+        <v>845</v>
       </c>
       <c r="G448" s="3"/>
     </row>
@@ -13165,7 +13247,7 @@
       </c>
       <c r="E449" s="4"/>
       <c r="F449" s="3" t="s">
-        <v>844</v>
+        <v>845</v>
       </c>
       <c r="G449" s="3"/>
     </row>
@@ -13184,7 +13266,7 @@
       </c>
       <c r="E450" s="4"/>
       <c r="F450" s="3" t="s">
-        <v>844</v>
+        <v>845</v>
       </c>
       <c r="G450" s="3"/>
     </row>
@@ -13201,7 +13283,7 @@
       <c r="D451" s="4"/>
       <c r="E451" s="4"/>
       <c r="F451" s="3" t="s">
-        <v>844</v>
+        <v>845</v>
       </c>
       <c r="G451" s="3"/>
     </row>
@@ -13218,7 +13300,7 @@
       <c r="D452" s="4"/>
       <c r="E452" s="4"/>
       <c r="F452" s="3" t="s">
-        <v>844</v>
+        <v>845</v>
       </c>
       <c r="G452" s="3"/>
     </row>
@@ -13235,7 +13317,7 @@
       <c r="D453" s="4"/>
       <c r="E453" s="4"/>
       <c r="F453" s="3" t="s">
-        <v>844</v>
+        <v>845</v>
       </c>
       <c r="G453" s="3"/>
     </row>
@@ -13252,7 +13334,7 @@
       <c r="D454" s="4"/>
       <c r="E454" s="4"/>
       <c r="F454" s="3" t="s">
-        <v>844</v>
+        <v>845</v>
       </c>
       <c r="G454" s="3"/>
     </row>
@@ -13269,7 +13351,7 @@
       <c r="D455" s="4"/>
       <c r="E455" s="4"/>
       <c r="F455" s="3" t="s">
-        <v>844</v>
+        <v>845</v>
       </c>
       <c r="G455" s="3"/>
     </row>
@@ -13286,7 +13368,7 @@
       <c r="D456" s="4"/>
       <c r="E456" s="4"/>
       <c r="F456" s="3" t="s">
-        <v>844</v>
+        <v>845</v>
       </c>
       <c r="G456" s="3"/>
     </row>
@@ -13303,7 +13385,7 @@
       <c r="D457" s="4"/>
       <c r="E457" s="4"/>
       <c r="F457" s="3" t="s">
-        <v>844</v>
+        <v>845</v>
       </c>
       <c r="G457" s="3"/>
     </row>
@@ -13320,7 +13402,7 @@
       <c r="D458" s="4"/>
       <c r="E458" s="4"/>
       <c r="F458" s="3" t="s">
-        <v>844</v>
+        <v>845</v>
       </c>
       <c r="G458" s="3"/>
     </row>
@@ -13337,7 +13419,7 @@
       <c r="D459" s="4"/>
       <c r="E459" s="4"/>
       <c r="F459" s="3" t="s">
-        <v>844</v>
+        <v>845</v>
       </c>
       <c r="G459" s="3"/>
     </row>
@@ -13354,7 +13436,7 @@
       <c r="D460" s="4"/>
       <c r="E460" s="4"/>
       <c r="F460" s="3" t="s">
-        <v>844</v>
+        <v>845</v>
       </c>
       <c r="G460" s="3"/>
     </row>
@@ -13371,7 +13453,7 @@
       <c r="D461" s="4"/>
       <c r="E461" s="4"/>
       <c r="F461" s="3" t="s">
-        <v>844</v>
+        <v>845</v>
       </c>
       <c r="G461" s="3"/>
     </row>
@@ -13388,7 +13470,7 @@
       <c r="D462" s="4"/>
       <c r="E462" s="4"/>
       <c r="F462" s="3" t="s">
-        <v>844</v>
+        <v>845</v>
       </c>
       <c r="G462" s="3"/>
     </row>
@@ -13675,7 +13757,7 @@
       </c>
       <c r="E477" s="6"/>
       <c r="F477" s="3" t="s">
-        <v>845</v>
+        <v>846</v>
       </c>
       <c r="G477" s="5" t="s">
         <v>659</v>
@@ -13696,7 +13778,7 @@
       </c>
       <c r="E478" s="6"/>
       <c r="F478" s="3" t="s">
-        <v>845</v>
+        <v>846</v>
       </c>
       <c r="G478" s="5" t="s">
         <v>661</v>
@@ -13717,7 +13799,7 @@
       </c>
       <c r="E479" s="6"/>
       <c r="F479" s="3" t="s">
-        <v>845</v>
+        <v>846</v>
       </c>
       <c r="G479" s="5" t="s">
         <v>663</v>
@@ -13738,7 +13820,7 @@
       </c>
       <c r="E480" s="6"/>
       <c r="F480" s="3" t="s">
-        <v>845</v>
+        <v>846</v>
       </c>
       <c r="G480" s="5" t="s">
         <v>665</v>
@@ -13759,7 +13841,7 @@
       </c>
       <c r="E481" s="6"/>
       <c r="F481" s="3" t="s">
-        <v>845</v>
+        <v>846</v>
       </c>
       <c r="G481" s="5" t="s">
         <v>663</v>
@@ -13780,7 +13862,7 @@
       </c>
       <c r="E482" s="6"/>
       <c r="F482" s="3" t="s">
-        <v>845</v>
+        <v>846</v>
       </c>
       <c r="G482" s="5" t="s">
         <v>665</v>
@@ -13801,7 +13883,7 @@
       </c>
       <c r="E483" s="6"/>
       <c r="F483" s="3" t="s">
-        <v>845</v>
+        <v>846</v>
       </c>
       <c r="G483" s="5" t="s">
         <v>669</v>
@@ -13812,7 +13894,7 @@
         <v>384</v>
       </c>
       <c r="B484" s="5" t="s">
-        <v>1094</v>
+        <v>762</v>
       </c>
       <c r="C484" s="6">
         <v>6800</v>
@@ -13822,7 +13904,7 @@
       </c>
       <c r="E484" s="6"/>
       <c r="F484" s="3" t="s">
-        <v>845</v>
+        <v>846</v>
       </c>
       <c r="G484" s="5" t="s">
         <v>669</v>
@@ -13843,7 +13925,7 @@
       </c>
       <c r="E485" s="6"/>
       <c r="F485" s="3" t="s">
-        <v>845</v>
+        <v>846</v>
       </c>
       <c r="G485" s="5" t="s">
         <v>671</v>
@@ -13864,7 +13946,7 @@
       </c>
       <c r="E486" s="6"/>
       <c r="F486" s="3" t="s">
-        <v>845</v>
+        <v>846</v>
       </c>
       <c r="G486" s="5" t="s">
         <v>673</v>
@@ -13885,7 +13967,7 @@
       </c>
       <c r="E487" s="6"/>
       <c r="F487" s="3" t="s">
-        <v>845</v>
+        <v>846</v>
       </c>
       <c r="G487" s="5" t="s">
         <v>675</v>
@@ -13906,7 +13988,7 @@
       </c>
       <c r="E488" s="6"/>
       <c r="F488" s="3" t="s">
-        <v>845</v>
+        <v>846</v>
       </c>
       <c r="G488" s="5" t="s">
         <v>677</v>
@@ -13927,7 +14009,7 @@
       </c>
       <c r="E489" s="6"/>
       <c r="F489" s="3" t="s">
-        <v>845</v>
+        <v>846</v>
       </c>
       <c r="G489" s="5" t="s">
         <v>679</v>
@@ -13948,7 +14030,7 @@
       </c>
       <c r="E490" s="6"/>
       <c r="F490" s="3" t="s">
-        <v>845</v>
+        <v>846</v>
       </c>
       <c r="G490" s="5" t="s">
         <v>681</v>
@@ -13969,7 +14051,7 @@
       </c>
       <c r="E491" s="6"/>
       <c r="F491" s="3" t="s">
-        <v>845</v>
+        <v>846</v>
       </c>
       <c r="G491" s="5" t="s">
         <v>683</v>
@@ -13990,7 +14072,7 @@
       </c>
       <c r="E492" s="6"/>
       <c r="F492" s="3" t="s">
-        <v>845</v>
+        <v>846</v>
       </c>
       <c r="G492" s="5" t="s">
         <v>685</v>
@@ -14011,7 +14093,7 @@
       </c>
       <c r="E493" s="6"/>
       <c r="F493" s="3" t="s">
-        <v>845</v>
+        <v>846</v>
       </c>
       <c r="G493" s="5" t="s">
         <v>687</v>
@@ -14032,7 +14114,7 @@
       </c>
       <c r="E494" s="6"/>
       <c r="F494" s="3" t="s">
-        <v>845</v>
+        <v>846</v>
       </c>
       <c r="G494" s="5" t="s">
         <v>689</v>
@@ -14053,7 +14135,7 @@
       </c>
       <c r="E495" s="6"/>
       <c r="F495" s="3" t="s">
-        <v>845</v>
+        <v>846</v>
       </c>
       <c r="G495" s="5" t="s">
         <v>685</v>
@@ -14074,7 +14156,7 @@
       </c>
       <c r="E496" s="6"/>
       <c r="F496" s="3" t="s">
-        <v>845</v>
+        <v>846</v>
       </c>
       <c r="G496" s="5" t="s">
         <v>692</v>
@@ -14095,7 +14177,7 @@
       </c>
       <c r="E497" s="6"/>
       <c r="F497" s="3" t="s">
-        <v>845</v>
+        <v>846</v>
       </c>
       <c r="G497" s="5" t="s">
         <v>693</v>
@@ -14116,7 +14198,7 @@
       </c>
       <c r="E498" s="6"/>
       <c r="F498" s="3" t="s">
-        <v>845</v>
+        <v>846</v>
       </c>
       <c r="G498" s="5" t="s">
         <v>694</v>
@@ -14137,7 +14219,7 @@
       </c>
       <c r="E499" s="4"/>
       <c r="F499" s="3" t="s">
-        <v>846</v>
+        <v>847</v>
       </c>
       <c r="G499" s="3" t="s">
         <v>696</v>
@@ -14158,7 +14240,7 @@
       </c>
       <c r="E500" s="4"/>
       <c r="F500" s="3" t="s">
-        <v>846</v>
+        <v>847</v>
       </c>
       <c r="G500" s="3" t="s">
         <v>698</v>
@@ -14179,7 +14261,7 @@
       </c>
       <c r="E501" s="4"/>
       <c r="F501" s="3" t="s">
-        <v>846</v>
+        <v>847</v>
       </c>
       <c r="G501" s="3" t="s">
         <v>700</v>
@@ -14200,7 +14282,7 @@
       </c>
       <c r="E502" s="4"/>
       <c r="F502" s="3" t="s">
-        <v>846</v>
+        <v>847</v>
       </c>
       <c r="G502" s="3" t="s">
         <v>702</v>
@@ -14221,7 +14303,7 @@
       </c>
       <c r="E503" s="4"/>
       <c r="F503" s="3" t="s">
-        <v>846</v>
+        <v>847</v>
       </c>
       <c r="G503" s="3" t="s">
         <v>704</v>
@@ -14242,7 +14324,7 @@
       </c>
       <c r="E504" s="4"/>
       <c r="F504" s="3" t="s">
-        <v>846</v>
+        <v>847</v>
       </c>
       <c r="G504" s="3" t="s">
         <v>706</v>
@@ -14263,7 +14345,7 @@
       </c>
       <c r="E505" s="4"/>
       <c r="F505" s="3" t="s">
-        <v>846</v>
+        <v>847</v>
       </c>
       <c r="G505" s="3" t="s">
         <v>708</v>
@@ -14274,7 +14356,7 @@
         <v>384</v>
       </c>
       <c r="B506" s="3" t="s">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="C506" s="4">
         <v>850</v>
@@ -14284,10 +14366,10 @@
       </c>
       <c r="E506" s="4"/>
       <c r="F506" s="3" t="s">
-        <v>860</v>
+        <v>1093</v>
       </c>
       <c r="G506" s="3" t="s">
-        <v>782</v>
+        <v>783</v>
       </c>
     </row>
     <row r="507" spans="1:7" x14ac:dyDescent="0.3">
@@ -14295,7 +14377,7 @@
         <v>384</v>
       </c>
       <c r="B507" s="3" t="s">
-        <v>763</v>
+        <v>764</v>
       </c>
       <c r="C507" s="4">
         <v>1350</v>
@@ -14305,10 +14387,10 @@
       </c>
       <c r="E507" s="4"/>
       <c r="F507" s="3" t="s">
-        <v>860</v>
+        <v>1093</v>
       </c>
       <c r="G507" s="3" t="s">
-        <v>782</v>
+        <v>783</v>
       </c>
     </row>
     <row r="508" spans="1:7" x14ac:dyDescent="0.3">
@@ -14316,7 +14398,7 @@
         <v>384</v>
       </c>
       <c r="B508" s="3" t="s">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="C508" s="4">
         <v>1550</v>
@@ -14326,10 +14408,10 @@
       </c>
       <c r="E508" s="4"/>
       <c r="F508" s="3" t="s">
-        <v>860</v>
+        <v>1093</v>
       </c>
       <c r="G508" s="3" t="s">
-        <v>782</v>
+        <v>783</v>
       </c>
     </row>
     <row r="509" spans="1:7" x14ac:dyDescent="0.3">
@@ -14337,7 +14419,7 @@
         <v>384</v>
       </c>
       <c r="B509" s="3" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="C509" s="4">
         <v>1000</v>
@@ -14347,10 +14429,10 @@
       </c>
       <c r="E509" s="4"/>
       <c r="F509" s="3" t="s">
-        <v>860</v>
+        <v>1093</v>
       </c>
       <c r="G509" s="3" t="s">
-        <v>782</v>
+        <v>783</v>
       </c>
     </row>
     <row r="510" spans="1:7" x14ac:dyDescent="0.3">
@@ -14358,7 +14440,7 @@
         <v>384</v>
       </c>
       <c r="B510" s="3" t="s">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="C510" s="4">
         <v>1400</v>
@@ -14368,10 +14450,10 @@
       </c>
       <c r="E510" s="4"/>
       <c r="F510" s="3" t="s">
-        <v>860</v>
+        <v>1093</v>
       </c>
       <c r="G510" s="3" t="s">
-        <v>782</v>
+        <v>783</v>
       </c>
     </row>
     <row r="511" spans="1:7" x14ac:dyDescent="0.3">
@@ -14379,7 +14461,7 @@
         <v>384</v>
       </c>
       <c r="B511" s="3" t="s">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="C511" s="4">
         <v>2300</v>
@@ -14389,10 +14471,10 @@
       </c>
       <c r="E511" s="4"/>
       <c r="F511" s="3" t="s">
-        <v>860</v>
+        <v>1093</v>
       </c>
       <c r="G511" s="3" t="s">
-        <v>782</v>
+        <v>783</v>
       </c>
     </row>
     <row r="512" spans="1:7" x14ac:dyDescent="0.3">
@@ -14400,7 +14482,7 @@
         <v>384</v>
       </c>
       <c r="B512" s="3" t="s">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="C512" s="4">
         <f>850+400</f>
@@ -14412,10 +14494,10 @@
       </c>
       <c r="E512" s="4"/>
       <c r="F512" s="3" t="s">
-        <v>860</v>
+        <v>1093</v>
       </c>
       <c r="G512" s="3" t="s">
-        <v>782</v>
+        <v>783</v>
       </c>
     </row>
     <row r="513" spans="1:7" x14ac:dyDescent="0.3">
@@ -14423,7 +14505,7 @@
         <v>384</v>
       </c>
       <c r="B513" s="3" t="s">
-        <v>769</v>
+        <v>770</v>
       </c>
       <c r="C513" s="4">
         <f>1350+400</f>
@@ -14435,10 +14517,10 @@
       </c>
       <c r="E513" s="4"/>
       <c r="F513" s="3" t="s">
-        <v>860</v>
+        <v>1093</v>
       </c>
       <c r="G513" s="3" t="s">
-        <v>782</v>
+        <v>783</v>
       </c>
     </row>
     <row r="514" spans="1:7" x14ac:dyDescent="0.3">
@@ -14446,7 +14528,7 @@
         <v>384</v>
       </c>
       <c r="B514" s="3" t="s">
-        <v>773</v>
+        <v>774</v>
       </c>
       <c r="C514" s="4">
         <f>1550+400</f>
@@ -14458,10 +14540,10 @@
       </c>
       <c r="E514" s="4"/>
       <c r="F514" s="3" t="s">
-        <v>860</v>
+        <v>1093</v>
       </c>
       <c r="G514" s="3" t="s">
-        <v>782</v>
+        <v>783</v>
       </c>
     </row>
     <row r="515" spans="1:7" x14ac:dyDescent="0.3">
@@ -14469,7 +14551,7 @@
         <v>384</v>
       </c>
       <c r="B515" s="3" t="s">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="C515" s="4">
         <f>1000+400</f>
@@ -14481,10 +14563,10 @@
       </c>
       <c r="E515" s="4"/>
       <c r="F515" s="3" t="s">
-        <v>860</v>
+        <v>1093</v>
       </c>
       <c r="G515" s="3" t="s">
-        <v>782</v>
+        <v>783</v>
       </c>
     </row>
     <row r="516" spans="1:7" x14ac:dyDescent="0.3">
@@ -14492,7 +14574,7 @@
         <v>384</v>
       </c>
       <c r="B516" s="3" t="s">
-        <v>771</v>
+        <v>772</v>
       </c>
       <c r="C516" s="4">
         <f>1400+400</f>
@@ -14504,10 +14586,10 @@
       </c>
       <c r="E516" s="4"/>
       <c r="F516" s="3" t="s">
-        <v>860</v>
+        <v>1093</v>
       </c>
       <c r="G516" s="3" t="s">
-        <v>782</v>
+        <v>783</v>
       </c>
     </row>
     <row r="517" spans="1:7" x14ac:dyDescent="0.3">
@@ -14515,7 +14597,7 @@
         <v>384</v>
       </c>
       <c r="B517" s="3" t="s">
-        <v>772</v>
+        <v>773</v>
       </c>
       <c r="C517" s="4">
         <f>2300+400</f>
@@ -14527,10 +14609,10 @@
       </c>
       <c r="E517" s="4"/>
       <c r="F517" s="3" t="s">
-        <v>860</v>
+        <v>1093</v>
       </c>
       <c r="G517" s="3" t="s">
-        <v>782</v>
+        <v>783</v>
       </c>
     </row>
     <row r="518" spans="1:7" x14ac:dyDescent="0.3">
@@ -14538,7 +14620,7 @@
         <v>384</v>
       </c>
       <c r="B518" s="3" t="s">
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="C518" s="4">
         <v>1200</v>
@@ -14548,10 +14630,10 @@
       </c>
       <c r="E518" s="4"/>
       <c r="F518" s="3" t="s">
-        <v>860</v>
+        <v>1093</v>
       </c>
       <c r="G518" s="3" t="s">
-        <v>783</v>
+        <v>784</v>
       </c>
     </row>
     <row r="519" spans="1:7" x14ac:dyDescent="0.3">
@@ -14559,7 +14641,7 @@
         <v>384</v>
       </c>
       <c r="B519" s="3" t="s">
-        <v>775</v>
+        <v>776</v>
       </c>
       <c r="C519" s="4">
         <v>800</v>
@@ -14569,10 +14651,10 @@
       </c>
       <c r="E519" s="4"/>
       <c r="F519" s="3" t="s">
-        <v>860</v>
+        <v>1093</v>
       </c>
       <c r="G519" s="3" t="s">
-        <v>783</v>
+        <v>784</v>
       </c>
     </row>
     <row r="520" spans="1:7" x14ac:dyDescent="0.3">
@@ -14580,7 +14662,7 @@
         <v>384</v>
       </c>
       <c r="B520" s="3" t="s">
-        <v>776</v>
+        <v>777</v>
       </c>
       <c r="C520" s="4">
         <v>2100</v>
@@ -14590,10 +14672,10 @@
       </c>
       <c r="E520" s="4"/>
       <c r="F520" s="3" t="s">
-        <v>860</v>
+        <v>1093</v>
       </c>
       <c r="G520" s="3" t="s">
-        <v>783</v>
+        <v>784</v>
       </c>
     </row>
     <row r="521" spans="1:7" x14ac:dyDescent="0.3">
@@ -14601,7 +14683,7 @@
         <v>384</v>
       </c>
       <c r="B521" s="3" t="s">
-        <v>777</v>
+        <v>778</v>
       </c>
       <c r="C521" s="4">
         <v>1900</v>
@@ -14611,10 +14693,10 @@
       </c>
       <c r="E521" s="4"/>
       <c r="F521" s="3" t="s">
-        <v>860</v>
+        <v>1093</v>
       </c>
       <c r="G521" s="3" t="s">
-        <v>783</v>
+        <v>784</v>
       </c>
     </row>
     <row r="522" spans="1:7" x14ac:dyDescent="0.3">
@@ -14622,7 +14704,7 @@
         <v>384</v>
       </c>
       <c r="B522" s="3" t="s">
-        <v>779</v>
+        <v>780</v>
       </c>
       <c r="C522" s="4">
         <v>1800</v>
@@ -14632,10 +14714,10 @@
       </c>
       <c r="E522" s="4"/>
       <c r="F522" s="3" t="s">
-        <v>860</v>
+        <v>1093</v>
       </c>
       <c r="G522" s="3" t="s">
-        <v>783</v>
+        <v>784</v>
       </c>
     </row>
     <row r="523" spans="1:7" x14ac:dyDescent="0.3">
@@ -14643,7 +14725,7 @@
         <v>384</v>
       </c>
       <c r="B523" s="3" t="s">
-        <v>778</v>
+        <v>779</v>
       </c>
       <c r="C523" s="4">
         <v>1900</v>
@@ -14653,10 +14735,10 @@
       </c>
       <c r="E523" s="4"/>
       <c r="F523" s="3" t="s">
-        <v>860</v>
+        <v>1093</v>
       </c>
       <c r="G523" s="3" t="s">
-        <v>783</v>
+        <v>784</v>
       </c>
     </row>
     <row r="524" spans="1:7" x14ac:dyDescent="0.3">
@@ -14664,7 +14746,7 @@
         <v>384</v>
       </c>
       <c r="B524" s="3" t="s">
-        <v>780</v>
+        <v>781</v>
       </c>
       <c r="C524" s="4">
         <v>1500</v>
@@ -14674,10 +14756,10 @@
       </c>
       <c r="E524" s="4"/>
       <c r="F524" s="3" t="s">
-        <v>860</v>
+        <v>1094</v>
       </c>
       <c r="G524" s="3" t="s">
-        <v>789</v>
+        <v>790</v>
       </c>
     </row>
     <row r="525" spans="1:7" x14ac:dyDescent="0.3">
@@ -14685,7 +14767,7 @@
         <v>384</v>
       </c>
       <c r="B525" s="3" t="s">
-        <v>781</v>
+        <v>782</v>
       </c>
       <c r="C525" s="4">
         <v>1200</v>
@@ -14695,10 +14777,10 @@
       </c>
       <c r="E525" s="4"/>
       <c r="F525" s="3" t="s">
-        <v>860</v>
+        <v>1094</v>
       </c>
       <c r="G525" s="3" t="s">
-        <v>789</v>
+        <v>790</v>
       </c>
     </row>
     <row r="526" spans="1:7" x14ac:dyDescent="0.3">
@@ -14706,7 +14788,7 @@
         <v>384</v>
       </c>
       <c r="B526" s="3" t="s">
-        <v>785</v>
+        <v>786</v>
       </c>
       <c r="C526" s="4">
         <v>1200</v>
@@ -14716,10 +14798,10 @@
       </c>
       <c r="E526" s="4"/>
       <c r="F526" s="3" t="s">
-        <v>860</v>
+        <v>1094</v>
       </c>
       <c r="G526" s="3" t="s">
-        <v>784</v>
+        <v>785</v>
       </c>
     </row>
     <row r="527" spans="1:7" x14ac:dyDescent="0.3">
@@ -14727,7 +14809,7 @@
         <v>384</v>
       </c>
       <c r="B527" s="3" t="s">
-        <v>786</v>
+        <v>787</v>
       </c>
       <c r="C527" s="4">
         <v>1300</v>
@@ -14737,10 +14819,10 @@
       </c>
       <c r="E527" s="4"/>
       <c r="F527" s="3" t="s">
-        <v>860</v>
+        <v>1094</v>
       </c>
       <c r="G527" s="3" t="s">
-        <v>784</v>
+        <v>785</v>
       </c>
     </row>
     <row r="528" spans="1:7" x14ac:dyDescent="0.3">
@@ -14748,7 +14830,7 @@
         <v>384</v>
       </c>
       <c r="B528" s="3" t="s">
-        <v>787</v>
+        <v>788</v>
       </c>
       <c r="C528" s="4">
         <v>1200</v>
@@ -14758,10 +14840,10 @@
       </c>
       <c r="E528" s="4"/>
       <c r="F528" s="3" t="s">
-        <v>860</v>
+        <v>1094</v>
       </c>
       <c r="G528" s="3" t="s">
-        <v>790</v>
+        <v>791</v>
       </c>
     </row>
     <row r="529" spans="1:7" x14ac:dyDescent="0.3">
@@ -14769,7 +14851,7 @@
         <v>384</v>
       </c>
       <c r="B529" s="3" t="s">
-        <v>788</v>
+        <v>789</v>
       </c>
       <c r="C529" s="4">
         <v>1000</v>
@@ -14779,10 +14861,10 @@
       </c>
       <c r="E529" s="4"/>
       <c r="F529" s="3" t="s">
-        <v>860</v>
+        <v>1094</v>
       </c>
       <c r="G529" s="3" t="s">
-        <v>790</v>
+        <v>791</v>
       </c>
     </row>
     <row r="530" spans="1:7" x14ac:dyDescent="0.3">
@@ -14790,7 +14872,7 @@
         <v>384</v>
       </c>
       <c r="B530" s="3" t="s">
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="C530" s="4">
         <v>1100</v>
@@ -14800,16 +14882,16 @@
       </c>
       <c r="E530" s="4"/>
       <c r="F530" s="3" t="s">
-        <v>861</v>
+        <v>1109</v>
       </c>
       <c r="G530" s="3"/>
     </row>
     <row r="531" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A531" s="3" t="s">
+        <v>861</v>
+      </c>
+      <c r="B531" s="3" t="s">
         <v>862</v>
-      </c>
-      <c r="B531" s="3" t="s">
-        <v>863</v>
       </c>
       <c r="C531" s="4">
         <v>1900</v>
@@ -14819,16 +14901,16 @@
       </c>
       <c r="E531" s="4"/>
       <c r="F531" s="3" t="s">
-        <v>861</v>
+        <v>1110</v>
       </c>
       <c r="G531" s="3"/>
     </row>
     <row r="532" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A532" s="3" t="s">
-        <v>862</v>
+        <v>861</v>
       </c>
       <c r="B532" s="3" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
       <c r="C532" s="4">
         <v>2200</v>
@@ -14838,10 +14920,10 @@
       </c>
       <c r="E532" s="4"/>
       <c r="F532" s="3" t="s">
-        <v>861</v>
+        <v>1110</v>
       </c>
       <c r="G532" s="3" t="s">
-        <v>865</v>
+        <v>864</v>
       </c>
     </row>
     <row r="533" spans="1:7" x14ac:dyDescent="0.3">
@@ -14849,7 +14931,7 @@
         <v>384</v>
       </c>
       <c r="B533" s="3" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
       <c r="C533" s="4">
         <v>650</v>
@@ -14859,10 +14941,10 @@
       </c>
       <c r="E533" s="4"/>
       <c r="F533" s="3" t="s">
-        <v>860</v>
+        <v>1095</v>
       </c>
       <c r="G533" s="3" t="s">
-        <v>867</v>
+        <v>866</v>
       </c>
     </row>
     <row r="534" spans="1:7" x14ac:dyDescent="0.3">
@@ -14870,7 +14952,7 @@
         <v>384</v>
       </c>
       <c r="B534" s="3" t="s">
-        <v>868</v>
+        <v>867</v>
       </c>
       <c r="C534" s="4">
         <f>1550+200</f>
@@ -14882,10 +14964,10 @@
       </c>
       <c r="E534" s="4"/>
       <c r="F534" s="3" t="s">
-        <v>860</v>
+        <v>1096</v>
       </c>
       <c r="G534" s="3" t="s">
-        <v>870</v>
+        <v>869</v>
       </c>
     </row>
     <row r="535" spans="1:7" x14ac:dyDescent="0.3">
@@ -14893,7 +14975,7 @@
         <v>384</v>
       </c>
       <c r="B535" s="3" t="s">
-        <v>869</v>
+        <v>868</v>
       </c>
       <c r="C535" s="4">
         <v>1550</v>
@@ -14903,10 +14985,10 @@
       </c>
       <c r="E535" s="4"/>
       <c r="F535" s="3" t="s">
-        <v>860</v>
+        <v>1096</v>
       </c>
       <c r="G535" s="3" t="s">
-        <v>870</v>
+        <v>869</v>
       </c>
     </row>
     <row r="536" spans="1:7" x14ac:dyDescent="0.3">
@@ -14914,7 +14996,7 @@
         <v>384</v>
       </c>
       <c r="B536" s="3" t="s">
-        <v>871</v>
+        <v>870</v>
       </c>
       <c r="C536" s="4">
         <v>2500</v>
@@ -14924,10 +15006,10 @@
       </c>
       <c r="E536" s="4"/>
       <c r="F536" s="3" t="s">
-        <v>860</v>
+        <v>1097</v>
       </c>
       <c r="G536" s="3" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
     </row>
     <row r="537" spans="1:7" x14ac:dyDescent="0.3">
@@ -14935,7 +15017,7 @@
         <v>384</v>
       </c>
       <c r="B537" s="3" t="s">
-        <v>873</v>
+        <v>872</v>
       </c>
       <c r="C537" s="4">
         <v>2300</v>
@@ -14945,10 +15027,10 @@
       </c>
       <c r="E537" s="4"/>
       <c r="F537" s="3" t="s">
-        <v>860</v>
+        <v>1098</v>
       </c>
       <c r="G537" s="3" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
     </row>
     <row r="538" spans="1:7" x14ac:dyDescent="0.3">
@@ -14956,7 +15038,7 @@
         <v>384</v>
       </c>
       <c r="B538" s="3" t="s">
-        <v>874</v>
+        <v>873</v>
       </c>
       <c r="C538" s="4">
         <v>1100</v>
@@ -14966,10 +15048,10 @@
       </c>
       <c r="E538" s="4"/>
       <c r="F538" s="3" t="s">
-        <v>860</v>
+        <v>1099</v>
       </c>
       <c r="G538" s="3" t="s">
-        <v>875</v>
+        <v>874</v>
       </c>
     </row>
     <row r="539" spans="1:7" x14ac:dyDescent="0.3">
@@ -14977,7 +15059,7 @@
         <v>384</v>
       </c>
       <c r="B539" s="3" t="s">
-        <v>876</v>
+        <v>875</v>
       </c>
       <c r="C539" s="4">
         <v>1000</v>
@@ -14987,10 +15069,10 @@
       </c>
       <c r="E539" s="4"/>
       <c r="F539" s="3" t="s">
-        <v>860</v>
+        <v>1099</v>
       </c>
       <c r="G539" s="3" t="s">
-        <v>875</v>
+        <v>874</v>
       </c>
     </row>
     <row r="540" spans="1:7" x14ac:dyDescent="0.3">
@@ -14998,7 +15080,7 @@
         <v>384</v>
       </c>
       <c r="B540" s="3" t="s">
-        <v>877</v>
+        <v>876</v>
       </c>
       <c r="C540" s="4">
         <v>900</v>
@@ -15008,10 +15090,10 @@
       </c>
       <c r="E540" s="4"/>
       <c r="F540" s="3" t="s">
-        <v>860</v>
+        <v>1099</v>
       </c>
       <c r="G540" s="3" t="s">
-        <v>875</v>
+        <v>874</v>
       </c>
     </row>
     <row r="541" spans="1:7" x14ac:dyDescent="0.3">
@@ -15019,7 +15101,7 @@
         <v>384</v>
       </c>
       <c r="B541" s="3" t="s">
-        <v>878</v>
+        <v>877</v>
       </c>
       <c r="C541" s="4">
         <v>1400</v>
@@ -15029,18 +15111,18 @@
       </c>
       <c r="E541" s="4"/>
       <c r="F541" s="3" t="s">
-        <v>860</v>
+        <v>1099</v>
       </c>
       <c r="G541" s="3" t="s">
-        <v>875</v>
+        <v>874</v>
       </c>
     </row>
     <row r="542" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A542" s="3" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
       <c r="B542" s="3" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
       <c r="C542" s="4">
         <v>1700</v>
@@ -15050,16 +15132,16 @@
       </c>
       <c r="E542" s="4"/>
       <c r="F542" s="3" t="s">
-        <v>860</v>
+        <v>1100</v>
       </c>
       <c r="G542" s="3"/>
     </row>
     <row r="543" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A543" s="3" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
       <c r="B543" s="3" t="s">
-        <v>880</v>
+        <v>879</v>
       </c>
       <c r="C543" s="4">
         <v>1700</v>
@@ -15069,16 +15151,16 @@
       </c>
       <c r="E543" s="4"/>
       <c r="F543" s="3" t="s">
-        <v>860</v>
+        <v>1101</v>
       </c>
       <c r="G543" s="3"/>
     </row>
     <row r="544" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A544" s="3" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
       <c r="B544" s="3" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
       <c r="C544" s="4">
         <v>1000</v>
@@ -15088,16 +15170,16 @@
       </c>
       <c r="E544" s="4"/>
       <c r="F544" s="3" t="s">
-        <v>860</v>
+        <v>1101</v>
       </c>
       <c r="G544" s="3"/>
     </row>
     <row r="545" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A545" s="3" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
       <c r="B545" s="3" t="s">
-        <v>882</v>
+        <v>881</v>
       </c>
       <c r="C545" s="4">
         <v>1300</v>
@@ -15107,16 +15189,16 @@
       </c>
       <c r="E545" s="4"/>
       <c r="F545" s="3" t="s">
-        <v>860</v>
+        <v>1101</v>
       </c>
       <c r="G545" s="3"/>
     </row>
     <row r="546" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A546" s="3" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
       <c r="B546" s="3" t="s">
-        <v>883</v>
+        <v>882</v>
       </c>
       <c r="C546" s="4">
         <v>1400</v>
@@ -15126,16 +15208,16 @@
       </c>
       <c r="E546" s="4"/>
       <c r="F546" s="3" t="s">
-        <v>860</v>
+        <v>1101</v>
       </c>
       <c r="G546" s="3"/>
     </row>
     <row r="547" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A547" s="3" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
       <c r="B547" s="3" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
       <c r="C547" s="4">
         <v>1800</v>
@@ -15151,10 +15233,10 @@
     </row>
     <row r="548" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A548" s="3" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
       <c r="B548" s="3" t="s">
-        <v>885</v>
+        <v>884</v>
       </c>
       <c r="C548" s="4">
         <v>1300</v>
@@ -15170,10 +15252,10 @@
     </row>
     <row r="549" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A549" s="3" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
       <c r="B549" s="3" t="s">
-        <v>886</v>
+        <v>885</v>
       </c>
       <c r="C549" s="4">
         <v>700</v>
@@ -15189,10 +15271,10 @@
     </row>
     <row r="550" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A550" s="3" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
       <c r="B550" s="3" t="s">
-        <v>887</v>
+        <v>886</v>
       </c>
       <c r="C550" s="4">
         <v>2700</v>
@@ -15208,10 +15290,10 @@
     </row>
     <row r="551" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A551" s="3" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
       <c r="B551" s="3" t="s">
-        <v>888</v>
+        <v>887</v>
       </c>
       <c r="C551" s="4">
         <v>2500</v>
@@ -15227,10 +15309,10 @@
     </row>
     <row r="552" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A552" s="3" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
       <c r="B552" s="3" t="s">
-        <v>889</v>
+        <v>888</v>
       </c>
       <c r="C552" s="4">
         <v>2500</v>
@@ -15246,10 +15328,10 @@
     </row>
     <row r="553" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A553" s="3" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
       <c r="B553" s="3" t="s">
-        <v>890</v>
+        <v>889</v>
       </c>
       <c r="C553" s="4">
         <v>1400</v>
@@ -15265,10 +15347,10 @@
     </row>
     <row r="554" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A554" s="3" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
       <c r="B554" s="3" t="s">
-        <v>891</v>
+        <v>890</v>
       </c>
       <c r="C554" s="4">
         <v>800</v>
@@ -15284,10 +15366,10 @@
     </row>
     <row r="555" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A555" s="3" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
       <c r="B555" s="3" t="s">
-        <v>892</v>
+        <v>891</v>
       </c>
       <c r="C555" s="4">
         <v>2000</v>
@@ -15303,10 +15385,10 @@
     </row>
     <row r="556" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A556" s="3" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
       <c r="B556" s="3" t="s">
-        <v>893</v>
+        <v>892</v>
       </c>
       <c r="C556" s="4">
         <v>1200</v>
@@ -15322,10 +15404,10 @@
     </row>
     <row r="557" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A557" s="3" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
       <c r="B557" s="3" t="s">
-        <v>894</v>
+        <v>893</v>
       </c>
       <c r="C557" s="4">
         <v>5600</v>
@@ -15341,10 +15423,10 @@
     </row>
     <row r="558" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A558" s="3" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
       <c r="B558" s="3" t="s">
-        <v>895</v>
+        <v>894</v>
       </c>
       <c r="C558" s="4">
         <v>8000</v>
@@ -15360,10 +15442,10 @@
     </row>
     <row r="559" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A559" s="3" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
       <c r="B559" s="3" t="s">
-        <v>896</v>
+        <v>895</v>
       </c>
       <c r="C559" s="4">
         <v>1700</v>
@@ -15379,10 +15461,10 @@
     </row>
     <row r="560" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A560" s="3" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
       <c r="B560" s="3" t="s">
-        <v>897</v>
+        <v>896</v>
       </c>
       <c r="C560" s="4">
         <v>1400</v>
@@ -15398,10 +15480,10 @@
     </row>
     <row r="561" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A561" s="3" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
       <c r="B561" s="3" t="s">
-        <v>898</v>
+        <v>897</v>
       </c>
       <c r="C561" s="4">
         <v>1200</v>
@@ -15417,10 +15499,10 @@
     </row>
     <row r="562" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A562" s="3" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
       <c r="B562" s="3" t="s">
-        <v>899</v>
+        <v>898</v>
       </c>
       <c r="C562" s="4">
         <v>2200</v>
@@ -15436,10 +15518,10 @@
     </row>
     <row r="563" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A563" s="3" t="s">
-        <v>862</v>
+        <v>861</v>
       </c>
       <c r="B563" s="3" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
       <c r="C563" s="4">
         <v>1200</v>
@@ -15449,16 +15531,16 @@
       </c>
       <c r="E563" s="4"/>
       <c r="F563" s="3" t="s">
-        <v>860</v>
+        <v>1102</v>
       </c>
       <c r="G563" s="3"/>
     </row>
     <row r="564" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A564" s="3" t="s">
-        <v>862</v>
+        <v>861</v>
       </c>
       <c r="B564" s="3" t="s">
-        <v>902</v>
+        <v>901</v>
       </c>
       <c r="C564" s="4">
         <v>650</v>
@@ -15468,16 +15550,16 @@
       </c>
       <c r="E564" s="4"/>
       <c r="F564" s="3" t="s">
-        <v>860</v>
+        <v>1103</v>
       </c>
       <c r="G564" s="3"/>
     </row>
     <row r="565" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A565" s="3" t="s">
-        <v>862</v>
+        <v>861</v>
       </c>
       <c r="B565" s="7" t="s">
-        <v>903</v>
+        <v>902</v>
       </c>
       <c r="C565" s="4">
         <v>450</v>
@@ -15487,16 +15569,16 @@
       </c>
       <c r="E565" s="4"/>
       <c r="F565" s="3" t="s">
-        <v>860</v>
+        <v>1103</v>
       </c>
       <c r="G565" s="3"/>
     </row>
     <row r="566" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A566" s="3" t="s">
-        <v>862</v>
+        <v>861</v>
       </c>
       <c r="B566" s="7" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="C566" s="4">
         <v>750</v>
@@ -15506,16 +15588,16 @@
       </c>
       <c r="E566" s="4"/>
       <c r="F566" s="3" t="s">
-        <v>860</v>
+        <v>1104</v>
       </c>
       <c r="G566" s="3"/>
     </row>
     <row r="567" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A567" s="3" t="s">
-        <v>862</v>
+        <v>861</v>
       </c>
       <c r="B567" s="7" t="s">
-        <v>909</v>
+        <v>908</v>
       </c>
       <c r="C567" s="4">
         <v>850</v>
@@ -15525,16 +15607,16 @@
       </c>
       <c r="E567" s="4"/>
       <c r="F567" s="3" t="s">
-        <v>860</v>
+        <v>1104</v>
       </c>
       <c r="G567" s="3"/>
     </row>
     <row r="568" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A568" s="3" t="s">
-        <v>862</v>
+        <v>861</v>
       </c>
       <c r="B568" s="7" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
       <c r="C568" s="4">
         <v>1050</v>
@@ -15544,16 +15626,16 @@
       </c>
       <c r="E568" s="4"/>
       <c r="F568" s="3" t="s">
-        <v>860</v>
+        <v>1104</v>
       </c>
       <c r="G568" s="3"/>
     </row>
     <row r="569" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A569" s="3" t="s">
-        <v>862</v>
+        <v>861</v>
       </c>
       <c r="B569" s="7" t="s">
-        <v>911</v>
+        <v>910</v>
       </c>
       <c r="C569" s="4">
         <v>1150</v>
@@ -15563,16 +15645,16 @@
       </c>
       <c r="E569" s="4"/>
       <c r="F569" s="3" t="s">
-        <v>860</v>
+        <v>1104</v>
       </c>
       <c r="G569" s="3"/>
     </row>
     <row r="570" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A570" s="3" t="s">
-        <v>862</v>
+        <v>861</v>
       </c>
       <c r="B570" s="7" t="s">
-        <v>912</v>
+        <v>911</v>
       </c>
       <c r="C570" s="4">
         <v>1000</v>
@@ -15582,16 +15664,16 @@
       </c>
       <c r="E570" s="4"/>
       <c r="F570" s="3" t="s">
-        <v>860</v>
+        <v>1106</v>
       </c>
       <c r="G570" s="3"/>
     </row>
     <row r="571" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A571" s="3" t="s">
-        <v>862</v>
+        <v>861</v>
       </c>
       <c r="B571" s="7" t="s">
-        <v>913</v>
+        <v>912</v>
       </c>
       <c r="C571" s="4">
         <v>900</v>
@@ -15601,16 +15683,16 @@
       </c>
       <c r="E571" s="4"/>
       <c r="F571" s="3" t="s">
-        <v>860</v>
+        <v>1106</v>
       </c>
       <c r="G571" s="3"/>
     </row>
     <row r="572" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A572" s="3" t="s">
-        <v>862</v>
+        <v>861</v>
       </c>
       <c r="B572" s="3" t="s">
-        <v>904</v>
+        <v>903</v>
       </c>
       <c r="C572" s="4">
         <v>800</v>
@@ -15620,16 +15702,16 @@
       </c>
       <c r="E572" s="4"/>
       <c r="F572" s="3" t="s">
-        <v>860</v>
+        <v>1105</v>
       </c>
       <c r="G572" s="3"/>
     </row>
     <row r="573" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A573" s="3" t="s">
-        <v>862</v>
+        <v>861</v>
       </c>
       <c r="B573" s="3" t="s">
-        <v>905</v>
+        <v>904</v>
       </c>
       <c r="C573" s="4">
         <v>1600</v>
@@ -15639,16 +15721,16 @@
       </c>
       <c r="E573" s="4"/>
       <c r="F573" s="3" t="s">
-        <v>860</v>
+        <v>1105</v>
       </c>
       <c r="G573" s="3"/>
     </row>
     <row r="574" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A574" s="3" t="s">
-        <v>862</v>
+        <v>861</v>
       </c>
       <c r="B574" s="3" t="s">
-        <v>906</v>
+        <v>905</v>
       </c>
       <c r="C574" s="4">
         <v>500</v>
@@ -15658,16 +15740,16 @@
       </c>
       <c r="E574" s="4"/>
       <c r="F574" s="3" t="s">
-        <v>860</v>
+        <v>1107</v>
       </c>
       <c r="G574" s="3"/>
     </row>
     <row r="575" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A575" s="3" t="s">
-        <v>862</v>
+        <v>861</v>
       </c>
       <c r="B575" s="3" t="s">
-        <v>907</v>
+        <v>906</v>
       </c>
       <c r="C575" s="4">
         <v>800</v>
@@ -15677,16 +15759,16 @@
       </c>
       <c r="E575" s="4"/>
       <c r="F575" s="3" t="s">
-        <v>860</v>
+        <v>1108</v>
       </c>
       <c r="G575" s="3"/>
     </row>
     <row r="576" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A576" s="3" t="s">
-        <v>862</v>
+        <v>861</v>
       </c>
       <c r="B576" s="3" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
       <c r="C576" s="4">
         <v>1600</v>
@@ -15696,16 +15778,16 @@
       </c>
       <c r="E576" s="4"/>
       <c r="F576" s="3" t="s">
-        <v>860</v>
+        <v>1102</v>
       </c>
       <c r="G576" s="3"/>
     </row>
     <row r="577" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A577" s="3" t="s">
-        <v>862</v>
+        <v>861</v>
       </c>
       <c r="B577" s="3" t="s">
-        <v>915</v>
+        <v>914</v>
       </c>
       <c r="C577" s="4">
         <v>850</v>
@@ -15715,16 +15797,16 @@
       </c>
       <c r="E577" s="4"/>
       <c r="F577" s="3" t="s">
-        <v>860</v>
+        <v>1103</v>
       </c>
       <c r="G577" s="3"/>
     </row>
     <row r="578" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A578" s="3" t="s">
-        <v>862</v>
+        <v>861</v>
       </c>
       <c r="B578" s="7" t="s">
-        <v>916</v>
+        <v>915</v>
       </c>
       <c r="C578" s="4">
         <v>650</v>
@@ -15734,16 +15816,16 @@
       </c>
       <c r="E578" s="4"/>
       <c r="F578" s="3" t="s">
-        <v>860</v>
+        <v>1103</v>
       </c>
       <c r="G578" s="3"/>
     </row>
     <row r="579" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A579" s="3" t="s">
-        <v>862</v>
+        <v>861</v>
       </c>
       <c r="B579" s="7" t="s">
-        <v>917</v>
+        <v>916</v>
       </c>
       <c r="C579" s="4">
         <v>1150</v>
@@ -15753,16 +15835,16 @@
       </c>
       <c r="E579" s="4"/>
       <c r="F579" s="3" t="s">
-        <v>860</v>
+        <v>1104</v>
       </c>
       <c r="G579" s="3"/>
     </row>
     <row r="580" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A580" s="3" t="s">
-        <v>862</v>
+        <v>861</v>
       </c>
       <c r="B580" s="7" t="s">
-        <v>918</v>
+        <v>917</v>
       </c>
       <c r="C580" s="4">
         <v>1250</v>
@@ -15772,16 +15854,16 @@
       </c>
       <c r="E580" s="4"/>
       <c r="F580" s="3" t="s">
-        <v>860</v>
+        <v>1104</v>
       </c>
       <c r="G580" s="3"/>
     </row>
     <row r="581" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A581" s="3" t="s">
-        <v>862</v>
+        <v>861</v>
       </c>
       <c r="B581" s="7" t="s">
-        <v>919</v>
+        <v>918</v>
       </c>
       <c r="C581" s="4">
         <v>1450</v>
@@ -15791,16 +15873,16 @@
       </c>
       <c r="E581" s="4"/>
       <c r="F581" s="3" t="s">
-        <v>860</v>
+        <v>1104</v>
       </c>
       <c r="G581" s="3"/>
     </row>
     <row r="582" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A582" s="3" t="s">
-        <v>862</v>
+        <v>861</v>
       </c>
       <c r="B582" s="7" t="s">
-        <v>920</v>
+        <v>919</v>
       </c>
       <c r="C582" s="4">
         <v>1550</v>
@@ -15810,16 +15892,16 @@
       </c>
       <c r="E582" s="4"/>
       <c r="F582" s="3" t="s">
-        <v>860</v>
+        <v>1104</v>
       </c>
       <c r="G582" s="3"/>
     </row>
     <row r="583" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A583" s="3" t="s">
-        <v>862</v>
+        <v>861</v>
       </c>
       <c r="B583" s="7" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="C583" s="4">
         <v>1400</v>
@@ -15829,16 +15911,16 @@
       </c>
       <c r="E583" s="4"/>
       <c r="F583" s="3" t="s">
-        <v>860</v>
+        <v>1106</v>
       </c>
       <c r="G583" s="3"/>
     </row>
     <row r="584" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A584" s="3" t="s">
-        <v>862</v>
+        <v>861</v>
       </c>
       <c r="B584" s="7" t="s">
-        <v>922</v>
+        <v>921</v>
       </c>
       <c r="C584" s="4">
         <v>1300</v>
@@ -15848,16 +15930,16 @@
       </c>
       <c r="E584" s="4"/>
       <c r="F584" s="3" t="s">
-        <v>860</v>
+        <v>1106</v>
       </c>
       <c r="G584" s="3"/>
     </row>
     <row r="585" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A585" s="3" t="s">
-        <v>862</v>
+        <v>861</v>
       </c>
       <c r="B585" s="3" t="s">
-        <v>923</v>
+        <v>922</v>
       </c>
       <c r="C585" s="4">
         <v>1200</v>
@@ -15867,16 +15949,16 @@
       </c>
       <c r="E585" s="4"/>
       <c r="F585" s="3" t="s">
-        <v>860</v>
+        <v>1105</v>
       </c>
       <c r="G585" s="3"/>
     </row>
     <row r="586" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A586" s="3" t="s">
-        <v>862</v>
+        <v>861</v>
       </c>
       <c r="B586" s="3" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="C586" s="4">
         <v>2000</v>
@@ -15886,16 +15968,16 @@
       </c>
       <c r="E586" s="4"/>
       <c r="F586" s="3" t="s">
-        <v>860</v>
+        <v>1105</v>
       </c>
       <c r="G586" s="3"/>
     </row>
     <row r="587" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A587" s="3" t="s">
-        <v>862</v>
+        <v>861</v>
       </c>
       <c r="B587" s="3" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
       <c r="C587" s="4">
         <v>1000</v>
@@ -15905,16 +15987,16 @@
       </c>
       <c r="E587" s="4"/>
       <c r="F587" s="3" t="s">
-        <v>971</v>
+        <v>1111</v>
       </c>
       <c r="G587" s="3"/>
     </row>
     <row r="588" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A588" s="3" t="s">
-        <v>862</v>
+        <v>861</v>
       </c>
       <c r="B588" s="3" t="s">
-        <v>902</v>
+        <v>901</v>
       </c>
       <c r="C588" s="4">
         <v>600</v>
@@ -15924,16 +16006,16 @@
       </c>
       <c r="E588" s="4"/>
       <c r="F588" s="3" t="s">
-        <v>971</v>
+        <v>1112</v>
       </c>
       <c r="G588" s="3"/>
     </row>
     <row r="589" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A589" s="3" t="s">
-        <v>862</v>
+        <v>861</v>
       </c>
       <c r="B589" s="7" t="s">
-        <v>903</v>
+        <v>902</v>
       </c>
       <c r="C589" s="4">
         <v>450</v>
@@ -15943,16 +16025,16 @@
       </c>
       <c r="E589" s="4"/>
       <c r="F589" s="3" t="s">
-        <v>971</v>
+        <v>1112</v>
       </c>
       <c r="G589" s="3"/>
     </row>
     <row r="590" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A590" s="3" t="s">
-        <v>862</v>
+        <v>861</v>
       </c>
       <c r="B590" s="3" t="s">
-        <v>972</v>
+        <v>970</v>
       </c>
       <c r="C590" s="4">
         <v>900</v>
@@ -15962,16 +16044,16 @@
       </c>
       <c r="E590" s="4"/>
       <c r="F590" s="3" t="s">
-        <v>971</v>
+        <v>1113</v>
       </c>
       <c r="G590" s="3"/>
     </row>
     <row r="591" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A591" s="3" t="s">
-        <v>862</v>
+        <v>861</v>
       </c>
       <c r="B591" s="3" t="s">
-        <v>973</v>
+        <v>971</v>
       </c>
       <c r="C591" s="4">
         <v>800</v>
@@ -15981,16 +16063,16 @@
       </c>
       <c r="E591" s="4"/>
       <c r="F591" s="3" t="s">
-        <v>971</v>
+        <v>1113</v>
       </c>
       <c r="G591" s="3"/>
     </row>
     <row r="592" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A592" s="3" t="s">
-        <v>862</v>
+        <v>861</v>
       </c>
       <c r="B592" s="3" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
       <c r="C592" s="4">
         <v>1400</v>
@@ -16000,16 +16082,16 @@
       </c>
       <c r="E592" s="4"/>
       <c r="F592" s="3" t="s">
-        <v>971</v>
+        <v>1111</v>
       </c>
       <c r="G592" s="3"/>
     </row>
     <row r="593" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A593" s="3" t="s">
-        <v>862</v>
+        <v>861</v>
       </c>
       <c r="B593" s="3" t="s">
-        <v>915</v>
+        <v>914</v>
       </c>
       <c r="C593" s="4">
         <v>800</v>
@@ -16019,16 +16101,16 @@
       </c>
       <c r="E593" s="4"/>
       <c r="F593" s="3" t="s">
-        <v>971</v>
+        <v>1112</v>
       </c>
       <c r="G593" s="3"/>
     </row>
     <row r="594" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A594" s="3" t="s">
-        <v>862</v>
+        <v>861</v>
       </c>
       <c r="B594" s="7" t="s">
-        <v>974</v>
+        <v>972</v>
       </c>
       <c r="C594" s="4">
         <v>650</v>
@@ -16038,16 +16120,16 @@
       </c>
       <c r="E594" s="4"/>
       <c r="F594" s="3" t="s">
-        <v>971</v>
+        <v>1112</v>
       </c>
       <c r="G594" s="3"/>
     </row>
     <row r="595" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A595" s="3" t="s">
-        <v>862</v>
+        <v>861</v>
       </c>
       <c r="B595" s="3" t="s">
-        <v>975</v>
+        <v>973</v>
       </c>
       <c r="C595" s="4">
         <v>1200</v>
@@ -16057,16 +16139,16 @@
       </c>
       <c r="E595" s="4"/>
       <c r="F595" s="3" t="s">
-        <v>971</v>
+        <v>1113</v>
       </c>
       <c r="G595" s="3"/>
     </row>
     <row r="596" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A596" s="3" t="s">
-        <v>862</v>
+        <v>861</v>
       </c>
       <c r="B596" s="3" t="s">
-        <v>976</v>
+        <v>974</v>
       </c>
       <c r="C596" s="4">
         <v>1100</v>
@@ -16076,7 +16158,7 @@
       </c>
       <c r="E596" s="4"/>
       <c r="F596" s="3" t="s">
-        <v>971</v>
+        <v>1113</v>
       </c>
       <c r="G596" s="3"/>
     </row>
@@ -16085,7 +16167,7 @@
         <v>384</v>
       </c>
       <c r="B597" s="3" t="s">
-        <v>977</v>
+        <v>975</v>
       </c>
       <c r="C597" s="4">
         <v>750</v>
@@ -16095,7 +16177,7 @@
       </c>
       <c r="E597" s="4"/>
       <c r="F597" s="3" t="s">
-        <v>994</v>
+        <v>1115</v>
       </c>
       <c r="G597" s="3"/>
     </row>
@@ -16104,7 +16186,7 @@
         <v>384</v>
       </c>
       <c r="B598" s="3" t="s">
-        <v>978</v>
+        <v>976</v>
       </c>
       <c r="C598" s="4">
         <v>1150</v>
@@ -16114,7 +16196,7 @@
       </c>
       <c r="E598" s="4"/>
       <c r="F598" s="3" t="s">
-        <v>994</v>
+        <v>1115</v>
       </c>
       <c r="G598" s="3"/>
     </row>
@@ -16123,7 +16205,7 @@
         <v>384</v>
       </c>
       <c r="B599" s="3" t="s">
-        <v>979</v>
+        <v>977</v>
       </c>
       <c r="C599" s="4">
         <v>850</v>
@@ -16133,7 +16215,7 @@
       </c>
       <c r="E599" s="4"/>
       <c r="F599" s="3" t="s">
-        <v>994</v>
+        <v>1115</v>
       </c>
       <c r="G599" s="3"/>
     </row>
@@ -16142,7 +16224,7 @@
         <v>384</v>
       </c>
       <c r="B600" s="3" t="s">
-        <v>980</v>
+        <v>978</v>
       </c>
       <c r="C600" s="4">
         <v>1250</v>
@@ -16152,7 +16234,7 @@
       </c>
       <c r="E600" s="4"/>
       <c r="F600" s="3" t="s">
-        <v>994</v>
+        <v>1115</v>
       </c>
       <c r="G600" s="3"/>
     </row>
@@ -16161,7 +16243,7 @@
         <v>384</v>
       </c>
       <c r="B601" s="3" t="s">
-        <v>981</v>
+        <v>979</v>
       </c>
       <c r="C601" s="4">
         <v>1350</v>
@@ -16171,7 +16253,7 @@
       </c>
       <c r="E601" s="4"/>
       <c r="F601" s="3" t="s">
-        <v>994</v>
+        <v>1115</v>
       </c>
       <c r="G601" s="3"/>
     </row>
@@ -16180,7 +16262,7 @@
         <v>384</v>
       </c>
       <c r="B602" s="3" t="s">
-        <v>982</v>
+        <v>980</v>
       </c>
       <c r="C602" s="4">
         <v>1750</v>
@@ -16190,7 +16272,7 @@
       </c>
       <c r="E602" s="4"/>
       <c r="F602" s="3" t="s">
-        <v>994</v>
+        <v>1115</v>
       </c>
       <c r="G602" s="3"/>
     </row>
@@ -16199,7 +16281,7 @@
         <v>384</v>
       </c>
       <c r="B603" s="3" t="s">
-        <v>983</v>
+        <v>981</v>
       </c>
       <c r="C603" s="4">
         <v>1550</v>
@@ -16209,7 +16291,7 @@
       </c>
       <c r="E603" s="4"/>
       <c r="F603" s="3" t="s">
-        <v>994</v>
+        <v>1115</v>
       </c>
       <c r="G603" s="3"/>
     </row>
@@ -16218,7 +16300,7 @@
         <v>384</v>
       </c>
       <c r="B604" s="3" t="s">
-        <v>984</v>
+        <v>982</v>
       </c>
       <c r="C604" s="4">
         <v>1950</v>
@@ -16228,7 +16310,7 @@
       </c>
       <c r="E604" s="4"/>
       <c r="F604" s="3" t="s">
-        <v>994</v>
+        <v>1115</v>
       </c>
       <c r="G604" s="3"/>
     </row>
@@ -16237,7 +16319,7 @@
         <v>384</v>
       </c>
       <c r="B605" s="3" t="s">
-        <v>985</v>
+        <v>983</v>
       </c>
       <c r="C605" s="4">
         <v>2400</v>
@@ -16247,7 +16329,7 @@
       </c>
       <c r="E605" s="4"/>
       <c r="F605" s="3" t="s">
-        <v>994</v>
+        <v>1115</v>
       </c>
       <c r="G605" s="3"/>
     </row>
@@ -16256,7 +16338,7 @@
         <v>384</v>
       </c>
       <c r="B606" s="3" t="s">
-        <v>986</v>
+        <v>984</v>
       </c>
       <c r="C606" s="4">
         <v>2400</v>
@@ -16266,7 +16348,7 @@
       </c>
       <c r="E606" s="4"/>
       <c r="F606" s="3" t="s">
-        <v>994</v>
+        <v>1115</v>
       </c>
       <c r="G606" s="3"/>
     </row>
@@ -16275,7 +16357,7 @@
         <v>384</v>
       </c>
       <c r="B607" s="3" t="s">
-        <v>987</v>
+        <v>985</v>
       </c>
       <c r="C607" s="4">
         <v>3110</v>
@@ -16285,7 +16367,7 @@
       </c>
       <c r="E607" s="4"/>
       <c r="F607" s="3" t="s">
-        <v>994</v>
+        <v>1115</v>
       </c>
       <c r="G607" s="3"/>
     </row>
@@ -16294,7 +16376,7 @@
         <v>384</v>
       </c>
       <c r="B608" s="3" t="s">
-        <v>988</v>
+        <v>986</v>
       </c>
       <c r="C608" s="4">
         <v>2200</v>
@@ -16304,7 +16386,7 @@
       </c>
       <c r="E608" s="4"/>
       <c r="F608" s="3" t="s">
-        <v>994</v>
+        <v>1115</v>
       </c>
       <c r="G608" s="3"/>
     </row>
@@ -16313,7 +16395,7 @@
         <v>384</v>
       </c>
       <c r="B609" s="3" t="s">
-        <v>989</v>
+        <v>987</v>
       </c>
       <c r="C609" s="4">
         <v>1000</v>
@@ -16323,7 +16405,7 @@
       </c>
       <c r="E609" s="4"/>
       <c r="F609" s="3" t="s">
-        <v>994</v>
+        <v>1115</v>
       </c>
     </row>
     <row r="610" spans="1:6" x14ac:dyDescent="0.3">
@@ -16331,7 +16413,7 @@
         <v>384</v>
       </c>
       <c r="B610" s="3" t="s">
-        <v>990</v>
+        <v>988</v>
       </c>
       <c r="C610" s="4">
         <v>1400</v>
@@ -16341,7 +16423,7 @@
       </c>
       <c r="E610" s="4"/>
       <c r="F610" s="3" t="s">
-        <v>994</v>
+        <v>1115</v>
       </c>
     </row>
     <row r="611" spans="1:6" x14ac:dyDescent="0.3">
@@ -16349,7 +16431,7 @@
         <v>384</v>
       </c>
       <c r="B611" s="3" t="s">
-        <v>991</v>
+        <v>989</v>
       </c>
       <c r="C611" s="4">
         <v>1300</v>
@@ -16359,7 +16441,7 @@
       </c>
       <c r="E611" s="4"/>
       <c r="F611" s="3" t="s">
-        <v>994</v>
+        <v>1115</v>
       </c>
     </row>
     <row r="612" spans="1:6" x14ac:dyDescent="0.3">
@@ -16367,7 +16449,7 @@
         <v>384</v>
       </c>
       <c r="B612" s="3" t="s">
-        <v>992</v>
+        <v>990</v>
       </c>
       <c r="C612" s="4">
         <v>2200</v>
@@ -16377,7 +16459,7 @@
       </c>
       <c r="E612" s="4"/>
       <c r="F612" s="3" t="s">
-        <v>994</v>
+        <v>1115</v>
       </c>
     </row>
     <row r="613" spans="1:6" x14ac:dyDescent="0.3">
@@ -16385,7 +16467,7 @@
         <v>384</v>
       </c>
       <c r="B613" s="3" t="s">
-        <v>993</v>
+        <v>991</v>
       </c>
       <c r="C613" s="4">
         <v>1900</v>
@@ -16395,7 +16477,7 @@
       </c>
       <c r="E613" s="4"/>
       <c r="F613" s="3" t="s">
-        <v>994</v>
+        <v>1115</v>
       </c>
     </row>
     <row r="614" spans="1:6" x14ac:dyDescent="0.3">
@@ -16403,7 +16485,7 @@
         <v>384</v>
       </c>
       <c r="B614" s="3" t="s">
-        <v>995</v>
+        <v>992</v>
       </c>
       <c r="C614" s="4">
         <v>350</v>
@@ -16413,7 +16495,7 @@
       </c>
       <c r="E614" s="4"/>
       <c r="F614" s="3" t="s">
-        <v>994</v>
+        <v>1115</v>
       </c>
     </row>
     <row r="615" spans="1:6" x14ac:dyDescent="0.3">
@@ -16421,7 +16503,7 @@
         <v>384</v>
       </c>
       <c r="B615" s="3" t="s">
-        <v>996</v>
+        <v>993</v>
       </c>
       <c r="C615" s="4">
         <v>450</v>
@@ -16431,7 +16513,7 @@
       </c>
       <c r="E615" s="4"/>
       <c r="F615" s="3" t="s">
-        <v>994</v>
+        <v>1115</v>
       </c>
     </row>
     <row r="616" spans="1:6" x14ac:dyDescent="0.3">
@@ -16439,7 +16521,7 @@
         <v>384</v>
       </c>
       <c r="B616" s="3" t="s">
-        <v>997</v>
+        <v>994</v>
       </c>
       <c r="C616" s="4">
         <v>450</v>
@@ -16449,7 +16531,7 @@
       </c>
       <c r="E616" s="4"/>
       <c r="F616" s="3" t="s">
-        <v>994</v>
+        <v>1115</v>
       </c>
     </row>
     <row r="617" spans="1:6" x14ac:dyDescent="0.3">
@@ -16457,7 +16539,7 @@
         <v>384</v>
       </c>
       <c r="B617" s="3" t="s">
-        <v>998</v>
+        <v>995</v>
       </c>
       <c r="C617" s="4">
         <v>1000</v>
@@ -16467,7 +16549,7 @@
       </c>
       <c r="E617" s="4"/>
       <c r="F617" s="3" t="s">
-        <v>994</v>
+        <v>1115</v>
       </c>
     </row>
     <row r="618" spans="1:6" x14ac:dyDescent="0.3">
@@ -16475,7 +16557,7 @@
         <v>384</v>
       </c>
       <c r="B618" s="3" t="s">
-        <v>999</v>
+        <v>996</v>
       </c>
       <c r="C618" s="4">
         <v>1200</v>
@@ -16485,7 +16567,7 @@
       </c>
       <c r="E618" s="4"/>
       <c r="F618" s="3" t="s">
-        <v>994</v>
+        <v>1115</v>
       </c>
     </row>
     <row r="619" spans="1:6" x14ac:dyDescent="0.3">
@@ -16493,7 +16575,7 @@
         <v>384</v>
       </c>
       <c r="B619" s="3" t="s">
-        <v>1000</v>
+        <v>997</v>
       </c>
       <c r="C619" s="4">
         <v>1400</v>
@@ -16503,7 +16585,7 @@
       </c>
       <c r="E619" s="4"/>
       <c r="F619" s="3" t="s">
-        <v>994</v>
+        <v>1115</v>
       </c>
     </row>
     <row r="620" spans="1:6" x14ac:dyDescent="0.3">
@@ -16511,7 +16593,7 @@
         <v>384</v>
       </c>
       <c r="B620" s="3" t="s">
-        <v>1001</v>
+        <v>998</v>
       </c>
       <c r="C620" s="4">
         <v>1300</v>
@@ -16521,7 +16603,7 @@
       </c>
       <c r="E620" s="4"/>
       <c r="F620" s="3" t="s">
-        <v>994</v>
+        <v>1115</v>
       </c>
     </row>
     <row r="621" spans="1:6" x14ac:dyDescent="0.3">
@@ -16529,7 +16611,7 @@
         <v>384</v>
       </c>
       <c r="B621" s="3" t="s">
-        <v>1002</v>
+        <v>999</v>
       </c>
       <c r="C621" s="4">
         <v>1200</v>
@@ -16539,7 +16621,7 @@
       </c>
       <c r="E621" s="4"/>
       <c r="F621" s="3" t="s">
-        <v>994</v>
+        <v>1115</v>
       </c>
     </row>
     <row r="622" spans="1:6" x14ac:dyDescent="0.3">
@@ -16547,7 +16629,7 @@
         <v>384</v>
       </c>
       <c r="B622" s="3" t="s">
-        <v>1003</v>
+        <v>1000</v>
       </c>
       <c r="C622" s="4">
         <v>2800</v>
@@ -16557,7 +16639,7 @@
       </c>
       <c r="E622" s="4"/>
       <c r="F622" s="3" t="s">
-        <v>994</v>
+        <v>1115</v>
       </c>
     </row>
     <row r="623" spans="1:6" x14ac:dyDescent="0.3">
@@ -16565,7 +16647,7 @@
         <v>384</v>
       </c>
       <c r="B623" s="3" t="s">
-        <v>1004</v>
+        <v>1001</v>
       </c>
       <c r="C623" s="4">
         <v>2400</v>
@@ -16575,7 +16657,7 @@
       </c>
       <c r="E623" s="4"/>
       <c r="F623" s="3" t="s">
-        <v>994</v>
+        <v>1115</v>
       </c>
     </row>
     <row r="624" spans="1:6" x14ac:dyDescent="0.3">
@@ -16583,7 +16665,7 @@
         <v>384</v>
       </c>
       <c r="B624" s="3" t="s">
-        <v>1005</v>
+        <v>1002</v>
       </c>
       <c r="C624" s="4">
         <v>2050</v>
@@ -16593,7 +16675,7 @@
       </c>
       <c r="E624" s="4"/>
       <c r="F624" s="3" t="s">
-        <v>994</v>
+        <v>1115</v>
       </c>
     </row>
     <row r="625" spans="1:6" x14ac:dyDescent="0.3">
@@ -16601,7 +16683,7 @@
         <v>384</v>
       </c>
       <c r="B625" s="3" t="s">
-        <v>1006</v>
+        <v>1003</v>
       </c>
       <c r="C625" s="4">
         <v>1650</v>
@@ -16611,7 +16693,7 @@
       </c>
       <c r="E625" s="4"/>
       <c r="F625" s="3" t="s">
-        <v>994</v>
+        <v>1115</v>
       </c>
     </row>
     <row r="626" spans="1:6" x14ac:dyDescent="0.3">
@@ -16619,7 +16701,7 @@
         <v>384</v>
       </c>
       <c r="B626" s="3" t="s">
-        <v>1007</v>
+        <v>1004</v>
       </c>
       <c r="C626" s="4">
         <v>3400</v>
@@ -16629,7 +16711,7 @@
       </c>
       <c r="E626" s="4"/>
       <c r="F626" s="3" t="s">
-        <v>994</v>
+        <v>1115</v>
       </c>
     </row>
     <row r="627" spans="1:6" x14ac:dyDescent="0.3">
@@ -16637,7 +16719,7 @@
         <v>384</v>
       </c>
       <c r="B627" s="3" t="s">
-        <v>1008</v>
+        <v>1005</v>
       </c>
       <c r="C627" s="4">
         <v>3050</v>
@@ -16647,7 +16729,7 @@
       </c>
       <c r="E627" s="4"/>
       <c r="F627" s="3" t="s">
-        <v>994</v>
+        <v>1115</v>
       </c>
     </row>
     <row r="628" spans="1:6" x14ac:dyDescent="0.3">
@@ -16655,7 +16737,7 @@
         <v>384</v>
       </c>
       <c r="B628" s="3" t="s">
-        <v>1009</v>
+        <v>1006</v>
       </c>
       <c r="C628" s="4">
         <v>2600</v>
@@ -16665,7 +16747,7 @@
       </c>
       <c r="E628" s="4"/>
       <c r="F628" s="3" t="s">
-        <v>994</v>
+        <v>1115</v>
       </c>
     </row>
     <row r="629" spans="1:6" x14ac:dyDescent="0.3">
@@ -16673,7 +16755,7 @@
         <v>384</v>
       </c>
       <c r="B629" s="3" t="s">
-        <v>1010</v>
+        <v>1007</v>
       </c>
       <c r="C629" s="4">
         <v>2150</v>
@@ -16683,7 +16765,7 @@
       </c>
       <c r="E629" s="4"/>
       <c r="F629" s="3" t="s">
-        <v>994</v>
+        <v>1115</v>
       </c>
     </row>
     <row r="630" spans="1:6" x14ac:dyDescent="0.3">
@@ -16691,7 +16773,7 @@
         <v>384</v>
       </c>
       <c r="B630" s="3" t="s">
-        <v>1011</v>
+        <v>1008</v>
       </c>
       <c r="C630" s="4">
         <v>2350</v>
@@ -16701,7 +16783,7 @@
       </c>
       <c r="E630" s="4"/>
       <c r="F630" s="3" t="s">
-        <v>994</v>
+        <v>1115</v>
       </c>
     </row>
     <row r="631" spans="1:6" x14ac:dyDescent="0.3">
@@ -16709,7 +16791,7 @@
         <v>384</v>
       </c>
       <c r="B631" s="3" t="s">
-        <v>1012</v>
+        <v>1009</v>
       </c>
       <c r="C631" s="4">
         <v>1750</v>
@@ -16719,7 +16801,7 @@
       </c>
       <c r="E631" s="4"/>
       <c r="F631" s="3" t="s">
-        <v>994</v>
+        <v>1115</v>
       </c>
     </row>
     <row r="632" spans="1:6" x14ac:dyDescent="0.3">
@@ -16727,7 +16809,7 @@
         <v>384</v>
       </c>
       <c r="B632" s="3" t="s">
-        <v>1013</v>
+        <v>1010</v>
       </c>
       <c r="C632" s="4">
         <v>1250</v>
@@ -16737,7 +16819,7 @@
       </c>
       <c r="E632" s="4"/>
       <c r="F632" s="3" t="s">
-        <v>994</v>
+        <v>1115</v>
       </c>
     </row>
     <row r="633" spans="1:6" x14ac:dyDescent="0.3">
@@ -16745,7 +16827,7 @@
         <v>384</v>
       </c>
       <c r="B633" s="3" t="s">
-        <v>1014</v>
+        <v>1011</v>
       </c>
       <c r="C633" s="4">
         <v>850</v>
@@ -16755,7 +16837,7 @@
       </c>
       <c r="E633" s="4"/>
       <c r="F633" s="3" t="s">
-        <v>994</v>
+        <v>1115</v>
       </c>
     </row>
     <row r="634" spans="1:6" x14ac:dyDescent="0.3">
@@ -16763,7 +16845,7 @@
         <v>384</v>
       </c>
       <c r="B634" s="3" t="s">
-        <v>1015</v>
+        <v>1012</v>
       </c>
       <c r="C634" s="4">
         <v>1150</v>
@@ -16773,7 +16855,7 @@
       </c>
       <c r="E634" s="4"/>
       <c r="F634" s="3" t="s">
-        <v>994</v>
+        <v>1115</v>
       </c>
     </row>
     <row r="635" spans="1:6" x14ac:dyDescent="0.3">
@@ -16781,7 +16863,7 @@
         <v>384</v>
       </c>
       <c r="B635" s="3" t="s">
-        <v>1016</v>
+        <v>1013</v>
       </c>
       <c r="C635" s="4">
         <v>950</v>
@@ -16791,7 +16873,7 @@
       </c>
       <c r="E635" s="4"/>
       <c r="F635" s="3" t="s">
-        <v>994</v>
+        <v>1115</v>
       </c>
     </row>
     <row r="636" spans="1:6" x14ac:dyDescent="0.3">
@@ -16799,7 +16881,7 @@
         <v>384</v>
       </c>
       <c r="B636" s="3" t="s">
-        <v>1017</v>
+        <v>1014</v>
       </c>
       <c r="C636" s="4">
         <v>1250</v>
@@ -16809,7 +16891,7 @@
       </c>
       <c r="E636" s="4"/>
       <c r="F636" s="3" t="s">
-        <v>994</v>
+        <v>1115</v>
       </c>
     </row>
     <row r="637" spans="1:6" x14ac:dyDescent="0.3">
@@ -16817,7 +16899,7 @@
         <v>384</v>
       </c>
       <c r="B637" s="3" t="s">
-        <v>1018</v>
+        <v>1015</v>
       </c>
       <c r="C637" s="4">
         <v>650</v>
@@ -16827,7 +16909,7 @@
       </c>
       <c r="E637" s="4"/>
       <c r="F637" s="3" t="s">
-        <v>994</v>
+        <v>1115</v>
       </c>
     </row>
     <row r="638" spans="1:6" x14ac:dyDescent="0.3">
@@ -16835,7 +16917,7 @@
         <v>384</v>
       </c>
       <c r="B638" s="3" t="s">
-        <v>1019</v>
+        <v>1016</v>
       </c>
       <c r="C638" s="4">
         <v>950</v>
@@ -16845,7 +16927,7 @@
       </c>
       <c r="E638" s="4"/>
       <c r="F638" s="3" t="s">
-        <v>994</v>
+        <v>1115</v>
       </c>
     </row>
     <row r="639" spans="1:6" x14ac:dyDescent="0.3">
@@ -16853,7 +16935,7 @@
         <v>384</v>
       </c>
       <c r="B639" s="3" t="s">
-        <v>1020</v>
+        <v>1017</v>
       </c>
       <c r="C639" s="4">
         <v>750</v>
@@ -16863,7 +16945,7 @@
       </c>
       <c r="E639" s="4"/>
       <c r="F639" s="3" t="s">
-        <v>994</v>
+        <v>1115</v>
       </c>
     </row>
     <row r="640" spans="1:6" x14ac:dyDescent="0.3">
@@ -16871,7 +16953,7 @@
         <v>384</v>
       </c>
       <c r="B640" s="3" t="s">
-        <v>1021</v>
+        <v>1018</v>
       </c>
       <c r="C640" s="4">
         <v>1050</v>
@@ -16881,7 +16963,7 @@
       </c>
       <c r="E640" s="4"/>
       <c r="F640" s="3" t="s">
-        <v>994</v>
+        <v>1115</v>
       </c>
     </row>
     <row r="641" spans="1:6" x14ac:dyDescent="0.3">
@@ -16889,7 +16971,7 @@
         <v>384</v>
       </c>
       <c r="B641" s="3" t="s">
-        <v>1022</v>
+        <v>1019</v>
       </c>
       <c r="C641" s="4">
         <v>750</v>
@@ -16899,7 +16981,7 @@
       </c>
       <c r="E641" s="4"/>
       <c r="F641" s="3" t="s">
-        <v>994</v>
+        <v>1115</v>
       </c>
     </row>
     <row r="642" spans="1:6" x14ac:dyDescent="0.3">
@@ -16907,7 +16989,7 @@
         <v>384</v>
       </c>
       <c r="B642" s="3" t="s">
-        <v>1023</v>
+        <v>1020</v>
       </c>
       <c r="C642" s="4">
         <v>1050</v>
@@ -16917,7 +16999,7 @@
       </c>
       <c r="E642" s="4"/>
       <c r="F642" s="3" t="s">
-        <v>994</v>
+        <v>1115</v>
       </c>
     </row>
     <row r="643" spans="1:6" x14ac:dyDescent="0.3">
@@ -16925,7 +17007,7 @@
         <v>384</v>
       </c>
       <c r="B643" s="3" t="s">
-        <v>1024</v>
+        <v>1021</v>
       </c>
       <c r="C643" s="4">
         <v>3200</v>
@@ -16935,7 +17017,7 @@
       </c>
       <c r="E643" s="4"/>
       <c r="F643" s="3" t="s">
-        <v>994</v>
+        <v>1115</v>
       </c>
     </row>
     <row r="644" spans="1:6" x14ac:dyDescent="0.3">
@@ -16943,7 +17025,7 @@
         <v>384</v>
       </c>
       <c r="B644" s="3" t="s">
-        <v>1025</v>
+        <v>1022</v>
       </c>
       <c r="C644" s="4">
         <v>3600</v>
@@ -16953,15 +17035,15 @@
       </c>
       <c r="E644" s="4"/>
       <c r="F644" s="3" t="s">
-        <v>994</v>
+        <v>1115</v>
       </c>
     </row>
     <row r="645" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A645" s="3" t="s">
-        <v>862</v>
+        <v>861</v>
       </c>
       <c r="B645" s="3" t="s">
-        <v>1026</v>
+        <v>1023</v>
       </c>
       <c r="C645" s="4">
         <v>550</v>
@@ -16971,15 +17053,15 @@
       </c>
       <c r="E645" s="4"/>
       <c r="F645" s="3" t="s">
-        <v>994</v>
+        <v>1115</v>
       </c>
     </row>
     <row r="646" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A646" s="3" t="s">
-        <v>862</v>
+        <v>861</v>
       </c>
       <c r="B646" s="3" t="s">
-        <v>1027</v>
+        <v>1024</v>
       </c>
       <c r="C646" s="4">
         <v>750</v>
@@ -16989,15 +17071,15 @@
       </c>
       <c r="E646" s="4"/>
       <c r="F646" s="3" t="s">
-        <v>994</v>
+        <v>1115</v>
       </c>
     </row>
     <row r="647" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A647" s="3" t="s">
-        <v>862</v>
+        <v>861</v>
       </c>
       <c r="B647" s="3" t="s">
-        <v>1028</v>
+        <v>1025</v>
       </c>
       <c r="C647" s="4">
         <v>1550</v>
@@ -17007,15 +17089,15 @@
       </c>
       <c r="E647" s="4"/>
       <c r="F647" s="3" t="s">
-        <v>994</v>
+        <v>1115</v>
       </c>
     </row>
     <row r="648" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A648" s="3" t="s">
-        <v>862</v>
+        <v>861</v>
       </c>
       <c r="B648" s="3" t="s">
-        <v>1029</v>
+        <v>1026</v>
       </c>
       <c r="C648" s="4">
         <v>1750</v>
@@ -17025,15 +17107,15 @@
       </c>
       <c r="E648" s="4"/>
       <c r="F648" s="3" t="s">
-        <v>994</v>
+        <v>1115</v>
       </c>
     </row>
     <row r="649" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A649" s="3" t="s">
-        <v>862</v>
+        <v>861</v>
       </c>
       <c r="B649" s="3" t="s">
-        <v>1030</v>
+        <v>1027</v>
       </c>
       <c r="C649" s="4">
         <v>600</v>
@@ -17043,15 +17125,15 @@
       </c>
       <c r="E649" s="4"/>
       <c r="F649" s="3" t="s">
-        <v>994</v>
+        <v>1115</v>
       </c>
     </row>
     <row r="650" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A650" s="3" t="s">
-        <v>862</v>
+        <v>861</v>
       </c>
       <c r="B650" s="3" t="s">
-        <v>1031</v>
+        <v>1028</v>
       </c>
       <c r="C650" s="4">
         <v>400</v>
@@ -17061,15 +17143,15 @@
       </c>
       <c r="E650" s="4"/>
       <c r="F650" s="3" t="s">
-        <v>994</v>
+        <v>1115</v>
       </c>
     </row>
     <row r="651" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A651" s="3" t="s">
-        <v>862</v>
+        <v>861</v>
       </c>
       <c r="B651" s="3" t="s">
-        <v>1032</v>
+        <v>1029</v>
       </c>
       <c r="C651" s="4">
         <v>1100</v>
@@ -17079,15 +17161,15 @@
       </c>
       <c r="E651" s="4"/>
       <c r="F651" s="3" t="s">
-        <v>994</v>
+        <v>1115</v>
       </c>
     </row>
     <row r="652" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A652" s="3" t="s">
-        <v>862</v>
+        <v>861</v>
       </c>
       <c r="B652" s="3" t="s">
-        <v>1033</v>
+        <v>1030</v>
       </c>
       <c r="C652" s="4">
         <v>900</v>
@@ -17097,15 +17179,15 @@
       </c>
       <c r="E652" s="4"/>
       <c r="F652" s="3" t="s">
-        <v>994</v>
+        <v>1115</v>
       </c>
     </row>
     <row r="653" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A653" s="3" t="s">
-        <v>862</v>
+        <v>861</v>
       </c>
       <c r="B653" s="3" t="s">
-        <v>1034</v>
+        <v>1031</v>
       </c>
       <c r="C653" s="4">
         <v>900</v>
@@ -17115,15 +17197,15 @@
       </c>
       <c r="E653" s="4"/>
       <c r="F653" s="3" t="s">
-        <v>994</v>
+        <v>1115</v>
       </c>
     </row>
     <row r="654" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A654" s="3" t="s">
-        <v>862</v>
+        <v>861</v>
       </c>
       <c r="B654" s="3" t="s">
-        <v>1035</v>
+        <v>1032</v>
       </c>
       <c r="C654" s="4">
         <v>700</v>
@@ -17133,7 +17215,7 @@
       </c>
       <c r="E654" s="4"/>
       <c r="F654" s="3" t="s">
-        <v>994</v>
+        <v>1115</v>
       </c>
     </row>
     <row r="655" spans="1:6" x14ac:dyDescent="0.3">
@@ -17141,7 +17223,7 @@
         <v>384</v>
       </c>
       <c r="B655" s="3" t="s">
-        <v>1036</v>
+        <v>1033</v>
       </c>
       <c r="C655" s="4">
         <v>1250</v>
@@ -17151,7 +17233,7 @@
       </c>
       <c r="E655" s="4"/>
       <c r="F655" s="3" t="s">
-        <v>994</v>
+        <v>1115</v>
       </c>
     </row>
     <row r="656" spans="1:6" x14ac:dyDescent="0.3">
@@ -17159,7 +17241,7 @@
         <v>384</v>
       </c>
       <c r="B656" s="3" t="s">
-        <v>1037</v>
+        <v>1034</v>
       </c>
       <c r="C656" s="4">
         <v>800</v>
@@ -17169,7 +17251,7 @@
       </c>
       <c r="E656" s="4"/>
       <c r="F656" s="3" t="s">
-        <v>994</v>
+        <v>1115</v>
       </c>
     </row>
     <row r="657" spans="1:6" x14ac:dyDescent="0.3">
@@ -17177,7 +17259,7 @@
         <v>384</v>
       </c>
       <c r="B657" s="3" t="s">
-        <v>1038</v>
+        <v>1035</v>
       </c>
       <c r="C657" s="4">
         <v>1200</v>
@@ -17187,7 +17269,7 @@
       </c>
       <c r="E657" s="4"/>
       <c r="F657" s="3" t="s">
-        <v>994</v>
+        <v>1115</v>
       </c>
     </row>
     <row r="658" spans="1:6" x14ac:dyDescent="0.3">
@@ -17195,7 +17277,7 @@
         <v>384</v>
       </c>
       <c r="B658" s="3" t="s">
-        <v>1039</v>
+        <v>1036</v>
       </c>
       <c r="C658" s="4">
         <v>1300</v>
@@ -17205,15 +17287,15 @@
       </c>
       <c r="E658" s="4"/>
       <c r="F658" s="3" t="s">
-        <v>994</v>
+        <v>1115</v>
       </c>
     </row>
     <row r="659" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A659" s="3" t="s">
-        <v>862</v>
+        <v>861</v>
       </c>
       <c r="B659" s="3" t="s">
-        <v>1040</v>
+        <v>1037</v>
       </c>
       <c r="C659" s="4">
         <v>750</v>
@@ -17223,15 +17305,15 @@
       </c>
       <c r="E659" s="4"/>
       <c r="F659" s="3" t="s">
-        <v>994</v>
+        <v>1115</v>
       </c>
     </row>
     <row r="660" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A660" s="3" t="s">
-        <v>862</v>
+        <v>861</v>
       </c>
       <c r="B660" s="3" t="s">
-        <v>1041</v>
+        <v>1038</v>
       </c>
       <c r="C660" s="4">
         <v>1350</v>
@@ -17241,15 +17323,15 @@
       </c>
       <c r="E660" s="4"/>
       <c r="F660" s="3" t="s">
-        <v>994</v>
+        <v>1115</v>
       </c>
     </row>
     <row r="661" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A661" s="3" t="s">
-        <v>862</v>
+        <v>861</v>
       </c>
       <c r="B661" s="3" t="s">
-        <v>1042</v>
+        <v>1039</v>
       </c>
       <c r="C661" s="4">
         <v>1200</v>
@@ -17259,15 +17341,15 @@
       </c>
       <c r="E661" s="4"/>
       <c r="F661" s="3" t="s">
-        <v>994</v>
+        <v>1115</v>
       </c>
     </row>
     <row r="662" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A662" s="3" t="s">
-        <v>862</v>
+        <v>861</v>
       </c>
       <c r="B662" s="3" t="s">
-        <v>1043</v>
+        <v>1040</v>
       </c>
       <c r="C662" s="4">
         <v>1000</v>
@@ -17277,15 +17359,15 @@
       </c>
       <c r="E662" s="4"/>
       <c r="F662" s="3" t="s">
-        <v>994</v>
+        <v>1115</v>
       </c>
     </row>
     <row r="663" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A663" s="3" t="s">
-        <v>862</v>
+        <v>861</v>
       </c>
       <c r="B663" s="3" t="s">
-        <v>1044</v>
+        <v>1041</v>
       </c>
       <c r="C663" s="4">
         <v>1200</v>
@@ -17295,15 +17377,15 @@
       </c>
       <c r="E663" s="4"/>
       <c r="F663" s="3" t="s">
-        <v>994</v>
+        <v>1115</v>
       </c>
     </row>
     <row r="664" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A664" s="3" t="s">
-        <v>862</v>
+        <v>861</v>
       </c>
       <c r="B664" s="3" t="s">
-        <v>1045</v>
+        <v>1042</v>
       </c>
       <c r="C664" s="4">
         <v>1400</v>
@@ -17313,15 +17395,15 @@
       </c>
       <c r="E664" s="4"/>
       <c r="F664" s="3" t="s">
-        <v>994</v>
+        <v>1115</v>
       </c>
     </row>
     <row r="665" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A665" s="3" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
       <c r="B665" s="3" t="s">
-        <v>1046</v>
+        <v>1043</v>
       </c>
       <c r="C665" s="4">
         <v>1200</v>
@@ -17331,15 +17413,15 @@
       </c>
       <c r="E665" s="4"/>
       <c r="F665" s="3" t="s">
-        <v>994</v>
+        <v>1115</v>
       </c>
     </row>
     <row r="666" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A666" s="3" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
       <c r="B666" s="3" t="s">
-        <v>1047</v>
+        <v>1044</v>
       </c>
       <c r="C666" s="4">
         <v>1500</v>
@@ -17349,15 +17431,15 @@
       </c>
       <c r="E666" s="4"/>
       <c r="F666" s="3" t="s">
-        <v>994</v>
+        <v>1115</v>
       </c>
     </row>
     <row r="667" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A667" s="3" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
       <c r="B667" s="3" t="s">
-        <v>1048</v>
+        <v>1045</v>
       </c>
       <c r="C667" s="4">
         <v>1750</v>
@@ -17367,15 +17449,15 @@
       </c>
       <c r="E667" s="4"/>
       <c r="F667" s="3" t="s">
-        <v>994</v>
+        <v>1115</v>
       </c>
     </row>
     <row r="668" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A668" s="3" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
       <c r="B668" s="3" t="s">
-        <v>1049</v>
+        <v>1046</v>
       </c>
       <c r="C668" s="4">
         <v>1500</v>
@@ -17385,7 +17467,7 @@
       </c>
       <c r="E668" s="4"/>
       <c r="F668" s="3" t="s">
-        <v>994</v>
+        <v>1115</v>
       </c>
     </row>
     <row r="669" spans="1:6" x14ac:dyDescent="0.3">
@@ -17393,7 +17475,7 @@
         <v>384</v>
       </c>
       <c r="B669" s="3" t="s">
-        <v>1050</v>
+        <v>1047</v>
       </c>
       <c r="C669" s="4">
         <v>1650</v>
@@ -17403,7 +17485,7 @@
       </c>
       <c r="E669" s="4"/>
       <c r="F669" s="3" t="s">
-        <v>1052</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="670" spans="1:6" x14ac:dyDescent="0.3">
@@ -17411,7 +17493,7 @@
         <v>384</v>
       </c>
       <c r="B670" s="3" t="s">
-        <v>1051</v>
+        <v>1048</v>
       </c>
       <c r="C670" s="4">
         <v>1450</v>
@@ -17421,7 +17503,7 @@
       </c>
       <c r="E670" s="4"/>
       <c r="F670" s="3" t="s">
-        <v>1052</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="671" spans="1:6" x14ac:dyDescent="0.3">
@@ -17429,7 +17511,7 @@
         <v>384</v>
       </c>
       <c r="B671" s="3" t="s">
-        <v>1053</v>
+        <v>1050</v>
       </c>
       <c r="C671" s="4">
         <v>1750</v>
@@ -17439,7 +17521,7 @@
       </c>
       <c r="E671" s="4"/>
       <c r="F671" s="3" t="s">
-        <v>1055</v>
+        <v>1052</v>
       </c>
     </row>
     <row r="672" spans="1:6" x14ac:dyDescent="0.3">
@@ -17447,7 +17529,7 @@
         <v>384</v>
       </c>
       <c r="B672" s="3" t="s">
-        <v>1054</v>
+        <v>1051</v>
       </c>
       <c r="C672" s="4">
         <v>1550</v>
@@ -17457,7 +17539,7 @@
       </c>
       <c r="E672" s="4"/>
       <c r="F672" s="3" t="s">
-        <v>1055</v>
+        <v>1052</v>
       </c>
     </row>
     <row r="673" spans="1:6" x14ac:dyDescent="0.3">
@@ -17465,7 +17547,7 @@
         <v>5</v>
       </c>
       <c r="B673" s="5" t="s">
-        <v>1057</v>
+        <v>1054</v>
       </c>
       <c r="C673" s="4">
         <v>600</v>
@@ -17473,7 +17555,7 @@
       <c r="D673" s="4"/>
       <c r="E673" s="4"/>
       <c r="F673" s="3" t="s">
-        <v>1056</v>
+        <v>1053</v>
       </c>
     </row>
     <row r="674" spans="1:6" x14ac:dyDescent="0.3">
@@ -17481,7 +17563,7 @@
         <v>5</v>
       </c>
       <c r="B674" s="5" t="s">
-        <v>1058</v>
+        <v>1055</v>
       </c>
       <c r="C674" s="4">
         <v>1000</v>
@@ -17489,7 +17571,7 @@
       <c r="D674" s="4"/>
       <c r="E674" s="4"/>
       <c r="F674" s="3" t="s">
-        <v>1056</v>
+        <v>1053</v>
       </c>
     </row>
     <row r="675" spans="1:6" x14ac:dyDescent="0.3">
@@ -17497,7 +17579,7 @@
         <v>5</v>
       </c>
       <c r="B675" s="5" t="s">
-        <v>1059</v>
+        <v>1056</v>
       </c>
       <c r="C675" s="4">
         <v>600</v>
@@ -17505,7 +17587,7 @@
       <c r="D675" s="4"/>
       <c r="E675" s="4"/>
       <c r="F675" s="3" t="s">
-        <v>1056</v>
+        <v>1053</v>
       </c>
     </row>
     <row r="676" spans="1:6" x14ac:dyDescent="0.3">
@@ -17513,7 +17595,7 @@
         <v>5</v>
       </c>
       <c r="B676" s="5" t="s">
-        <v>1060</v>
+        <v>1057</v>
       </c>
       <c r="C676" s="4">
         <v>1000</v>
@@ -17521,7 +17603,7 @@
       <c r="D676" s="4"/>
       <c r="E676" s="4"/>
       <c r="F676" s="3" t="s">
-        <v>1056</v>
+        <v>1053</v>
       </c>
     </row>
     <row r="677" spans="1:6" x14ac:dyDescent="0.3">
@@ -17529,7 +17611,7 @@
         <v>5</v>
       </c>
       <c r="B677" s="5" t="s">
-        <v>1061</v>
+        <v>1058</v>
       </c>
       <c r="C677" s="4">
         <v>1200</v>
@@ -17537,7 +17619,7 @@
       <c r="D677" s="4"/>
       <c r="E677" s="4"/>
       <c r="F677" s="3" t="s">
-        <v>1056</v>
+        <v>1053</v>
       </c>
     </row>
     <row r="678" spans="1:6" x14ac:dyDescent="0.3">
@@ -17545,7 +17627,7 @@
         <v>5</v>
       </c>
       <c r="B678" s="5" t="s">
-        <v>1062</v>
+        <v>1059</v>
       </c>
       <c r="C678" s="4">
         <v>1000</v>
@@ -17553,7 +17635,7 @@
       <c r="D678" s="4"/>
       <c r="E678" s="4"/>
       <c r="F678" s="3" t="s">
-        <v>1056</v>
+        <v>1053</v>
       </c>
     </row>
     <row r="679" spans="1:6" x14ac:dyDescent="0.3">
@@ -17561,7 +17643,7 @@
         <v>5</v>
       </c>
       <c r="B679" s="5" t="s">
-        <v>1063</v>
+        <v>1060</v>
       </c>
       <c r="C679" s="4">
         <v>700</v>
@@ -17569,7 +17651,7 @@
       <c r="D679" s="4"/>
       <c r="E679" s="4"/>
       <c r="F679" s="3" t="s">
-        <v>1056</v>
+        <v>1053</v>
       </c>
     </row>
     <row r="680" spans="1:6" x14ac:dyDescent="0.3">
@@ -17577,7 +17659,7 @@
         <v>5</v>
       </c>
       <c r="B680" s="5" t="s">
-        <v>1064</v>
+        <v>1061</v>
       </c>
       <c r="C680" s="4">
         <v>1000</v>
@@ -17585,7 +17667,7 @@
       <c r="D680" s="4"/>
       <c r="E680" s="4"/>
       <c r="F680" s="3" t="s">
-        <v>1056</v>
+        <v>1053</v>
       </c>
     </row>
     <row r="681" spans="1:6" x14ac:dyDescent="0.3">
@@ -17593,7 +17675,7 @@
         <v>5</v>
       </c>
       <c r="B681" s="5" t="s">
-        <v>1065</v>
+        <v>1062</v>
       </c>
       <c r="C681" s="4">
         <v>800</v>
@@ -17601,7 +17683,7 @@
       <c r="D681" s="4"/>
       <c r="E681" s="4"/>
       <c r="F681" s="3" t="s">
-        <v>1056</v>
+        <v>1053</v>
       </c>
     </row>
     <row r="682" spans="1:6" x14ac:dyDescent="0.3">
@@ -17609,7 +17691,7 @@
         <v>5</v>
       </c>
       <c r="B682" s="5" t="s">
-        <v>1095</v>
+        <v>1077</v>
       </c>
       <c r="C682" s="4">
         <v>1200</v>
@@ -17617,7 +17699,7 @@
       <c r="D682" s="4"/>
       <c r="E682" s="4"/>
       <c r="F682" s="3" t="s">
-        <v>1056</v>
+        <v>1053</v>
       </c>
     </row>
     <row r="683" spans="1:6" x14ac:dyDescent="0.3">
@@ -17625,7 +17707,7 @@
         <v>5</v>
       </c>
       <c r="B683" s="5" t="s">
-        <v>1066</v>
+        <v>1063</v>
       </c>
       <c r="C683" s="4">
         <v>1200</v>
@@ -17633,7 +17715,7 @@
       <c r="D683" s="4"/>
       <c r="E683" s="4"/>
       <c r="F683" s="3" t="s">
-        <v>1056</v>
+        <v>1053</v>
       </c>
     </row>
     <row r="684" spans="1:6" x14ac:dyDescent="0.3">
@@ -17641,7 +17723,7 @@
         <v>5</v>
       </c>
       <c r="B684" s="5" t="s">
-        <v>1067</v>
+        <v>1064</v>
       </c>
       <c r="C684" s="4">
         <v>1400</v>
@@ -17649,7 +17731,7 @@
       <c r="D684" s="4"/>
       <c r="E684" s="4"/>
       <c r="F684" s="3" t="s">
-        <v>1056</v>
+        <v>1053</v>
       </c>
     </row>
     <row r="685" spans="1:6" x14ac:dyDescent="0.3">
@@ -17657,7 +17739,7 @@
         <v>5</v>
       </c>
       <c r="B685" s="5" t="s">
-        <v>1068</v>
+        <v>1065</v>
       </c>
       <c r="C685" s="4">
         <v>2000</v>
@@ -17665,7 +17747,7 @@
       <c r="D685" s="4"/>
       <c r="E685" s="4"/>
       <c r="F685" s="3" t="s">
-        <v>1056</v>
+        <v>1053</v>
       </c>
     </row>
     <row r="686" spans="1:6" x14ac:dyDescent="0.3">
@@ -17673,7 +17755,7 @@
         <v>5</v>
       </c>
       <c r="B686" s="5" t="s">
-        <v>1069</v>
+        <v>1066</v>
       </c>
       <c r="C686" s="4">
         <v>1200</v>
@@ -17681,7 +17763,7 @@
       <c r="D686" s="4"/>
       <c r="E686" s="4"/>
       <c r="F686" s="3" t="s">
-        <v>1056</v>
+        <v>1053</v>
       </c>
     </row>
     <row r="687" spans="1:6" x14ac:dyDescent="0.3">
@@ -17689,7 +17771,7 @@
         <v>5</v>
       </c>
       <c r="B687" s="5" t="s">
-        <v>1070</v>
+        <v>1067</v>
       </c>
       <c r="C687" s="4">
         <v>1500</v>
@@ -17697,7 +17779,7 @@
       <c r="D687" s="4"/>
       <c r="E687" s="4"/>
       <c r="F687" s="3" t="s">
-        <v>1056</v>
+        <v>1053</v>
       </c>
     </row>
     <row r="688" spans="1:6" x14ac:dyDescent="0.3">
@@ -17705,7 +17787,7 @@
         <v>5</v>
       </c>
       <c r="B688" s="5" t="s">
-        <v>1071</v>
+        <v>1068</v>
       </c>
       <c r="C688" s="4">
         <v>2000</v>
@@ -17713,7 +17795,7 @@
       <c r="D688" s="4"/>
       <c r="E688" s="4"/>
       <c r="F688" s="3" t="s">
-        <v>1056</v>
+        <v>1053</v>
       </c>
     </row>
     <row r="689" spans="1:6" x14ac:dyDescent="0.3">
@@ -17721,7 +17803,7 @@
         <v>5</v>
       </c>
       <c r="B689" s="5" t="s">
-        <v>1072</v>
+        <v>1069</v>
       </c>
       <c r="C689" s="4">
         <v>1500</v>
@@ -17729,7 +17811,7 @@
       <c r="D689" s="4"/>
       <c r="E689" s="4"/>
       <c r="F689" s="3" t="s">
-        <v>1056</v>
+        <v>1053</v>
       </c>
     </row>
     <row r="690" spans="1:6" x14ac:dyDescent="0.3">
@@ -17737,7 +17819,7 @@
         <v>5</v>
       </c>
       <c r="B690" s="5" t="s">
-        <v>1073</v>
+        <v>1070</v>
       </c>
       <c r="C690" s="4">
         <v>1500</v>
@@ -17745,7 +17827,7 @@
       <c r="D690" s="4"/>
       <c r="E690" s="4"/>
       <c r="F690" s="3" t="s">
-        <v>1056</v>
+        <v>1053</v>
       </c>
     </row>
     <row r="691" spans="1:6" x14ac:dyDescent="0.3">
@@ -17753,7 +17835,7 @@
         <v>5</v>
       </c>
       <c r="B691" s="5" t="s">
-        <v>1074</v>
+        <v>1071</v>
       </c>
       <c r="C691" s="4">
         <v>1800</v>
@@ -17761,7 +17843,7 @@
       <c r="D691" s="4"/>
       <c r="E691" s="4"/>
       <c r="F691" s="3" t="s">
-        <v>1056</v>
+        <v>1053</v>
       </c>
     </row>
     <row r="692" spans="1:6" x14ac:dyDescent="0.3">
@@ -17769,7 +17851,7 @@
         <v>5</v>
       </c>
       <c r="B692" s="5" t="s">
-        <v>1075</v>
+        <v>1072</v>
       </c>
       <c r="C692" s="4">
         <v>2500</v>
@@ -17777,7 +17859,7 @@
       <c r="D692" s="4"/>
       <c r="E692" s="4"/>
       <c r="F692" s="3" t="s">
-        <v>1056</v>
+        <v>1053</v>
       </c>
     </row>
     <row r="693" spans="1:6" x14ac:dyDescent="0.3">
@@ -17785,7 +17867,7 @@
         <v>5</v>
       </c>
       <c r="B693" s="5" t="s">
-        <v>1076</v>
+        <v>1073</v>
       </c>
       <c r="C693" s="4">
         <v>1200</v>
@@ -17793,7 +17875,7 @@
       <c r="D693" s="4"/>
       <c r="E693" s="4"/>
       <c r="F693" s="3" t="s">
-        <v>1056</v>
+        <v>1053</v>
       </c>
     </row>
     <row r="694" spans="1:6" x14ac:dyDescent="0.3">
@@ -17801,7 +17883,7 @@
         <v>5</v>
       </c>
       <c r="B694" s="5" t="s">
-        <v>1077</v>
+        <v>1074</v>
       </c>
       <c r="C694" s="4">
         <v>1500</v>
@@ -17809,7 +17891,7 @@
       <c r="D694" s="4"/>
       <c r="E694" s="4"/>
       <c r="F694" s="3" t="s">
-        <v>1056</v>
+        <v>1053</v>
       </c>
     </row>
     <row r="695" spans="1:6" x14ac:dyDescent="0.3">
@@ -17817,7 +17899,7 @@
         <v>5</v>
       </c>
       <c r="B695" s="5" t="s">
-        <v>1078</v>
+        <v>1075</v>
       </c>
       <c r="C695" s="4">
         <v>1500</v>
@@ -17825,7 +17907,7 @@
       <c r="D695" s="4"/>
       <c r="E695" s="4"/>
       <c r="F695" s="3" t="s">
-        <v>1056</v>
+        <v>1053</v>
       </c>
     </row>
     <row r="696" spans="1:6" x14ac:dyDescent="0.3">
@@ -17833,7 +17915,7 @@
         <v>5</v>
       </c>
       <c r="B696" s="5" t="s">
-        <v>1079</v>
+        <v>1076</v>
       </c>
       <c r="C696" s="4">
         <v>1000</v>
@@ -17841,7 +17923,7 @@
       <c r="D696" s="4"/>
       <c r="E696" s="4"/>
       <c r="F696" s="3" t="s">
-        <v>1056</v>
+        <v>1053</v>
       </c>
     </row>
     <row r="697" spans="1:6" x14ac:dyDescent="0.3">
@@ -17849,7 +17931,7 @@
         <v>5</v>
       </c>
       <c r="B697" s="3" t="s">
-        <v>1080</v>
+        <v>1078</v>
       </c>
       <c r="C697" s="4">
         <v>100</v>
@@ -17861,7 +17943,7 @@
         <v>100</v>
       </c>
       <c r="F697" s="3" t="s">
-        <v>1086</v>
+        <v>1084</v>
       </c>
     </row>
     <row r="698" spans="1:6" x14ac:dyDescent="0.3">
@@ -17869,7 +17951,7 @@
         <v>5</v>
       </c>
       <c r="B698" s="3" t="s">
-        <v>1081</v>
+        <v>1079</v>
       </c>
       <c r="C698" s="4">
         <v>100</v>
@@ -17881,7 +17963,7 @@
         <v>100</v>
       </c>
       <c r="F698" s="3" t="s">
-        <v>1086</v>
+        <v>1084</v>
       </c>
     </row>
     <row r="699" spans="1:6" x14ac:dyDescent="0.3">
@@ -17889,7 +17971,7 @@
         <v>5</v>
       </c>
       <c r="B699" s="3" t="s">
-        <v>1082</v>
+        <v>1080</v>
       </c>
       <c r="C699" s="4">
         <v>300</v>
@@ -17901,7 +17983,7 @@
         <v>300</v>
       </c>
       <c r="F699" s="3" t="s">
-        <v>1086</v>
+        <v>1084</v>
       </c>
     </row>
     <row r="700" spans="1:6" x14ac:dyDescent="0.3">
@@ -17909,7 +17991,7 @@
         <v>5</v>
       </c>
       <c r="B700" s="3" t="s">
-        <v>1083</v>
+        <v>1081</v>
       </c>
       <c r="C700" s="4">
         <v>40</v>
@@ -17921,7 +18003,7 @@
         <v>40</v>
       </c>
       <c r="F700" s="3" t="s">
-        <v>1086</v>
+        <v>1084</v>
       </c>
     </row>
     <row r="701" spans="1:6" x14ac:dyDescent="0.3">
@@ -17929,7 +18011,7 @@
         <v>5</v>
       </c>
       <c r="B701" s="3" t="s">
-        <v>1084</v>
+        <v>1082</v>
       </c>
       <c r="C701" s="4">
         <v>200</v>
@@ -17941,7 +18023,7 @@
         <v>200</v>
       </c>
       <c r="F701" s="3" t="s">
-        <v>1086</v>
+        <v>1084</v>
       </c>
     </row>
     <row r="702" spans="1:6" x14ac:dyDescent="0.3">
@@ -17949,7 +18031,7 @@
         <v>5</v>
       </c>
       <c r="B702" s="3" t="s">
-        <v>1093</v>
+        <v>1091</v>
       </c>
       <c r="C702" s="4">
         <v>500</v>
@@ -17961,7 +18043,7 @@
         <v>500</v>
       </c>
       <c r="F702" s="3" t="s">
-        <v>1086</v>
+        <v>1084</v>
       </c>
     </row>
     <row r="703" spans="1:6" x14ac:dyDescent="0.3">
@@ -17969,7 +18051,7 @@
         <v>5</v>
       </c>
       <c r="B703" s="3" t="s">
-        <v>1085</v>
+        <v>1083</v>
       </c>
       <c r="C703" s="4">
         <v>5</v>
@@ -17981,7 +18063,7 @@
         <v>5</v>
       </c>
       <c r="F703" s="3" t="s">
-        <v>1086</v>
+        <v>1084</v>
       </c>
     </row>
     <row r="704" spans="1:6" x14ac:dyDescent="0.3">
@@ -17989,7 +18071,7 @@
         <v>5</v>
       </c>
       <c r="B704" s="3" t="s">
-        <v>1088</v>
+        <v>1086</v>
       </c>
       <c r="C704" s="4">
         <v>80</v>
@@ -18001,7 +18083,7 @@
         <v>80</v>
       </c>
       <c r="F704" s="3" t="s">
-        <v>1087</v>
+        <v>1085</v>
       </c>
     </row>
     <row r="705" spans="1:6" x14ac:dyDescent="0.3">
@@ -18009,7 +18091,7 @@
         <v>5</v>
       </c>
       <c r="B705" s="3" t="s">
-        <v>1089</v>
+        <v>1087</v>
       </c>
       <c r="C705" s="4">
         <v>80</v>
@@ -18021,7 +18103,7 @@
         <v>80</v>
       </c>
       <c r="F705" s="3" t="s">
-        <v>1087</v>
+        <v>1085</v>
       </c>
     </row>
     <row r="706" spans="1:6" x14ac:dyDescent="0.3">
@@ -18029,7 +18111,7 @@
         <v>5</v>
       </c>
       <c r="B706" s="3" t="s">
-        <v>1090</v>
+        <v>1088</v>
       </c>
       <c r="C706" s="4">
         <v>80</v>
@@ -18041,7 +18123,7 @@
         <v>80</v>
       </c>
       <c r="F706" s="3" t="s">
-        <v>1087</v>
+        <v>1085</v>
       </c>
     </row>
     <row r="707" spans="1:6" x14ac:dyDescent="0.3">
@@ -18049,7 +18131,7 @@
         <v>5</v>
       </c>
       <c r="B707" s="3" t="s">
-        <v>1091</v>
+        <v>1089</v>
       </c>
       <c r="C707" s="4">
         <v>20</v>
@@ -18061,7 +18143,7 @@
         <v>20</v>
       </c>
       <c r="F707" s="3" t="s">
-        <v>1087</v>
+        <v>1085</v>
       </c>
     </row>
     <row r="708" spans="1:6" x14ac:dyDescent="0.3">
@@ -18069,7 +18151,7 @@
         <v>5</v>
       </c>
       <c r="B708" s="3" t="s">
-        <v>1092</v>
+        <v>1090</v>
       </c>
       <c r="C708" s="4">
         <v>20</v>
@@ -18081,7 +18163,7 @@
         <v>20</v>
       </c>
       <c r="F708" s="3" t="s">
-        <v>1087</v>
+        <v>1085</v>
       </c>
     </row>
     <row r="709" spans="1:6" x14ac:dyDescent="0.3">
@@ -18389,6 +18471,7 @@
       <c r="F746" s="3"/>
     </row>
   </sheetData>
+  <autoFilter ref="A1:G708" xr:uid="{15F300B1-DC52-4A05-894C-2D13A4E4CB6B}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
@@ -18404,15 +18487,15 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A2" s="31" t="s">
-        <v>925</v>
-      </c>
-      <c r="B2" s="25"/>
-      <c r="C2" s="25"/>
-      <c r="D2" s="25"/>
-      <c r="E2" s="25"/>
-      <c r="F2" s="25"/>
-      <c r="G2" s="25"/>
+      <c r="A2" s="22" t="s">
+        <v>924</v>
+      </c>
+      <c r="B2" s="23"/>
+      <c r="C2" s="23"/>
+      <c r="D2" s="23"/>
+      <c r="E2" s="23"/>
+      <c r="F2" s="23"/>
+      <c r="G2" s="23"/>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" s="9"/>
@@ -18424,58 +18507,58 @@
       <c r="G3" s="8"/>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A4" s="26" t="s">
+      <c r="A4" s="24" t="s">
+        <v>925</v>
+      </c>
+      <c r="B4" s="26" t="s">
         <v>926</v>
       </c>
-      <c r="B4" s="28" t="s">
+      <c r="C4" s="27"/>
+      <c r="D4" s="26" t="s">
         <v>927</v>
       </c>
-      <c r="C4" s="29"/>
-      <c r="D4" s="28" t="s">
+      <c r="E4" s="27"/>
+      <c r="F4" s="26" t="s">
         <v>928</v>
       </c>
-      <c r="E4" s="29"/>
-      <c r="F4" s="28" t="s">
+      <c r="G4" s="27"/>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A5" s="25"/>
+      <c r="B5" s="10" t="s">
         <v>929</v>
       </c>
-      <c r="G4" s="29"/>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A5" s="27"/>
-      <c r="B5" s="10" t="s">
+      <c r="C5" s="10" t="s">
         <v>930</v>
       </c>
-      <c r="C5" s="10" t="s">
+      <c r="D5" s="10" t="s">
+        <v>929</v>
+      </c>
+      <c r="E5" s="10" t="s">
+        <v>930</v>
+      </c>
+      <c r="F5" s="10" t="s">
         <v>931</v>
       </c>
-      <c r="D5" s="10" t="s">
-        <v>930</v>
-      </c>
-      <c r="E5" s="10" t="s">
-        <v>931</v>
-      </c>
-      <c r="F5" s="10" t="s">
+      <c r="G5" s="10" t="s">
         <v>932</v>
-      </c>
-      <c r="G5" s="10" t="s">
-        <v>933</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" s="11" t="s">
-        <v>934</v>
+        <v>933</v>
       </c>
       <c r="B6" s="12">
         <v>0.35416666666666669</v>
       </c>
       <c r="C6" s="13" t="s">
-        <v>935</v>
+        <v>934</v>
       </c>
       <c r="D6" s="12">
         <v>0.45833333333333331</v>
       </c>
       <c r="E6" s="13" t="s">
-        <v>936</v>
+        <v>935</v>
       </c>
       <c r="F6" s="14">
         <v>650</v>
@@ -18486,19 +18569,19 @@
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" s="11" t="s">
-        <v>937</v>
+        <v>936</v>
       </c>
       <c r="B7" s="12">
         <v>0.35416666666666669</v>
       </c>
       <c r="C7" s="13" t="s">
-        <v>935</v>
+        <v>934</v>
       </c>
       <c r="D7" s="12">
         <v>0.44791666666666669</v>
       </c>
       <c r="E7" s="13" t="s">
-        <v>938</v>
+        <v>937</v>
       </c>
       <c r="F7" s="14">
         <v>650</v>
@@ -18508,37 +18591,37 @@
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A8" s="21" t="s">
+      <c r="A8" s="19" t="s">
+        <v>938</v>
+      </c>
+      <c r="B8" s="20"/>
+      <c r="C8" s="20"/>
+      <c r="D8" s="20"/>
+      <c r="E8" s="20"/>
+      <c r="F8" s="20"/>
+      <c r="G8" s="21"/>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A9" s="19" t="s">
         <v>939</v>
       </c>
-      <c r="B8" s="22"/>
-      <c r="C8" s="22"/>
-      <c r="D8" s="22"/>
-      <c r="E8" s="22"/>
-      <c r="F8" s="22"/>
-      <c r="G8" s="23"/>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A9" s="21" t="s">
+      <c r="B9" s="20"/>
+      <c r="C9" s="20"/>
+      <c r="D9" s="20"/>
+      <c r="E9" s="20"/>
+      <c r="F9" s="20"/>
+      <c r="G9" s="21"/>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A10" s="28" t="s">
         <v>940</v>
       </c>
-      <c r="B9" s="22"/>
-      <c r="C9" s="22"/>
-      <c r="D9" s="22"/>
-      <c r="E9" s="22"/>
-      <c r="F9" s="22"/>
-      <c r="G9" s="23"/>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A10" s="24" t="s">
-        <v>941</v>
-      </c>
-      <c r="B10" s="25"/>
-      <c r="C10" s="25"/>
-      <c r="D10" s="25"/>
-      <c r="E10" s="25"/>
-      <c r="F10" s="25"/>
-      <c r="G10" s="25"/>
+      <c r="B10" s="23"/>
+      <c r="C10" s="23"/>
+      <c r="D10" s="23"/>
+      <c r="E10" s="23"/>
+      <c r="F10" s="23"/>
+      <c r="G10" s="23"/>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" s="9"/>
@@ -18550,58 +18633,58 @@
       <c r="G11" s="8"/>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A12" s="26" t="s">
+      <c r="A12" s="24" t="s">
+        <v>925</v>
+      </c>
+      <c r="B12" s="26" t="s">
         <v>926</v>
       </c>
-      <c r="B12" s="28" t="s">
+      <c r="C12" s="27"/>
+      <c r="D12" s="26" t="s">
         <v>927</v>
       </c>
-      <c r="C12" s="29"/>
-      <c r="D12" s="28" t="s">
+      <c r="E12" s="27"/>
+      <c r="F12" s="26" t="s">
         <v>928</v>
       </c>
-      <c r="E12" s="29"/>
-      <c r="F12" s="28" t="s">
+      <c r="G12" s="27"/>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A13" s="25"/>
+      <c r="B13" s="10" t="s">
         <v>929</v>
       </c>
-      <c r="G12" s="29"/>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A13" s="27"/>
-      <c r="B13" s="10" t="s">
+      <c r="C13" s="10" t="s">
         <v>930</v>
       </c>
-      <c r="C13" s="10" t="s">
+      <c r="D13" s="10" t="s">
+        <v>929</v>
+      </c>
+      <c r="E13" s="10" t="s">
+        <v>930</v>
+      </c>
+      <c r="F13" s="10" t="s">
         <v>931</v>
       </c>
-      <c r="D13" s="10" t="s">
-        <v>930</v>
-      </c>
-      <c r="E13" s="10" t="s">
-        <v>931</v>
-      </c>
-      <c r="F13" s="10" t="s">
+      <c r="G13" s="10" t="s">
         <v>932</v>
       </c>
-      <c r="G13" s="10" t="s">
-        <v>933</v>
-      </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A14" s="19" t="s">
-        <v>942</v>
+      <c r="A14" s="29" t="s">
+        <v>941</v>
       </c>
       <c r="B14" s="12">
         <v>0.35416666666666669</v>
       </c>
       <c r="C14" s="13" t="s">
-        <v>935</v>
+        <v>934</v>
       </c>
       <c r="D14" s="12">
         <v>0.4375</v>
       </c>
       <c r="E14" s="13" t="s">
-        <v>943</v>
+        <v>942</v>
       </c>
       <c r="F14" s="14">
         <v>400</v>
@@ -18611,18 +18694,18 @@
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A15" s="30"/>
+      <c r="A15" s="31"/>
       <c r="B15" s="12">
         <v>0.45833333333333331</v>
       </c>
       <c r="C15" s="13" t="s">
-        <v>935</v>
+        <v>934</v>
       </c>
       <c r="D15" s="12">
         <v>0.54166666666666663</v>
       </c>
       <c r="E15" s="13" t="s">
-        <v>943</v>
+        <v>942</v>
       </c>
       <c r="F15" s="14">
         <v>400</v>
@@ -18632,18 +18715,18 @@
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A16" s="20"/>
+      <c r="A16" s="30"/>
       <c r="B16" s="12">
         <v>0.625</v>
       </c>
       <c r="C16" s="13" t="s">
-        <v>935</v>
+        <v>934</v>
       </c>
       <c r="D16" s="12">
         <v>0.70833333333333337</v>
       </c>
       <c r="E16" s="13" t="s">
-        <v>943</v>
+        <v>942</v>
       </c>
       <c r="F16" s="14">
         <v>400</v>
@@ -18653,20 +18736,20 @@
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A17" s="19" t="s">
-        <v>942</v>
+      <c r="A17" s="29" t="s">
+        <v>941</v>
       </c>
       <c r="B17" s="12">
         <v>0.35416666666666669</v>
       </c>
       <c r="C17" s="13" t="s">
-        <v>935</v>
+        <v>934</v>
       </c>
       <c r="D17" s="12">
         <v>0.47916666666666669</v>
       </c>
       <c r="E17" s="13" t="s">
-        <v>944</v>
+        <v>943</v>
       </c>
       <c r="F17" s="14">
         <v>650</v>
@@ -18676,18 +18759,18 @@
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A18" s="20"/>
+      <c r="A18" s="30"/>
       <c r="B18" s="12">
         <v>0.57291666666666663</v>
       </c>
       <c r="C18" s="13" t="s">
-        <v>935</v>
+        <v>934</v>
       </c>
       <c r="D18" s="12">
         <v>0.69791666666666663</v>
       </c>
       <c r="E18" s="13" t="s">
-        <v>944</v>
+        <v>943</v>
       </c>
       <c r="F18" s="14">
         <v>650</v>
@@ -18697,26 +18780,26 @@
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A19" s="21" t="s">
-        <v>945</v>
-      </c>
-      <c r="B19" s="22"/>
-      <c r="C19" s="22"/>
-      <c r="D19" s="22"/>
-      <c r="E19" s="22"/>
-      <c r="F19" s="22"/>
-      <c r="G19" s="23"/>
+      <c r="A19" s="19" t="s">
+        <v>944</v>
+      </c>
+      <c r="B19" s="20"/>
+      <c r="C19" s="20"/>
+      <c r="D19" s="20"/>
+      <c r="E19" s="20"/>
+      <c r="F19" s="20"/>
+      <c r="G19" s="21"/>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A20" s="24" t="s">
-        <v>941</v>
-      </c>
-      <c r="B20" s="25"/>
-      <c r="C20" s="25"/>
-      <c r="D20" s="25"/>
-      <c r="E20" s="25"/>
-      <c r="F20" s="25"/>
-      <c r="G20" s="25"/>
+      <c r="A20" s="28" t="s">
+        <v>940</v>
+      </c>
+      <c r="B20" s="23"/>
+      <c r="C20" s="23"/>
+      <c r="D20" s="23"/>
+      <c r="E20" s="23"/>
+      <c r="F20" s="23"/>
+      <c r="G20" s="23"/>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A21" s="15"/>
@@ -18728,58 +18811,58 @@
       <c r="G21" s="15"/>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A22" s="26" t="s">
+      <c r="A22" s="24" t="s">
+        <v>945</v>
+      </c>
+      <c r="B22" s="26" t="s">
+        <v>926</v>
+      </c>
+      <c r="C22" s="27"/>
+      <c r="D22" s="26" t="s">
+        <v>927</v>
+      </c>
+      <c r="E22" s="27"/>
+      <c r="F22" s="26" t="s">
+        <v>928</v>
+      </c>
+      <c r="G22" s="27"/>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A23" s="25"/>
+      <c r="B23" s="10" t="s">
+        <v>929</v>
+      </c>
+      <c r="C23" s="10" t="s">
+        <v>930</v>
+      </c>
+      <c r="D23" s="10" t="s">
+        <v>929</v>
+      </c>
+      <c r="E23" s="10" t="s">
+        <v>930</v>
+      </c>
+      <c r="F23" s="10" t="s">
+        <v>931</v>
+      </c>
+      <c r="G23" s="10" t="s">
+        <v>932</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A24" s="29" t="s">
         <v>946</v>
-      </c>
-      <c r="B22" s="28" t="s">
-        <v>927</v>
-      </c>
-      <c r="C22" s="29"/>
-      <c r="D22" s="28" t="s">
-        <v>928</v>
-      </c>
-      <c r="E22" s="29"/>
-      <c r="F22" s="28" t="s">
-        <v>929</v>
-      </c>
-      <c r="G22" s="29"/>
-    </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A23" s="27"/>
-      <c r="B23" s="10" t="s">
-        <v>930</v>
-      </c>
-      <c r="C23" s="10" t="s">
-        <v>931</v>
-      </c>
-      <c r="D23" s="10" t="s">
-        <v>930</v>
-      </c>
-      <c r="E23" s="10" t="s">
-        <v>931</v>
-      </c>
-      <c r="F23" s="10" t="s">
-        <v>932</v>
-      </c>
-      <c r="G23" s="10" t="s">
-        <v>933</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A24" s="19" t="s">
-        <v>947</v>
       </c>
       <c r="B24" s="12">
         <v>0.375</v>
       </c>
       <c r="C24" s="13" t="s">
-        <v>943</v>
+        <v>942</v>
       </c>
       <c r="D24" s="12">
         <v>0.45833333333333331</v>
       </c>
       <c r="E24" s="13" t="s">
-        <v>935</v>
+        <v>934</v>
       </c>
       <c r="F24" s="16">
         <v>450</v>
@@ -18789,18 +18872,18 @@
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A25" s="30"/>
+      <c r="A25" s="31"/>
       <c r="B25" s="12">
         <v>0.58333333333333337</v>
       </c>
       <c r="C25" s="13" t="s">
-        <v>943</v>
+        <v>942</v>
       </c>
       <c r="D25" s="12">
         <v>0.66666666666666663</v>
       </c>
       <c r="E25" s="13" t="s">
-        <v>948</v>
+        <v>947</v>
       </c>
       <c r="F25" s="16">
         <v>450</v>
@@ -18810,18 +18893,18 @@
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A26" s="20"/>
+      <c r="A26" s="30"/>
       <c r="B26" s="12">
         <v>0.64583333333333337</v>
       </c>
       <c r="C26" s="13" t="s">
-        <v>943</v>
+        <v>942</v>
       </c>
       <c r="D26" s="12">
         <v>0.72916666666666663</v>
       </c>
       <c r="E26" s="13" t="s">
-        <v>935</v>
+        <v>934</v>
       </c>
       <c r="F26" s="16">
         <v>450</v>
@@ -18831,20 +18914,20 @@
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A27" s="19" t="s">
-        <v>947</v>
+      <c r="A27" s="29" t="s">
+        <v>946</v>
       </c>
       <c r="B27" s="12">
         <v>0.41666666666666669</v>
       </c>
       <c r="C27" s="13" t="s">
-        <v>944</v>
+        <v>943</v>
       </c>
       <c r="D27" s="12">
         <v>0.54166666666666663</v>
       </c>
       <c r="E27" s="13" t="s">
-        <v>935</v>
+        <v>934</v>
       </c>
       <c r="F27" s="16">
         <v>700</v>
@@ -18854,18 +18937,18 @@
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A28" s="20"/>
+      <c r="A28" s="30"/>
       <c r="B28" s="12">
         <v>0.5625</v>
       </c>
       <c r="C28" s="13" t="s">
-        <v>944</v>
+        <v>943</v>
       </c>
       <c r="D28" s="12">
         <v>0.6875</v>
       </c>
       <c r="E28" s="13" t="s">
-        <v>935</v>
+        <v>934</v>
       </c>
       <c r="F28" s="16">
         <v>700</v>
@@ -18875,20 +18958,20 @@
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A29" s="19" t="s">
-        <v>949</v>
+      <c r="A29" s="29" t="s">
+        <v>948</v>
       </c>
       <c r="B29" s="12">
         <v>0.4375</v>
       </c>
       <c r="C29" s="13" t="s">
-        <v>943</v>
+        <v>942</v>
       </c>
       <c r="D29" s="12">
         <v>0.52083333333333337</v>
       </c>
       <c r="E29" s="13" t="s">
-        <v>950</v>
+        <v>949</v>
       </c>
       <c r="F29" s="16">
         <v>400</v>
@@ -18898,18 +18981,18 @@
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A30" s="20"/>
+      <c r="A30" s="30"/>
       <c r="B30" s="12">
         <v>0.64583333333333337</v>
       </c>
       <c r="C30" s="13" t="s">
-        <v>943</v>
+        <v>942</v>
       </c>
       <c r="D30" s="12">
         <v>0.72916666666666663</v>
       </c>
       <c r="E30" s="13" t="s">
-        <v>950</v>
+        <v>949</v>
       </c>
       <c r="F30" s="16">
         <v>400</v>
@@ -18919,20 +19002,20 @@
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A31" s="19" t="s">
-        <v>951</v>
+      <c r="A31" s="29" t="s">
+        <v>950</v>
       </c>
       <c r="B31" s="12">
         <v>0.39583333333333331</v>
       </c>
       <c r="C31" s="13" t="s">
-        <v>943</v>
+        <v>942</v>
       </c>
       <c r="D31" s="12">
         <v>0.45833333333333331</v>
       </c>
       <c r="E31" s="13" t="s">
-        <v>938</v>
+        <v>937</v>
       </c>
       <c r="F31" s="14">
         <v>500</v>
@@ -18942,18 +19025,18 @@
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A32" s="20"/>
+      <c r="A32" s="30"/>
       <c r="B32" s="12">
         <v>0.64583333333333337</v>
       </c>
       <c r="C32" s="13" t="s">
-        <v>943</v>
+        <v>942</v>
       </c>
       <c r="D32" s="12">
         <v>0.69791666666666663</v>
       </c>
       <c r="E32" s="13" t="s">
-        <v>938</v>
+        <v>937</v>
       </c>
       <c r="F32" s="14">
         <v>500</v>
@@ -18963,20 +19046,20 @@
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A33" s="19" t="s">
-        <v>952</v>
+      <c r="A33" s="29" t="s">
+        <v>951</v>
       </c>
       <c r="B33" s="12">
         <v>0.39583333333333331</v>
       </c>
       <c r="C33" s="13" t="s">
-        <v>943</v>
+        <v>942</v>
       </c>
       <c r="D33" s="12">
         <v>0.47916666666666669</v>
       </c>
       <c r="E33" s="13" t="s">
-        <v>936</v>
+        <v>935</v>
       </c>
       <c r="F33" s="14">
         <v>500</v>
@@ -18986,18 +19069,18 @@
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A34" s="20"/>
+      <c r="A34" s="30"/>
       <c r="B34" s="12">
         <v>0.64583333333333337</v>
       </c>
       <c r="C34" s="13" t="s">
-        <v>943</v>
+        <v>942</v>
       </c>
       <c r="D34" s="12">
         <v>0.72916666666666663</v>
       </c>
       <c r="E34" s="13" t="s">
-        <v>936</v>
+        <v>935</v>
       </c>
       <c r="F34" s="14">
         <v>500</v>
@@ -19007,20 +19090,20 @@
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A35" s="19" t="s">
-        <v>953</v>
+      <c r="A35" s="29" t="s">
+        <v>952</v>
       </c>
       <c r="B35" s="12">
         <v>0.47916666666666669</v>
       </c>
       <c r="C35" s="13" t="s">
-        <v>943</v>
+        <v>942</v>
       </c>
       <c r="D35" s="12">
         <v>0.52083333333333337</v>
       </c>
       <c r="E35" s="13" t="s">
-        <v>954</v>
+        <v>953</v>
       </c>
       <c r="F35" s="16" t="s">
         <v>7</v>
@@ -19030,18 +19113,18 @@
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A36" s="20"/>
+      <c r="A36" s="30"/>
       <c r="B36" s="12">
         <v>0.625</v>
       </c>
       <c r="C36" s="13" t="s">
-        <v>943</v>
+        <v>942</v>
       </c>
       <c r="D36" s="12">
         <v>0.66666666666666663</v>
       </c>
       <c r="E36" s="13" t="s">
-        <v>954</v>
+        <v>953</v>
       </c>
       <c r="F36" s="16" t="s">
         <v>7</v>
@@ -19051,48 +19134,48 @@
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A37" s="21" t="s">
+      <c r="A37" s="19" t="s">
+        <v>954</v>
+      </c>
+      <c r="B37" s="20"/>
+      <c r="C37" s="20"/>
+      <c r="D37" s="20"/>
+      <c r="E37" s="20"/>
+      <c r="F37" s="20"/>
+      <c r="G37" s="21"/>
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A38" s="19" t="s">
         <v>955</v>
       </c>
-      <c r="B37" s="22"/>
-      <c r="C37" s="22"/>
-      <c r="D37" s="22"/>
-      <c r="E37" s="22"/>
-      <c r="F37" s="22"/>
-      <c r="G37" s="23"/>
-    </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A38" s="21" t="s">
-        <v>956</v>
-      </c>
-      <c r="B38" s="22"/>
-      <c r="C38" s="22"/>
-      <c r="D38" s="22"/>
-      <c r="E38" s="22"/>
-      <c r="F38" s="22"/>
-      <c r="G38" s="23"/>
+      <c r="B38" s="20"/>
+      <c r="C38" s="20"/>
+      <c r="D38" s="20"/>
+      <c r="E38" s="20"/>
+      <c r="F38" s="20"/>
+      <c r="G38" s="21"/>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A39" s="21" t="s">
-        <v>945</v>
-      </c>
-      <c r="B39" s="22"/>
-      <c r="C39" s="22"/>
-      <c r="D39" s="22"/>
-      <c r="E39" s="22"/>
-      <c r="F39" s="22"/>
-      <c r="G39" s="23"/>
+      <c r="A39" s="19" t="s">
+        <v>944</v>
+      </c>
+      <c r="B39" s="20"/>
+      <c r="C39" s="20"/>
+      <c r="D39" s="20"/>
+      <c r="E39" s="20"/>
+      <c r="F39" s="20"/>
+      <c r="G39" s="21"/>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A40" s="24" t="s">
-        <v>941</v>
-      </c>
-      <c r="B40" s="25"/>
-      <c r="C40" s="25"/>
-      <c r="D40" s="25"/>
-      <c r="E40" s="25"/>
-      <c r="F40" s="25"/>
-      <c r="G40" s="25"/>
+      <c r="A40" s="28" t="s">
+        <v>940</v>
+      </c>
+      <c r="B40" s="23"/>
+      <c r="C40" s="23"/>
+      <c r="D40" s="23"/>
+      <c r="E40" s="23"/>
+      <c r="F40" s="23"/>
+      <c r="G40" s="23"/>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A41" s="15"/>
@@ -19104,58 +19187,58 @@
       <c r="G41" s="15"/>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A42" s="26" t="s">
+      <c r="A42" s="24" t="s">
+        <v>956</v>
+      </c>
+      <c r="B42" s="26" t="s">
+        <v>926</v>
+      </c>
+      <c r="C42" s="27"/>
+      <c r="D42" s="26" t="s">
+        <v>927</v>
+      </c>
+      <c r="E42" s="27"/>
+      <c r="F42" s="26" t="s">
+        <v>928</v>
+      </c>
+      <c r="G42" s="27"/>
+    </row>
+    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A43" s="25"/>
+      <c r="B43" s="10" t="s">
+        <v>929</v>
+      </c>
+      <c r="C43" s="10" t="s">
+        <v>930</v>
+      </c>
+      <c r="D43" s="10" t="s">
+        <v>929</v>
+      </c>
+      <c r="E43" s="10" t="s">
+        <v>930</v>
+      </c>
+      <c r="F43" s="10" t="s">
+        <v>931</v>
+      </c>
+      <c r="G43" s="10" t="s">
+        <v>932</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A44" s="29" t="s">
         <v>957</v>
-      </c>
-      <c r="B42" s="28" t="s">
-        <v>927</v>
-      </c>
-      <c r="C42" s="29"/>
-      <c r="D42" s="28" t="s">
-        <v>928</v>
-      </c>
-      <c r="E42" s="29"/>
-      <c r="F42" s="28" t="s">
-        <v>929</v>
-      </c>
-      <c r="G42" s="29"/>
-    </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A43" s="27"/>
-      <c r="B43" s="10" t="s">
-        <v>930</v>
-      </c>
-      <c r="C43" s="10" t="s">
-        <v>931</v>
-      </c>
-      <c r="D43" s="10" t="s">
-        <v>930</v>
-      </c>
-      <c r="E43" s="10" t="s">
-        <v>931</v>
-      </c>
-      <c r="F43" s="10" t="s">
-        <v>932</v>
-      </c>
-      <c r="G43" s="10" t="s">
-        <v>933</v>
-      </c>
-    </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A44" s="19" t="s">
-        <v>958</v>
       </c>
       <c r="B44" s="12">
         <v>0.33333333333333331</v>
       </c>
       <c r="C44" s="13" t="s">
-        <v>954</v>
+        <v>953</v>
       </c>
       <c r="D44" s="12">
         <v>0.375</v>
       </c>
       <c r="E44" s="13" t="s">
-        <v>943</v>
+        <v>942</v>
       </c>
       <c r="F44" s="16" t="s">
         <v>7</v>
@@ -19165,18 +19248,18 @@
       </c>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A45" s="20"/>
+      <c r="A45" s="30"/>
       <c r="B45" s="12">
         <v>0.54166666666666663</v>
       </c>
       <c r="C45" s="13" t="s">
-        <v>954</v>
+        <v>953</v>
       </c>
       <c r="D45" s="12">
         <v>0.58333333333333337</v>
       </c>
       <c r="E45" s="13" t="s">
-        <v>943</v>
+        <v>942</v>
       </c>
       <c r="F45" s="16" t="s">
         <v>7</v>
@@ -19187,19 +19270,19 @@
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A46" s="11" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="B46" s="12">
         <v>0.5625</v>
       </c>
       <c r="C46" s="13" t="s">
-        <v>954</v>
+        <v>953</v>
       </c>
       <c r="D46" s="12">
         <v>0.63541666666666663</v>
       </c>
       <c r="E46" s="13" t="s">
-        <v>938</v>
+        <v>937</v>
       </c>
       <c r="F46" s="14">
         <v>550</v>
@@ -19210,19 +19293,19 @@
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A47" s="11" t="s">
-        <v>960</v>
+        <v>959</v>
       </c>
       <c r="B47" s="12">
         <v>0.5625</v>
       </c>
       <c r="C47" s="13" t="s">
-        <v>954</v>
+        <v>953</v>
       </c>
       <c r="D47" s="12">
         <v>0.64583333333333337</v>
       </c>
       <c r="E47" s="13" t="s">
-        <v>936</v>
+        <v>935</v>
       </c>
       <c r="F47" s="14">
         <v>550</v>
@@ -19233,19 +19316,19 @@
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A48" s="11" t="s">
-        <v>961</v>
+        <v>960</v>
       </c>
       <c r="B48" s="12">
         <v>0.5625</v>
       </c>
       <c r="C48" s="13" t="s">
-        <v>954</v>
+        <v>953</v>
       </c>
       <c r="D48" s="12">
         <v>0.72916666666666663</v>
       </c>
       <c r="E48" s="13" t="s">
-        <v>935</v>
+        <v>934</v>
       </c>
       <c r="F48" s="14">
         <v>850</v>
@@ -19256,19 +19339,19 @@
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A49" s="11" t="s">
-        <v>962</v>
+        <v>961</v>
       </c>
       <c r="B49" s="12">
         <v>0.33333333333333331</v>
       </c>
       <c r="C49" s="13" t="s">
-        <v>954</v>
+        <v>953</v>
       </c>
       <c r="D49" s="12">
         <v>0.47916666666666669</v>
       </c>
       <c r="E49" s="13" t="s">
-        <v>935</v>
+        <v>934</v>
       </c>
       <c r="F49" s="14">
         <v>850</v>
@@ -19296,58 +19379,58 @@
       <c r="G51" s="8"/>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A52" s="26" t="s">
+      <c r="A52" s="24" t="s">
+        <v>962</v>
+      </c>
+      <c r="B52" s="26" t="s">
+        <v>926</v>
+      </c>
+      <c r="C52" s="27"/>
+      <c r="D52" s="26" t="s">
+        <v>927</v>
+      </c>
+      <c r="E52" s="27"/>
+      <c r="F52" s="26" t="s">
+        <v>928</v>
+      </c>
+      <c r="G52" s="27"/>
+    </row>
+    <row r="53" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A53" s="25"/>
+      <c r="B53" s="10" t="s">
+        <v>929</v>
+      </c>
+      <c r="C53" s="10" t="s">
+        <v>930</v>
+      </c>
+      <c r="D53" s="10" t="s">
+        <v>929</v>
+      </c>
+      <c r="E53" s="10" t="s">
+        <v>930</v>
+      </c>
+      <c r="F53" s="10" t="s">
+        <v>931</v>
+      </c>
+      <c r="G53" s="10" t="s">
+        <v>932</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A54" s="29" t="s">
         <v>963</v>
-      </c>
-      <c r="B52" s="28" t="s">
-        <v>927</v>
-      </c>
-      <c r="C52" s="29"/>
-      <c r="D52" s="28" t="s">
-        <v>928</v>
-      </c>
-      <c r="E52" s="29"/>
-      <c r="F52" s="28" t="s">
-        <v>929</v>
-      </c>
-      <c r="G52" s="29"/>
-    </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A53" s="27"/>
-      <c r="B53" s="10" t="s">
-        <v>930</v>
-      </c>
-      <c r="C53" s="10" t="s">
-        <v>931</v>
-      </c>
-      <c r="D53" s="10" t="s">
-        <v>930</v>
-      </c>
-      <c r="E53" s="10" t="s">
-        <v>931</v>
-      </c>
-      <c r="F53" s="10" t="s">
-        <v>932</v>
-      </c>
-      <c r="G53" s="10" t="s">
-        <v>933</v>
-      </c>
-    </row>
-    <row r="54" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A54" s="19" t="s">
-        <v>964</v>
       </c>
       <c r="B54" s="12">
         <v>0.40625</v>
       </c>
       <c r="C54" s="13" t="s">
-        <v>938</v>
+        <v>937</v>
       </c>
       <c r="D54" s="12">
         <v>0.47916666666666669</v>
       </c>
       <c r="E54" s="13" t="s">
-        <v>943</v>
+        <v>942</v>
       </c>
       <c r="F54" s="14">
         <v>500</v>
@@ -19357,18 +19440,18 @@
       </c>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A55" s="20"/>
+      <c r="A55" s="30"/>
       <c r="B55" s="12">
         <v>0.65625</v>
       </c>
       <c r="C55" s="13" t="s">
-        <v>938</v>
+        <v>937</v>
       </c>
       <c r="D55" s="12">
         <v>0.72916666666666663</v>
       </c>
       <c r="E55" s="13" t="s">
-        <v>943</v>
+        <v>942</v>
       </c>
       <c r="F55" s="14">
         <v>500</v>
@@ -19379,19 +19462,19 @@
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A56" s="11" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
       <c r="B56" s="12">
         <v>0.44791666666666669</v>
       </c>
       <c r="C56" s="13" t="s">
-        <v>938</v>
+        <v>937</v>
       </c>
       <c r="D56" s="12">
         <v>0.53125</v>
       </c>
       <c r="E56" s="13" t="s">
-        <v>954</v>
+        <v>953</v>
       </c>
       <c r="F56" s="14">
         <v>550</v>
@@ -19401,20 +19484,20 @@
       </c>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A57" s="19" t="s">
-        <v>966</v>
+      <c r="A57" s="29" t="s">
+        <v>965</v>
       </c>
       <c r="B57" s="12">
         <v>0.44791666666666669</v>
       </c>
       <c r="C57" s="13" t="s">
-        <v>938</v>
+        <v>937</v>
       </c>
       <c r="D57" s="12">
         <v>0.52083333333333337</v>
       </c>
       <c r="E57" s="13" t="s">
-        <v>935</v>
+        <v>934</v>
       </c>
       <c r="F57" s="14">
         <v>650</v>
@@ -19424,18 +19507,18 @@
       </c>
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A58" s="20"/>
+      <c r="A58" s="30"/>
       <c r="B58" s="12">
         <v>0.63541666666666663</v>
       </c>
       <c r="C58" s="13" t="s">
-        <v>938</v>
+        <v>937</v>
       </c>
       <c r="D58" s="12">
         <v>0.71875</v>
       </c>
       <c r="E58" s="13" t="s">
-        <v>935</v>
+        <v>934</v>
       </c>
       <c r="F58" s="14">
         <v>650</v>
@@ -19454,58 +19537,58 @@
       <c r="G59" s="14"/>
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A60" s="26" t="s">
+      <c r="A60" s="24" t="s">
+        <v>966</v>
+      </c>
+      <c r="B60" s="26" t="s">
+        <v>926</v>
+      </c>
+      <c r="C60" s="27"/>
+      <c r="D60" s="26" t="s">
+        <v>927</v>
+      </c>
+      <c r="E60" s="27"/>
+      <c r="F60" s="26" t="s">
+        <v>928</v>
+      </c>
+      <c r="G60" s="27"/>
+    </row>
+    <row r="61" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A61" s="25"/>
+      <c r="B61" s="10" t="s">
+        <v>929</v>
+      </c>
+      <c r="C61" s="10" t="s">
+        <v>930</v>
+      </c>
+      <c r="D61" s="10" t="s">
+        <v>929</v>
+      </c>
+      <c r="E61" s="10" t="s">
+        <v>930</v>
+      </c>
+      <c r="F61" s="10" t="s">
+        <v>931</v>
+      </c>
+      <c r="G61" s="10" t="s">
+        <v>932</v>
+      </c>
+    </row>
+    <row r="62" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A62" s="29" t="s">
         <v>967</v>
-      </c>
-      <c r="B60" s="28" t="s">
-        <v>927</v>
-      </c>
-      <c r="C60" s="29"/>
-      <c r="D60" s="28" t="s">
-        <v>928</v>
-      </c>
-      <c r="E60" s="29"/>
-      <c r="F60" s="28" t="s">
-        <v>929</v>
-      </c>
-      <c r="G60" s="29"/>
-    </row>
-    <row r="61" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A61" s="27"/>
-      <c r="B61" s="10" t="s">
-        <v>930</v>
-      </c>
-      <c r="C61" s="10" t="s">
-        <v>931</v>
-      </c>
-      <c r="D61" s="10" t="s">
-        <v>930</v>
-      </c>
-      <c r="E61" s="10" t="s">
-        <v>931</v>
-      </c>
-      <c r="F61" s="10" t="s">
-        <v>932</v>
-      </c>
-      <c r="G61" s="10" t="s">
-        <v>933</v>
-      </c>
-    </row>
-    <row r="62" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A62" s="19" t="s">
-        <v>968</v>
       </c>
       <c r="B62" s="12">
         <v>0.39583333333333331</v>
       </c>
       <c r="C62" s="13" t="s">
-        <v>936</v>
+        <v>935</v>
       </c>
       <c r="D62" s="12">
         <v>0.47916666666666669</v>
       </c>
       <c r="E62" s="13" t="s">
-        <v>943</v>
+        <v>942</v>
       </c>
       <c r="F62" s="14">
         <v>500</v>
@@ -19515,18 +19598,18 @@
       </c>
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A63" s="20"/>
+      <c r="A63" s="30"/>
       <c r="B63" s="12">
         <v>0.64583333333333337</v>
       </c>
       <c r="C63" s="13" t="s">
-        <v>936</v>
+        <v>935</v>
       </c>
       <c r="D63" s="12">
         <v>0.72916666666666663</v>
       </c>
       <c r="E63" s="13" t="s">
-        <v>943</v>
+        <v>942</v>
       </c>
       <c r="F63" s="14">
         <v>500</v>
@@ -19537,19 +19620,19 @@
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A64" s="11" t="s">
-        <v>969</v>
+        <v>968</v>
       </c>
       <c r="B64" s="12">
         <v>0.4375</v>
       </c>
       <c r="C64" s="13" t="s">
-        <v>936</v>
+        <v>935</v>
       </c>
       <c r="D64" s="12">
         <v>0.54166666666666663</v>
       </c>
       <c r="E64" s="13" t="s">
-        <v>954</v>
+        <v>953</v>
       </c>
       <c r="F64" s="14">
         <v>550</v>
@@ -19559,20 +19642,20 @@
       </c>
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A65" s="19" t="s">
-        <v>970</v>
+      <c r="A65" s="29" t="s">
+        <v>969</v>
       </c>
       <c r="B65" s="12">
         <v>0.4375</v>
       </c>
       <c r="C65" s="13" t="s">
-        <v>936</v>
+        <v>935</v>
       </c>
       <c r="D65" s="12">
         <v>0.52083333333333337</v>
       </c>
       <c r="E65" s="13" t="s">
-        <v>935</v>
+        <v>934</v>
       </c>
       <c r="F65" s="14">
         <v>650</v>
@@ -19582,18 +19665,18 @@
       </c>
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A66" s="20"/>
+      <c r="A66" s="30"/>
       <c r="B66" s="12">
         <v>0.625</v>
       </c>
       <c r="C66" s="13" t="s">
-        <v>936</v>
+        <v>935</v>
       </c>
       <c r="D66" s="12">
         <v>0.72916666666666663</v>
       </c>
       <c r="E66" s="13" t="s">
-        <v>935</v>
+        <v>934</v>
       </c>
       <c r="F66" s="14">
         <v>650</v>
@@ -19603,52 +19686,64 @@
       </c>
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A67" s="21" t="s">
-        <v>956</v>
-      </c>
-      <c r="B67" s="22"/>
-      <c r="C67" s="22"/>
-      <c r="D67" s="22"/>
-      <c r="E67" s="22"/>
-      <c r="F67" s="22"/>
-      <c r="G67" s="23"/>
+      <c r="A67" s="19" t="s">
+        <v>955</v>
+      </c>
+      <c r="B67" s="20"/>
+      <c r="C67" s="20"/>
+      <c r="D67" s="20"/>
+      <c r="E67" s="20"/>
+      <c r="F67" s="20"/>
+      <c r="G67" s="21"/>
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A68" s="21" t="s">
-        <v>945</v>
-      </c>
-      <c r="B68" s="22"/>
-      <c r="C68" s="22"/>
-      <c r="D68" s="22"/>
-      <c r="E68" s="22"/>
-      <c r="F68" s="22"/>
-      <c r="G68" s="23"/>
+      <c r="A68" s="19" t="s">
+        <v>944</v>
+      </c>
+      <c r="B68" s="20"/>
+      <c r="C68" s="20"/>
+      <c r="D68" s="20"/>
+      <c r="E68" s="20"/>
+      <c r="F68" s="20"/>
+      <c r="G68" s="21"/>
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A69" s="24" t="s">
-        <v>941</v>
-      </c>
-      <c r="B69" s="25"/>
-      <c r="C69" s="25"/>
-      <c r="D69" s="25"/>
-      <c r="E69" s="25"/>
-      <c r="F69" s="25"/>
-      <c r="G69" s="25"/>
+      <c r="A69" s="28" t="s">
+        <v>940</v>
+      </c>
+      <c r="B69" s="23"/>
+      <c r="C69" s="23"/>
+      <c r="D69" s="23"/>
+      <c r="E69" s="23"/>
+      <c r="F69" s="23"/>
+      <c r="G69" s="23"/>
     </row>
   </sheetData>
   <mergeCells count="50">
-    <mergeCell ref="A8:G8"/>
-    <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="B4:C4"/>
-    <mergeCell ref="D4:E4"/>
-    <mergeCell ref="F4:G4"/>
-    <mergeCell ref="A9:G9"/>
-    <mergeCell ref="A10:G10"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="B12:C12"/>
-    <mergeCell ref="D12:E12"/>
-    <mergeCell ref="F12:G12"/>
+    <mergeCell ref="A65:A66"/>
+    <mergeCell ref="A67:G67"/>
+    <mergeCell ref="A68:G68"/>
+    <mergeCell ref="A69:G69"/>
+    <mergeCell ref="A57:A58"/>
+    <mergeCell ref="A60:A61"/>
+    <mergeCell ref="B60:C60"/>
+    <mergeCell ref="D60:E60"/>
+    <mergeCell ref="F60:G60"/>
+    <mergeCell ref="A62:A63"/>
+    <mergeCell ref="A54:A55"/>
+    <mergeCell ref="A37:G37"/>
+    <mergeCell ref="A38:G38"/>
+    <mergeCell ref="A39:G39"/>
+    <mergeCell ref="A40:G40"/>
+    <mergeCell ref="A42:A43"/>
+    <mergeCell ref="B42:C42"/>
+    <mergeCell ref="D42:E42"/>
+    <mergeCell ref="F42:G42"/>
+    <mergeCell ref="A44:A45"/>
+    <mergeCell ref="A52:A53"/>
+    <mergeCell ref="B52:C52"/>
+    <mergeCell ref="D52:E52"/>
+    <mergeCell ref="F52:G52"/>
     <mergeCell ref="A35:A36"/>
     <mergeCell ref="A14:A16"/>
     <mergeCell ref="A17:A18"/>
@@ -19663,30 +19758,18 @@
     <mergeCell ref="A29:A30"/>
     <mergeCell ref="A31:A32"/>
     <mergeCell ref="A33:A34"/>
-    <mergeCell ref="A54:A55"/>
-    <mergeCell ref="A37:G37"/>
-    <mergeCell ref="A38:G38"/>
-    <mergeCell ref="A39:G39"/>
-    <mergeCell ref="A40:G40"/>
-    <mergeCell ref="A42:A43"/>
-    <mergeCell ref="B42:C42"/>
-    <mergeCell ref="D42:E42"/>
-    <mergeCell ref="F42:G42"/>
-    <mergeCell ref="A44:A45"/>
-    <mergeCell ref="A52:A53"/>
-    <mergeCell ref="B52:C52"/>
-    <mergeCell ref="D52:E52"/>
-    <mergeCell ref="F52:G52"/>
-    <mergeCell ref="A65:A66"/>
-    <mergeCell ref="A67:G67"/>
-    <mergeCell ref="A68:G68"/>
-    <mergeCell ref="A69:G69"/>
-    <mergeCell ref="A57:A58"/>
-    <mergeCell ref="A60:A61"/>
-    <mergeCell ref="B60:C60"/>
-    <mergeCell ref="D60:E60"/>
-    <mergeCell ref="F60:G60"/>
-    <mergeCell ref="A62:A63"/>
+    <mergeCell ref="A9:G9"/>
+    <mergeCell ref="A10:G10"/>
+    <mergeCell ref="A12:A13"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="D12:E12"/>
+    <mergeCell ref="F12:G12"/>
+    <mergeCell ref="A8:G8"/>
+    <mergeCell ref="A2:G2"/>
+    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="B4:C4"/>
+    <mergeCell ref="D4:E4"/>
+    <mergeCell ref="F4:G4"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
